--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2-质量对比不含崔阳'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2b-图数据'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3-重点项目'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3-重点项目'!$A$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4-前期调研清单'!$A$1:$H$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5-该结未结与重复'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'6-有效在手'!$A$1:$H$25</definedName>
@@ -961,7 +961,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>任务标题中标注「重点项目」</t>
+          <t>标题标注「重点项目」；另补录业务确认的2条：菲律宾生力取料机、MAK 2×150吨小仓（已签约）</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>纪律和转化都最好，样本内唯一签约</t>
+          <t>纪律和转化都最好，样本内唯一签约，重点4条都有效</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
@@ -1554,14 +1554,14 @@
         <v>2</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>16条关8条（含1签约）；MAK气力近期可成交、MONCEMENT拜访后有望落地；TESO只要预算、阿根廷希望不大仍进行中</t>
+          <t>16条关8条（含1签约MAK 2×150吨小仓）；在手重点3条：MAK气力近期可成交、MONCEMENT拜访后更新、生力取料机等授标；TESO只要预算、阿根廷希望不大仍进行中</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -2360,10 +2360,10 @@
         <v>2</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>3</v>
@@ -3026,10 +3026,10 @@
         <v>16</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>24</v>
@@ -3343,10 +3343,10 @@
         <v>0.5</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0</v>
@@ -4013,15 +4013,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11.5" customWidth="1" min="4" max="4"/>
     <col width="8.800000000000001" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4250,120 +4250,120 @@
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="9" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>崔阳</t>
+          <t>陈子凡</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>C00009094|崔阳|粮食|75万吨小麦深加工项目|方案V1|重点项目</t>
+          <t>20260304 菲律宾生力集团 取料机报价</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>未填</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>未更新</t>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>崔阳未填进展和状态</t>
+          <t>重点：生力取料机，等授标通知</t>
         </is>
       </c>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>等授标通知</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="9" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>冯乐</t>
+          <t>陈子凡</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
+          <t>20260302 C00007247 MAK 陈子凡 2x150吨小仓方案 报价</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
+          <t>已结项-签约</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>规范闭环</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>曾接受报价，新要求已技术反馈，等农场回复</t>
+          <t>重点：MAK 2×150吨小仓，已成交，样本内唯一签约</t>
         </is>
       </c>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
+          <t>已成交</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="9" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>郭朝伟</t>
+          <t>崔阳</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>20260715|郭朝伟|河南工大|模拟粮仓|方案V1 | 重点项目</t>
+          <t>C00009094|崔阳|粮食|75万吨小麦深加工项目|方案V1|重点项目</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
+          <t>未填</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>未更新</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>方案基本确定，待客户确认</t>
+          <t>崔阳未填进展和状态</t>
         </is>
       </c>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>方案基本确定，带客户确认后在沟通下一步</t>
-        </is>
-      </c>
+      <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>苗恒</t>
+          <t>冯乐</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
+          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -4378,64 +4378,64 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>重点，确认方案V4后更报价V2</t>
+          <t>曾接受报价，新要求已技术反馈，等农场回复</t>
         </is>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
+          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="9" t="n">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>苗恒</t>
+          <t>郭朝伟</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>C00008988｜苗恒｜粮食｜孟加拉2x3000吨稻谷仓项目｜方案V3 | 重点项目</t>
+          <t>20260715|郭朝伟|河南工大|模拟粮仓|方案V1 | 重点项目</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>暂停</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>规范闭环</t>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>重点项目已暂停</t>
+          <t>方案基本确定，待客户确认</t>
         </is>
       </c>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>方案基本确定，带客户确认后在沟通下一步</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="9" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>司斌</t>
+          <t>苗恒</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
+          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -4450,64 +4450,64 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>已到决策期，但钢构单价我方拿不到</t>
+          <t>重点，确认方案V4后更报价V2</t>
         </is>
       </c>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="9" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>王伟超</t>
+          <t>苗恒</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
+          <t>C00008988｜苗恒｜粮食｜孟加拉2x3000吨稻谷仓项目｜方案V3 | 重点项目</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>规范闭环</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>参观工厂，多次方案报价，调图纸等回复</t>
+          <t>重点项目已暂停</t>
         </is>
       </c>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="9" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>王伟乐</t>
+          <t>司斌</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -4522,28 +4522,28 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>咨询公司招投标准备，最新价澄清中</t>
+          <t>已到决策期，但钢构单价我方拿不到</t>
         </is>
       </c>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
+          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="9" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>王伟乐</t>
+          <t>王伟超</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
+          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -4551,25 +4551,97 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>老客户总部项目，已报价继续跟，库龄偏长</t>
+          <t>参观工厂，多次方案报价，调图纸等回复</t>
         </is>
       </c>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="inlineStr">
         <is>
+          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>咨询公司招投标准备，最新价澄清中</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>老客户总部项目，已报价继续跟，库龄偏长</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
           <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6312,7 +6384,11 @@
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>20260304 菲律宾生力集团 取料机报价</t>
@@ -6325,7 +6401,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>等授标通知</t>
+          <t>重点：生力取料机，等授标通知</t>
         </is>
       </c>
       <c r="G7" s="9" t="n"/>
@@ -8721,7 +8797,11 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr"/>
+      <c r="I30" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
           <t>有效跟进</t>
@@ -8729,7 +8809,7 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>等授标通知</t>
+          <t>重点：生力取料机，等授标通知</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
@@ -8774,7 +8854,11 @@
           <t>已结项-签约</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr"/>
+      <c r="I31" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J31" s="28" t="inlineStr">
         <is>
           <t>规范闭环</t>
@@ -8782,7 +8866,7 @@
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>已成交，样本内唯一签约</t>
+          <t>重点：MAK 2×150吨小仓，已成交，样本内唯一签约</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr"/>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -17,6 +17,9 @@
     <sheet name="6-有效在手" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="7-全量明细" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="8-逐人要点" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="9-客户集中度" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10-重复客户明细" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="9b-集中度图数据" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$15</definedName>
@@ -28,6 +31,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'6-有效在手'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'7-全量明细'!$A$1:$Q$170</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'8-逐人要点'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9-客户集中度'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'10-重复客户明细'!$A$1:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'9b-集中度图数据'!$A$1:$C$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -199,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -286,6 +292,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -364,7 +374,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -531,6 +540,128 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>任务条数 vs 客户数（C编码去重，无编码各计1）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'9b-集中度图数据'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'9b-集中度图数据'!$A$2:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'9b-集中度图数据'!$B$2:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'9b-集中度图数据'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'9b-集中度图数据'!$A$2:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'9b-集中度图数据'!$C$2:$C$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>数量</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -541,6 +672,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1861,6 +2019,2243 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11.6" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11.6" customWidth="1" min="8" max="8"/>
+    <col width="11.6" customWidth="1" min="9" max="9"/>
+    <col width="13.2" customWidth="1" min="10" max="10"/>
+    <col width="16.4" customWidth="1" min="11" max="11"/>
+    <col width="13.2" customWidth="1" min="12" max="12"/>
+    <col width="11.6" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>提报任务数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>条人均</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>有编码任务</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>有编码客户数</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>无编码任务</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>最大客户编码</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>最大客户简称</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>最大客户任务数</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>最大客户占本人任务</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>前3客户任务数</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>前3客户占比</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>重复客户数_至少2条</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>重复客户数_至少3条</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" s="27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>工业 Powerz螺旋输送机采购</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" s="30" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>C00009786</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>粮食 斯里兰卡10x2000吨稻谷仓项目</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="30" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="30" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>C00008345</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>粮食 咖啡仓方仓</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="30" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>工业 韩国Jeju-四套污泥仓</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" s="30" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>C00007247</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>工业 MAK砖厂现有气力输送系统更新项目 重点项目</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>C00008577</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>粮食 哈萨克斯坦4×3500吨粮食项目</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" s="30" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>越南QNC料场项目</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" s="30" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>C00009797</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>工业 新加坡波纹钢板储水罐</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="30" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>C00006335</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>粮食 苏丹农业银行粮储项目 V1</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="30" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>C00009344</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>工业 土库曼斯坦火车装载料斗项目</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="30" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>C00009858</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>粮食 斯里兰卡汉班托塔Golden Harvest Mill3x1500MT小麦</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>C00009593</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>粮食 乌干达生咖啡豆筒仓项目</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>郭朝伟</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>合计（客户不跨人去重）</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>169</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>141</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>141</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>113</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" s="31" t="inlineStr"/>
+      <c r="I15" s="31" t="inlineStr"/>
+      <c r="J15" s="31" t="inlineStr"/>
+      <c r="K15" s="31" t="inlineStr"/>
+      <c r="L15" s="31" t="inlineStr"/>
+      <c r="M15" s="31" t="inlineStr"/>
+      <c r="N15" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="O15" s="31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>客户编码</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>该客户任务数</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>任务标题</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>C00006570|崔阳|工业|Powerz螺旋输送机采购|方案V1</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>C00006570|崔阳|工业|POWERZ0508设备采购|方案V1</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>C00006570|崔阳|工业|灰渣气力输送项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>C00006570 Powerz 崔阳 工业 底渣输送机 方案V1</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>C00006570 Powerz 崔阳 工业 旋转给料系统 方案V1</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>C00006570 Powerz 崔阳  20260214 旋转阀</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>C00006570|崔阳|工业|Powerz输送机采购|方案V1</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>C00007843|崔阳|工业|Эннова散装机|方案V1</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>C00007843|崔阳|工业|Эннова新库兹涅兹克电厂烟气净化与脱硫系统项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>C00007843|崔阳|工业|石灰料仓及气力输送设备|方案V1</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>C00007843 | 崔阳 | 工业 | 哈萨克热列兹肯特热电站10号机组烟气净化（脱硫，除尘）项目 | 方案V1</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>C00007843 | 崔阳 | 工业 | 外贝加尔发电厂项目 | 方案</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>C00006514</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes哈萨克斯坦4个矿石仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>C00006514</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes烧碱和硫酸钠化工仓|方案V1</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>C00006514</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes电厂粉煤灰|方案V2</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>C00006514</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>C00006514 KOTEC 崔阳 工业 装配仓 方案V2</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>C00001305｜陈辉｜工业｜韩国Jeju-四套污泥仓｜方案V1</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>C00001305｜陈辉｜工业｜韩国welcron5套污泥仓｜方案V1</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>C00001305｜陈辉｜工业｜韩国140立方米 x 3套树脂仓｜方案V1</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>C00001305｜陈辉｜工业｜韩国3,000立方米 x 2套石膏粉仓｜方案V2</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>C00008036/韩鸿彪/越南QNC料场项目/方案V2</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>C00008036|韩鸿彪|工业|越南QNC-Halong2x1500T水泥仓方案V2</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>C00008036 韩鸿彪 越南 4x6000T筒仓系统配套输送设备方案 V5</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>C00008036|韩鸿彪|工业|越南QNC船对船水泥输送系统|方案V1</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>C00008345</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>C00008345｜司斌｜粮食｜咖啡仓方仓 |方案V1</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>C00008345</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>C00008345｜司斌｜粮食｜咖啡缓冲斗｜方案V1</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>C00008345</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>C00008345｜司斌｜粮食｜Probat国内咖啡仓方仓 |方案V1</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>C00009344</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>C00009344｜冯乐｜工业｜土库曼斯坦火车装载料斗项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>C00009344</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>C00009344｜冯乐｜新疆｜PP掺混料仓×10+PE掺混料仓×10项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>C00008577</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>C00008577｜尹韬越｜粮食｜哈萨克斯坦4×3500吨粮食项目｜方案V2</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>C00008577</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>C00008577 尹韬越哈萨克斯坦4×3500吨粮食项目 方案1</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>C00009055</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>C00009055 崔阳|工业|CC7 Europe 化工回收项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>C00009055</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>C00009055 崔阳|工业|CC7 Europe 石灰给料包项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>C00009506</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>C00009506  |崔阳|粮食| RUSAGRO农作物种子加工厂项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>C00009506</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>C00009506|崔阳|粮食| RUSAGRO大豆深度加工综合生产线|方案V1</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>C00001534</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>C00001534|崔阳|粮食| 30000吨 SILOS KZ 粮储综合体项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>C00001534</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>C00001534|崔阳|粮食| 1000吨小麦仓SILOS KZ 粮仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>已结项-丢单</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>C00007247</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>进行中，近期可成交</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>C00007247</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>20260302 C00007247 MAK 陈子凡 2x150吨小仓方案 报价</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>结项-签约</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>C00009244</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>C00009244｜陈辉｜工业｜火车卸料项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>C00009244</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>C00009244｜陈辉｜工业｜巴西钢板仓和卸到火车项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F42"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>提报任务数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>客户数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>郭朝伟</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -20,6 +20,7 @@
     <sheet name="9-客户集中度" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="10-重复客户明细" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="9b-集中度图数据" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="11-打单能力排名" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
@@ -34,6 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9-客户集中度'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'10-重复客户明细'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'9b-集中度图数据'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'11-打单能力排名'!$A$1:$R$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -205,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -293,6 +295,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -371,7 +382,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -540,7 +550,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -4465,6 +4474,851 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>提报</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>签约</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>有效在手</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>有效项目</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>有效项目率</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>每客户有效项目</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>进行中跟住率</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>注水条数</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>注水率</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>重点</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>重点有效</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>成色榜</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>火力榜</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>客户产出榜</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>注水榜（越高越差）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="32" t="n">
+        <v>0.131578947368421</v>
+      </c>
+      <c r="H2" s="33" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="I2" s="32" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="J2" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" s="32" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="L2" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="31" t="inlineStr"/>
+      <c r="O2" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" s="31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="32" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="H3" s="33" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="I3" s="32" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="32" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="31" t="inlineStr"/>
+      <c r="O3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="H4" s="33" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="I4" s="32" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="J4" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="32" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="L4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="31" t="inlineStr"/>
+      <c r="O4" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="R4" s="31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="32" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="H5" s="33" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="I5" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="31" t="inlineStr"/>
+      <c r="O5" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" s="31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="33" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="31" t="inlineStr"/>
+      <c r="O6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="32" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="I7" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="L7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="31" t="inlineStr"/>
+      <c r="O7" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" s="31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="H8" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="L8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="31" t="inlineStr"/>
+      <c r="O8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="31" t="inlineStr"/>
+      <c r="O9" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" s="31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J10" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L10" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="31" t="inlineStr"/>
+      <c r="O10" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" s="31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="32" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J11" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L11" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O11" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R11" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O12" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O13" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R13" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>口径：有效项目=签约+有效在手；注水=前期调研+该结未结+重复开单；排名仅对提报≥8的人。冯乐/张硕/王伟超样本不足，不进主排名。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A16:R16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -21,6 +21,8 @@
     <sheet name="10-重复客户明细" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="9b-集中度图数据" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="11-打单能力排名" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="12-丢单排名" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="13-丢单明细" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
@@ -207,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -303,6 +305,15 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5319,6 +5330,1599 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B1" s="34" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="C1" s="34" t="inlineStr">
+        <is>
+          <t>提报</t>
+        </is>
+      </c>
+      <c r="D1" s="34" t="inlineStr">
+        <is>
+          <t>丢单条数</t>
+        </is>
+      </c>
+      <c r="E1" s="34" t="inlineStr">
+        <is>
+          <t>丢单占提报</t>
+        </is>
+      </c>
+      <c r="F1" s="34" t="inlineStr">
+        <is>
+          <t>主因（按条数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>选其他/当地供应商6条；价格5条；未立项/取消/我方不做7条；失联1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="35" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>客户失联5条；需求不实2条；业主选混凝土仓1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="35" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>澄清未回后失联4条；做不了/风险过大主动停2条；交期1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>体量小主动放弃2条；钢构价格1条；益海砍预算1条；生力临建土建占比高未参与1条；中间商真实性存疑1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>价格3条；客户失联1条；报后无回复就结了1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>客户未反馈3条；客户失联1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>报价后失联3条；工艺做不了1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>客户改计划2条；价格不及当地供应商1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>客户失联2条</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>价格超预算1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>非终端业主、信息不全后失联1条</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>无（6条全进行中，尚未关账）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>口径：状态为已结项-丢单 / 已结项 的 60 条。不含暂停。国际业务部，已剔郭朝伟。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A16:F16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="36" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C1" s="36" t="inlineStr">
+        <is>
+          <t>归并原因</t>
+        </is>
+      </c>
+      <c r="D1" s="36" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>选其他供应商</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Powerz 设备采购，业主选其他家</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>选当地供应商</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Powerz 灰渣气力</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>选其他供应商</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Powerz 旋转给料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>选其他供应商</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Powerz 输送机</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>选当地供应商</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>75 吨熟石灰仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>选其他供应商</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Астон 葵花籽仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>价格过高</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>UZMET 铁合金石灰仓储，业主不继续</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>价格+资料不完整</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>SILOS KZ 30000 吨投标</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>价格+资料不完整</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>SILOS KZ 1000 吨，与 48 同一客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>价格过高</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>ELFORS 谷物码头，选其他家</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>价格敏感</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>粮食储运，选其他家</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>技术方案不满足</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Бункер-Порт 氧化铝，未进报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>报后一直说在考虑</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Anush 饲料仓，已结</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>产能存疑后取消</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Эннова 石灰仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>改选其他工艺</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>麻类深加工</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>我方主动拒绝</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Powerz 旋转阀，未报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>客户结束询价</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>cotes/KOTEC 装配仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>业主未立项</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ROSATOM 氧化铝仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>报价后失联</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>500 吨水泥仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>印尼 1×5000 玉米仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>阿联酋玻璃瓶厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>也门麸皮仓，更新后无答复</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>德国水泥仓+打包机</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>马拉维大豆仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>需求不实</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>孟加拉 4×18000 玉米仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>119</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>需求不实</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>土耳其石灰石粉末仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>选混凝土仓</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>印度 45000 吨氧化铝港口</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>澄清未回/兴趣不大</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>保加利亚 DPM 50 吨消石灰仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>澄清未回后失联</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>澳洲维多利亚农场仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>图纸错误澄清未回后失联</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>智利麦麸料斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>报价后失联</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>阿尔及利亚 6×5000 干燥</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>风险过大主动停</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>科特迪瓦可可豆，改与电建合作</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>做不了</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>污泥刮板机无法做</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>交期不满足</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>科特迪瓦航油罐，选土耳其钢板</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>体量小主动放弃</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>毛里求斯塑料圆仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>体量小主动放弃</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>印尼碳酸钙仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>钢构价格无竞争力</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>生力 SMC 平方仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>工厂砍预算</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>益海大豆仓，改修旧仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>土建占比高未参与</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>生力机场临建 EPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>中间商真实性存疑</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>南美水泥仓，北京中间商</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>哈萨克 4×3000 粮食</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>哈萨克 1×5000 粮仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>哈萨克 70000 吨筒仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>乌拉尔斯克转运站</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>报后无回复就结了</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>苏亚克磷矿石磨制</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>报价未反馈</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>德方仓和钢构</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>报给当地华人后不反馈</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>菲律宾 3×1000 玉米仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>报价无反馈</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>沙特 1×2000 水泥仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>出方案后失联</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>塞舌尔水泥码头</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>报价后不再联系</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>越南 500 吨粉煤灰</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>工厂未投用/按失联</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>马来发放仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>收集价格后失联</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>苏丹码头小麦仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>工艺做不了</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>蒙古 60 吨沙仓热能存储</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>客户改计划</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Kim Jeju 污泥仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>客户改计划</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Kim welcron 污泥仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>价格不及当地</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Kim 石膏粉仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>苏里南糙米碾白线</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>客户失联</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Sibelco 法国石英砂</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>预算远低于报价</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>南非 5×5000 玉米仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>非终端业主后失联</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>巴拿马粮库改造</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -23,6 +23,8 @@
     <sheet name="11-打单能力排名" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="12-丢单排名" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="13-丢单明细" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="14-多项目客户排名" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="15-多项目客户明细" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
@@ -90,7 +92,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -182,6 +184,11 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -209,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -313,6 +320,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6923,6 +6936,1075 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B1" s="37" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C1" s="37" t="inlineStr">
+        <is>
+          <t>编码</t>
+        </is>
+      </c>
+      <c r="D1" s="37" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="E1" s="37" t="inlineStr">
+        <is>
+          <t>项目数</t>
+        </is>
+      </c>
+      <c r="F1" s="37" t="inlineStr">
+        <is>
+          <t>已丢单</t>
+        </is>
+      </c>
+      <c r="G1" s="37" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="H1" s="37" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="I1" s="37" t="inlineStr">
+        <is>
+          <t>有效在手</t>
+        </is>
+      </c>
+      <c r="J1" s="37" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="K1" s="37" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>C00006570</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>5条已丢给当地/其他供应商；1条底渣机该暂停未停；1条已报价等回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>C00007843</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>1条已丢；3条方案未出数月写希望不大仍进行中；1条已报价等评审</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>菲律宾生力集团</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>（无编码，业务确认并户）</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>临建、SMC平方仓已丢；取料机等授标；锥底仓已报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>韩国 Kim</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>C00001305</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>渠道多询</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>一个渠道四条询价：污泥2条改计划、石膏粉价格不及当地、树脂暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>cotes</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>C00006514</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>矿石仓、粉煤灰仍在技术探讨；烧碱仓已报价；装配仓已丢</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>越南 QNC</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>C00008036</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>料场、船对船已暂停；包装线/输送在跟；广宁雨棚2条无编码未并入</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>咖啡仓</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>C00008345</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>方仓、缓冲斗、Probat国内方仓三条全挂进行中，该关没关</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>口径：国际业务部；同一客户键项目数&gt;2。陈子凡生力/SMC/Manila01已并户。刚好2条的客户不进本榜。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:K10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B1" s="38" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="C1" s="38" t="inlineStr">
+        <is>
+          <t>项目数</t>
+        </is>
+      </c>
+      <c r="D1" s="38" t="inlineStr">
+        <is>
+          <t>条目</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>35 进行中 浅层 螺旋输送机</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>52 丢单 设备采购 POWERZ0508</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>61 丢单 灰渣气力</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>62 进行中 该结未结 底渣输送机</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>64 丢单 旋转给料</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>66 丢单 旋转阀 我方拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Powerz</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>71 丢单 输送机采购</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>41 进行中 浅层 散装机已报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>51 进行中 该结未结 新库兹涅兹克脱硫 方案未出3个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>55 丢单 石灰仓产能取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>65 进行中 该结未结 哈萨克热电站脱硫 方案未出5个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Эннова</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>69 进行中 该结未结 外贝加尔电厂 方案未出6个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>菲律宾生力集团</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>25 丢单 机场临建 EPC土建占比高未参与</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>菲律宾生力集团</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>26 丢单 SMC平方仓 钢构价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>菲律宾生力集团</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>29 进行中 有效 取料机等授标</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>菲律宾生力集团</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>33 进行中 浅层 4×2000锥底仓已报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>韩国 Kim</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>3 丢单 Jeju污泥仓 客户改计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>韩国 Kim</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>4 丢单 welcron污泥仓 客户改计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>韩国 Kim</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>5 暂停 树脂仓 客户决策中</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>韩国 Kim</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>8 丢单 石膏粉仓 价格不及当地</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>cotes</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>39 进行中 有效 哈萨克4个矿石仓 技术探讨</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>cotes</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>46 进行中 浅层 烧碱和硫酸钠化工仓 已报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>cotes</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>53 进行中 有效 电厂粉煤灰 技术探讨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>cotes</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>67 丢单 KOTEC装配仓 客户结束询价</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>越南 QNC</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>84 暂停 料场规划后延</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>越南 QNC</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>86 进行中 浅层 Halong 2×1500水泥仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>越南 QNC</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>89 进行中 有效 4×6000筒仓配套输送 V5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>越南 QNC</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>92 暂停 船对船水泥输送 报价过高</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>咖啡仓</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>125 进行中 该结未结 咖啡仓方仓 三次报价无反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>咖啡仓</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>127 进行中 重复开单 咖啡缓冲斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>咖啡仓</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>136 进行中 重复开单 Probat国内咖啡仓方仓</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -25,6 +25,8 @@
     <sheet name="13-丢单明细" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="14-多项目客户排名" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="15-多项目客户明细" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="16-进行中阶段" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="17-进行中明细" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
@@ -50,7 +52,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,8 +93,12 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -189,6 +195,11 @@
         <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -216,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -326,6 +337,33 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8005,6 +8043,356 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="39" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="C1" s="39" t="inlineStr">
+        <is>
+          <t>前期调研</t>
+        </is>
+      </c>
+      <c r="D1" s="39" t="inlineStr">
+        <is>
+          <t>报价后观望</t>
+        </is>
+      </c>
+      <c r="E1" s="39" t="inlineStr">
+        <is>
+          <t>报价后决策</t>
+        </is>
+      </c>
+      <c r="F1" s="39" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B3" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="n">
+        <v>86</v>
+      </c>
+      <c r="C14" s="41" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="F14" s="41" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>口径：只统计状态=进行中。前期=规划/预算/立项/技术探讨未报价；观望=已报价后主要是等；决策=已报价且业主在比选/评审/澄清/授标/见面/征地/决策层；其他=该结未结+重复开单+方案未出数月+进展空。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A16:F16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9130,6 +9518,2639 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C1" s="42" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="D1" s="42" t="inlineStr">
+        <is>
+          <t>阶段说明</t>
+        </is>
+      </c>
+      <c r="E1" s="42" t="inlineStr">
+        <is>
+          <t>任务标题</t>
+        </is>
+      </c>
+      <c r="F1" s="42" t="inlineStr">
+        <is>
+          <t>当前进展</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="C2" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D2" s="43" t="inlineStr">
+        <is>
+          <t>勘察后出最终方案</t>
+        </is>
+      </c>
+      <c r="E2" s="43" t="inlineStr">
+        <is>
+          <t>C00005424|崔阳|工业|Sibur塑料颗粒的气力输送项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F2" s="43" t="inlineStr">
+        <is>
+          <t>项目进行实地勘察后，技术部正在出最终方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="inlineStr">
+        <is>
+          <t>报价已交最终业主，等回复</t>
+        </is>
+      </c>
+      <c r="E3" s="43" t="inlineStr">
+        <is>
+          <t>C00006570|崔阳|工业|Powerz螺旋输送机采购|方案V1</t>
+        </is>
+      </c>
+      <c r="F3" s="43" t="inlineStr">
+        <is>
+          <t>项目报价已提交最终业主</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>方案未出，仍在找厂家</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>C00006458 崔阳|工业|达涅利 辊道和步进梁项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="F4" s="43" t="inlineStr">
+        <is>
+          <t>正在寻找相应生产厂家，方案未出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="n">
+        <v>37</v>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>已报价，业主让等待回复</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>C00009596   崔阳|工业|乌克兰AIK-EKO 铜矿石筒仓项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="F5" s="43" t="inlineStr">
+        <is>
+          <t>报价已报出，业主让等待回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>资质已交业主审查</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>C00009055 崔阳|工业|CC7 Europe 化工回收项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>已将我方资质提交最终业主，业主进行资质审查</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>cotes矿石仓技术探讨，未报价</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes哈萨克斯坦4个矿石仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>处于技术探讨阶段 还未报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>报价给中间人，等业主审核</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>C00009720|崔阳|工业|乌兹别克斯坦撒马尔罕3000吨水泥厂项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>报价提供给中间人，中间人让等待业主审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>已报价，最终业主评审中</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>C00007843|崔阳|工业|Эннова散装机|方案V1</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>已提供报价 最终业主在评审</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>客户提议9月现场考察</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>C00009506  |崔阳|粮食| RUSAGRO农作物种子加工厂项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>客户提议九月份进行现场考察</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>与38同一CC7项目</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>C00009055 崔阳|工业|CC7 Europe 石灰给料包项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>和38是同一个项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>已报价cotec，无节点</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes烧碱和硫酸钠化工仓|方案V1</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>已报价给cotec 正在继续跟进中</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>初步报价，业主评估中</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>C00009347 |崔阳|粮食| Ebad Pir Moradian Global Skills 40000吨储粮项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>初步报价已提出，业主需要进行评估，和提交技术部门进行探讨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>51</v>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>方案未出3个月，希望不大</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>C00007843|崔阳|工业|Эннова新库兹涅兹克电厂烟气净化与脱硫系统项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>方案未出，时间跨度已经三个月，希望以不大，</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
+        <v>53</v>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>cotes粉煤灰技术探讨，未报价</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes电厂粉煤灰|方案V2</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
+        <is>
+          <t>处于技术探讨阶段 还未报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>58</v>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>重点只写「进行中 重点任务」</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>C00009094|崔阳|粮食|75万吨小麦深加工项目|方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>进行中 重点任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>找不到设备，该停未停</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>C00006570 Powerz 崔阳 工业 底渣输送机 方案V1</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>方案未出，国内找不到相应适合设备 暂停中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>方案未出5个月，希望不大</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>C00007843 | 崔阳 | 工业 | 哈萨克热列兹肯特热电站10号机组烟气净化（脱硫，除尘）项目 | 方案V1</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>方案未出，时间跨度已经五个月，希望以不大，</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="n">
+        <v>69</v>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>方案未出6个月，希望不大</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>C00007843 | 崔阳 | 工业 | 外贝加尔发电厂项目 | 方案</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>方案未出，时间跨度已经六个月，希望以不大，</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>立项阶段，自称暂停仍挂着</t>
+        </is>
+      </c>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>C00009506|崔阳|粮食| RUSAGRO大豆深度加工综合生产线|方案V1</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
+        <is>
+          <t>1.项目属于立项阶段，我方技术分析后，认为我们参与部分不是很多，决定暂时暂停任务，观望后再说</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>港口规划，已报预算</t>
+        </is>
+      </c>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>C00003352｜陈辉｜工业｜埃及4万吨料场项目｜方案V1（预算）</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
+        <is>
+          <t>TCI预期拿到了埃及一港口的运营权，有计划建散料库，已报预算，还在规划阶段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>大宇多次报价，双方比仓型</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F22" s="43" t="inlineStr">
+        <is>
+          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>塞拉利昂已拜访，缺资金</t>
+        </is>
+      </c>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>C00002715｜陈辉｜工业｜塞拉利昂2个3万吨clinker项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
+        <is>
+          <t>已去拜访客户，客户想法很多，缺资金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>突尼斯粮仓，还在找钱</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>C00009463｜陈辉｜粮食｜突尼斯粮仓6x5,000t+10x8,000t｜方案V1</t>
+        </is>
+      </c>
+      <c r="F24" s="43" t="inlineStr">
+        <is>
+          <t>突尼斯一家工程公司想建这几个粮仓，没有资金，要靠国外银行给贷款，介绍了TCI给他们。项目还在找钱的阶段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>大宇卸料，等DY分包结果</t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="inlineStr">
+        <is>
+          <t>C00009287｜陈辉｜工业｜大宇8套磷矿粉平底仓卸料｜方案V1</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
+        <is>
+          <t>大宇在土库曼化肥厂项目，筒仓的卸料分包给了韩国的一家公司DY，我们给DY报价，仅报一次，技术澄清比较多，DY如果中标大概率优选选我们。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>火车卸料，项目计划评审</t>
+        </is>
+      </c>
+      <c r="E26" s="43" t="inlineStr">
+        <is>
+          <t>C00009244｜陈辉｜工业｜火车卸料项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F26" s="43" t="inlineStr">
+        <is>
+          <t>客户自有仓，让我们报火车卸料后进仓和出仓相关设备。
+客户的项目仍在计划评审阶段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Lanwa老客户，利润被压着比</t>
+        </is>
+      </c>
+      <c r="E27" s="43" t="inlineStr">
+        <is>
+          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F27" s="43" t="inlineStr">
+        <is>
+          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>配合埃及总包投标</t>
+        </is>
+      </c>
+      <c r="E28" s="43" t="inlineStr">
+        <is>
+          <t>C00006497｜陈辉｜粮食｜埃及面粉项目｜方案V1（仅仓和钢构）</t>
+        </is>
+      </c>
+      <c r="F28" s="43" t="inlineStr">
+        <is>
+          <t>埃及总包的一个投标项目，我们报价配合其投标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>埃及建筑公司投铝厂</t>
+        </is>
+      </c>
+      <c r="E29" s="43" t="inlineStr">
+        <is>
+          <t>C00009849｜陈辉｜工业｜埃及3万吨混凝土仓（存氧化铝）项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F29" s="43" t="inlineStr">
+        <is>
+          <t>埃及的建筑公司作为投标人之一，向铝厂投标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>巴西仓，规划阶段了解价格</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>C00009244｜陈辉｜工业｜巴西钢板仓和卸到火车项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F30" s="43" t="inlineStr">
+        <is>
+          <t>规划阶段，客户未来可能有两万吨粘土仓的需求，目前只是了解仓型和价格。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>澳洲装配仓，预算评估仓型</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="inlineStr">
+        <is>
+          <t>C00009852｜陈辉｜工业｜澳洲8x6000t水泥装配仓｜方案V1（钢构量）</t>
+        </is>
+      </c>
+      <c r="F31" s="43" t="inlineStr">
+        <is>
+          <t>预算。客户仍在评估是建造混凝土仓or钢板仓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n">
+        <v>17</v>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>莱歇镀锌仓，业主询价比是否分包</t>
+        </is>
+      </c>
+      <c r="E32" s="43" t="inlineStr">
+        <is>
+          <t>C00003392｜陈辉｜工业｜莱歇6个热镀锌仓项目｜方案V1（钢构量）</t>
+        </is>
+      </c>
+      <c r="F32" s="43" t="inlineStr">
+        <is>
+          <t>莱歇在台北正在做的磨粉项目，这几个仓是原本是业主范围，现在想拿出来询价，来决定是分包给莱歇去做还是业主自己做。
+莱歇要求足够低价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="n">
+        <v>123</v>
+      </c>
+      <c r="C33" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>路易达孚只要预算</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>C00009733｜司斌｜粮食｜印度路易达孚4x500咖啡仓 |方案V1</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
+        <is>
+          <t>路易达孚印度公司咖啡公司，项目处于调研阶段，只要了预算，待管理层决定，不一定会上</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="n">
+        <v>124</v>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>斯里兰卡稻谷，已到决策期</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="F34" s="43" t="inlineStr">
+        <is>
+          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>咖啡仓三次报价无反馈</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>C00008345｜司斌｜粮食｜咖啡仓方仓 |方案V1</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="inlineStr">
+        <is>
+          <t>客户公司主业咖啡生产线，在全球都有项目，国内与星巴克，瑞幸都有合作。项目处于前期价格咨询。已就此公司进行了三次报价，但均无任何反馈，客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B36" s="43" t="n">
+        <v>126</v>
+      </c>
+      <c r="C36" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>越南灰仓，技术无法澄清</t>
+        </is>
+      </c>
+      <c r="E36" s="43" t="inlineStr">
+        <is>
+          <t>C00009546｜司斌｜工业｜越南6*800+2*450灰仓｜方案V1</t>
+        </is>
+      </c>
+      <c r="F36" s="43" t="inlineStr">
+        <is>
+          <t>对接公司是工程公司，但是主业与我们行业不相关，此项目为投标项目，对接公司与最终业主有过合作，但技术问题无法澄清，虽然发送了报价，但是在较少的技术澄清下，胜率不高</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="n">
+        <v>127</v>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>咖啡缓冲斗，重复开单</t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="inlineStr">
+        <is>
+          <t>C00008345｜司斌｜粮食｜咖啡缓冲斗｜方案V1</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr">
+        <is>
+          <t>与123是同一个客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="n">
+        <v>130</v>
+      </c>
+      <c r="C38" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>越南咖啡改造，方案后无回复</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>C00001287｜司斌｜粮食｜越南咖啡仓改造项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="inlineStr">
+        <is>
+          <t>已合作客户，上次拜访客户想要进行一定的改造，但是发送方案后一直没有任何回复，初步判断改造并非需要解决的大问题，可上可不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="n">
+        <v>131</v>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>多米尼加塑料仓，报价后不再沟通</t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="inlineStr">
+        <is>
+          <t>C00008398｜司斌｜工业｜多米尼加塑料颗粒筒仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
+        <is>
+          <t>客户公司是做木屑颗粒生产加工，目前是收集报价阶段，但是价格发送后不再沟通，初步判断价格不具有任何优势</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n">
+        <v>135</v>
+      </c>
+      <c r="C40" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>阿联酋饲料，工程公司前期调研</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="inlineStr">
+        <is>
+          <t>C00009949｜司斌｜粮食｜阿联酋饲料颗粒，项目在俄罗斯 |方案V1</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="inlineStr">
+        <is>
+          <t>对接公司是工程公司，想要对此项目进行投标，但目前项目信息较少，对于客户端属于前期的调研阶段。由于客户要求的时间较短，无法延期。且采购这段时间忙于投标其他项目，因此预估价格晚于客户逾期3天后，由于客户强调一定要再次时间收到预算，所以不利于后续跟进</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="n">
+        <v>136</v>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>Probat国内方仓，重复开单</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>C00008345｜司斌｜粮食｜Probat国内咖啡仓方仓 |方案V1</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
+        <is>
+          <t>与123是同一个客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="n">
+        <v>137</v>
+      </c>
+      <c r="C42" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
+          <t>伊朗石灰仓，战争前不可能上</t>
+        </is>
+      </c>
+      <c r="E42" s="43" t="inlineStr">
+        <is>
+          <t>C00009745｜司斌｜工业｜伊朗水净化项目石灰仓|方案V1</t>
+        </is>
+      </c>
+      <c r="F42" s="43" t="inlineStr">
+        <is>
+          <t>对接公司是工程公司，项目所处阶段为价格收集，由于霍尔木兹海峡现状，我认为在战争结束前不可能上</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="n">
+        <v>138</v>
+      </c>
+      <c r="C43" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>马来熟料料场，只要预算</t>
+        </is>
+      </c>
+      <c r="E43" s="43" t="inlineStr">
+        <is>
+          <t>C00009743｜司斌｜工业｜马来西亚熟料料场|方案V1</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
+        <is>
+          <t>最终业主是马来西亚的三大水泥厂之一，此项目在前期调研，想要知道预算，需要管理层对此进行评估再判断是否上项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t>TESO，询价或为了解预算</t>
+        </is>
+      </c>
+      <c r="E44" s="43" t="inlineStr">
+        <is>
+          <t>C00009556｜陈子凡｜工业｜蒙古TESO 4x2500水泥中转站｜方案V1</t>
+        </is>
+      </c>
+      <c r="F44" s="43" t="inlineStr">
+        <is>
+          <t>给客户发了方案，待更新报价。准备报价中，但客户主业是食品，本次询价可能只是为了解投资预算。 8月份在蒙古期间约客户见面，客户见面意愿不强</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B45" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>阿根廷面粉仓，希望不大</t>
+        </is>
+      </c>
+      <c r="E45" s="43" t="inlineStr">
+        <is>
+          <t>C00009734｜陈子凡｜粮食｜ 阿根廷6个面粉仓+3个润麦仓+1个麸皮仓 单仓｜重量计算+清单</t>
+        </is>
+      </c>
+      <c r="F45" s="43" t="inlineStr">
+        <is>
+          <t>报过价了，希望不大。客户为工程公司，项目投标中，且对方对中国供应链很了解，价格非常敏感</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C46" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>厄瓜多尔方仓，比价等通知</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="inlineStr">
+        <is>
+          <t>C00007248｜陈子凡｜工业｜厄瓜多尔塑料方仓项目｜清单</t>
+        </is>
+      </c>
+      <c r="F46" s="43" t="inlineStr">
+        <is>
+          <t>客户比价中。提交报价后等通知，本次报价相比1期项目有上涨，客户大概率会找新供应商比价</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B47" s="43" t="n">
+        <v>21</v>
+      </c>
+      <c r="C47" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>北京生物质，较前期</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="inlineStr">
+        <is>
+          <t>XXXXX｜陈子凡｜粮食｜北京生物质颗粒装车仓｜方案V1 | 初步方案</t>
+        </is>
+      </c>
+      <c r="F47" s="43" t="inlineStr">
+        <is>
+          <t>跟进中。项目较前期，联系人在出差，需要过一段时间再联系</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>蒙古MAK气力，近期可成交</t>
+        </is>
+      </c>
+      <c r="E48" s="43" t="inlineStr">
+        <is>
+          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F48" s="43" t="inlineStr">
+        <is>
+          <t>报价中</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B49" s="43" t="n">
+        <v>24</v>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
+        <is>
+          <t>MONCEMENT拜访后更新方案</t>
+        </is>
+      </c>
+      <c r="E49" s="43" t="inlineStr">
+        <is>
+          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F49" s="43" t="inlineStr">
+        <is>
+          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="n">
+        <v>29</v>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
+        <is>
+          <t>生力取料机，等授标</t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>20260304 菲律宾生力集团 取料机报价</t>
+        </is>
+      </c>
+      <c r="F50" s="43" t="inlineStr">
+        <is>
+          <t>等授标通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="n">
+        <v>33</v>
+      </c>
+      <c r="C51" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>生力锥底仓，上周报价等反馈</t>
+        </is>
+      </c>
+      <c r="E51" s="43" t="inlineStr">
+        <is>
+          <t>Manila01｜陈子凡｜粮食｜菲律宾4x2000吨锥底仓｜清单V1 | 报价清单</t>
+        </is>
+      </c>
+      <c r="F51" s="43" t="inlineStr">
+        <is>
+          <t>已提交报价，等反馈。单仓项目，上周报价，等反馈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="n">
+        <v>104</v>
+      </c>
+      <c r="C52" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>斯里兰卡稻谷，报价后反馈不积极</t>
+        </is>
+      </c>
+      <c r="E52" s="43" t="inlineStr">
+        <is>
+          <t>C00009786｜苗恒｜粮食｜斯里兰卡10x2000吨稻谷仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F52" s="43" t="inlineStr">
+        <is>
+          <t>客户与土耳其ALTINBILEK有合作，上次报价大概率找我们探价和比价，报价后反馈不积极</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B53" s="43" t="n">
+        <v>105</v>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>新加坡熟石灰，约8月底/9月初反馈</t>
+        </is>
+      </c>
+      <c r="E53" s="43" t="inlineStr">
+        <is>
+          <t>C00009762｜苗恒｜工业｜新加坡4x200m3熟石灰粉不锈钢仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F53" s="43" t="inlineStr">
+        <is>
+          <t>跟进中，客户为工程公司，回复8月底或9月初给我们反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B54" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D54" s="43" t="inlineStr">
+        <is>
+          <t>阿尔及利亚气力，9月更多现场信息</t>
+        </is>
+      </c>
+      <c r="E54" s="43" t="inlineStr">
+        <is>
+          <t>C00009353｜苗恒｜工业｜阿尔及利亚6x2500吨水泥仓+200TPH气力输送项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F54" s="43" t="inlineStr">
+        <is>
+          <t>跟进中，客户给了港口项目布置图，正在沟通方案布局，9月份客户会给更多项目现场信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B55" s="43" t="n">
+        <v>109</v>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="inlineStr">
+        <is>
+          <t>墨西哥粮仓，确认V4后更报价</t>
+        </is>
+      </c>
+      <c r="E55" s="43" t="inlineStr">
+        <is>
+          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F55" s="43" t="inlineStr">
+        <is>
+          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B56" s="43" t="n">
+        <v>113</v>
+      </c>
+      <c r="C56" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>斯里兰卡熟料，已联真实业主</t>
+        </is>
+      </c>
+      <c r="E56" s="43" t="inlineStr">
+        <is>
+          <t>C00009001｜苗恒｜工业｜斯里兰卡1x35000吨熟料仓项目｜方案V2</t>
+        </is>
+      </c>
+      <c r="F56" s="43" t="inlineStr">
+        <is>
+          <t>重点项目跟进中，客户找了江苏鹏飞做的整厂规划布置，让我们报混凝土仓报价，准备给客户更新第二版</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B57" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D57" s="43" t="inlineStr">
+        <is>
+          <t>伊拉克水泥仓，9.2上海见面</t>
+        </is>
+      </c>
+      <c r="E57" s="43" t="inlineStr">
+        <is>
+          <t>C00009921｜苗恒｜工业｜伊拉克2x10000吨水泥仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F57" s="43" t="inlineStr">
+        <is>
+          <t>已报价，客户预计9.2到上海，希望可以见一面</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="43" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="B58" s="43" t="n">
+        <v>121</v>
+      </c>
+      <c r="C58" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="inlineStr">
+        <is>
+          <t>与伊拉克同项目，重复开单</t>
+        </is>
+      </c>
+      <c r="E58" s="43" t="inlineStr">
+        <is>
+          <t>C00009883｜苗恒｜工业｜德国3x1600吨水泥仓+3个料斗投标项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F58" s="43" t="inlineStr">
+        <is>
+          <t>与上面伊拉克2x10000同属一个项目，需要等最终业主确认哪个方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="43" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B59" s="43" t="n">
+        <v>72</v>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="inlineStr">
+        <is>
+          <t>坦桑小麦仓，新技术要求已反馈</t>
+        </is>
+      </c>
+      <c r="E59" s="43" t="inlineStr">
+        <is>
+          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F59" s="43" t="inlineStr">
+        <is>
+          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B60" s="43" t="n">
+        <v>73</v>
+      </c>
+      <c r="C60" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="inlineStr">
+        <is>
+          <t>尼日利亚，中间商代询比价</t>
+        </is>
+      </c>
+      <c r="E60" s="43" t="inlineStr">
+        <is>
+          <t>C00009584|冯乐|粮食|尼日利亚-2×1200T玉米仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F60" s="43" t="inlineStr">
+        <is>
+          <t>目前是一位中间贸易商替业主询价，我方已提供方案和报价，多家供应商对比。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="43" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B61" s="43" t="n">
+        <v>74</v>
+      </c>
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>也门装配仓V3，技术澄清中</t>
+        </is>
+      </c>
+      <c r="E61" s="43" t="inlineStr">
+        <is>
+          <t>C00009383｜冯乐｜工业｜也门-3×1200m³水泥装配仓项目｜方案V3</t>
+        </is>
+      </c>
+      <c r="F61" s="43" t="inlineStr">
+        <is>
+          <t>已进行多次报价，客户对价格比较敏感，目前正在和对方团队进行技术澄清。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B62" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="C62" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
+        <is>
+          <t>土库曼料斗，等总包更新</t>
+        </is>
+      </c>
+      <c r="E62" s="43" t="inlineStr">
+        <is>
+          <t>C00009344｜冯乐｜工业｜土库曼斯坦火车装载料斗项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F62" s="43" t="inlineStr">
+        <is>
+          <t>客户是总承包商，我们是分包，已进行过两次商务报价。整个项目比较大，我们只负责料斗报价，目前等总包更新项目进展。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B63" s="43" t="n">
+        <v>76</v>
+      </c>
+      <c r="C63" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>阿根廷储存仓，业主规划收集报价</t>
+        </is>
+      </c>
+      <c r="E63" s="43" t="inlineStr">
+        <is>
+          <t>C00009727｜冯乐｜粮食｜阿根廷2×3000T+6×800T 储存仓项目｜方案V2</t>
+        </is>
+      </c>
+      <c r="F63" s="43" t="inlineStr">
+        <is>
+          <t>直接业主，是一家从农田到深加工全产业链的农业综合集团，该项目是业主的规划项目。目前处于收集多方供应商的方案和报价，我方已提供商务报价。等待业主回复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="43" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="B64" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="inlineStr">
+        <is>
+          <t>新疆掺混仓，已提供商务报价</t>
+        </is>
+      </c>
+      <c r="E64" s="43" t="inlineStr">
+        <is>
+          <t>C00009344｜冯乐｜新疆｜PP掺混料仓×10+PE掺混料仓×10项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F64" s="43" t="inlineStr">
+        <is>
+          <t>客户是总承包商，我们是分包，已提供商务方案报价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="43" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B65" s="43" t="n">
+        <v>82</v>
+      </c>
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="inlineStr">
+        <is>
+          <t>越南码头，土地审批+贷款，10月底更新</t>
+        </is>
+      </c>
+      <c r="E65" s="43" t="inlineStr">
+        <is>
+          <t>C00009357|韩鸿彪|工业|越南水泥码头+木屑颗粒仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F65" s="43" t="inlineStr">
+        <is>
+          <t>项目土地审批和银行贷款阶段，预计10月底会有进一步更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="43" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B66" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="C66" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="inlineStr">
+        <is>
+          <t>也门扩建V3，业主在对比方案</t>
+        </is>
+      </c>
+      <c r="E66" s="43" t="inlineStr">
+        <is>
+          <t>C00008493|韩鸿彪|工业|也门2x1600T水泥仓扩建项目方案V2</t>
+        </is>
+      </c>
+      <c r="F66" s="43" t="inlineStr">
+        <is>
+          <t>更新方案更新报价V3，业主在对比方案和报价，项目计划是27年Q1上</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="43" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="n">
+        <v>86</v>
+      </c>
+      <c r="C67" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>QNC Halong，配合性等业主反馈</t>
+        </is>
+      </c>
+      <c r="E67" s="43" t="inlineStr">
+        <is>
+          <t>C00008036|韩鸿彪|工业|越南QNC-Halong2x1500T水泥仓方案V2</t>
+        </is>
+      </c>
+      <c r="F67" s="43" t="inlineStr">
+        <is>
+          <t>越南4x6000业主的客户，等待业主的跟进反馈，配合性项目不做重点</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="43" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B68" s="43" t="n">
+        <v>88</v>
+      </c>
+      <c r="C68" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D68" s="43" t="inlineStr">
+        <is>
+          <t>广宁雨棚，报建复杂或将放弃</t>
+        </is>
+      </c>
+      <c r="E68" s="43" t="inlineStr">
+        <is>
+          <t>20260120 韩鸿彪 越南广宁水泥4*6000T筒仓配套装船钢结构雨棚（河边雨棚）</t>
+        </is>
+      </c>
+      <c r="F68" s="43" t="inlineStr">
+        <is>
+          <t>土地报批手续中，杰余报建水槽手续复杂和预算原因，可能会放弃该项目建设</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="43" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="n">
+        <v>89</v>
+      </c>
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D69" s="43" t="inlineStr">
+        <is>
+          <t>QNC包装线，更新报价等决策</t>
+        </is>
+      </c>
+      <c r="E69" s="43" t="inlineStr">
+        <is>
+          <t>C00008036 韩鸿彪 越南 4x6000T筒仓系统配套输送设备方案 V5</t>
+        </is>
+      </c>
+      <c r="F69" s="43" t="inlineStr">
+        <is>
+          <t>更新方案，更新报价，等待决策。业主计划先上一条（6台）包装线，第一个筒仓完工后先运行起来</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="n">
+        <v>91</v>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D70" s="43" t="inlineStr">
+        <is>
+          <t>卢旺达面粉厂，第一版报价阶段</t>
+        </is>
+      </c>
+      <c r="E70" s="43" t="inlineStr">
+        <is>
+          <t>C00009474|韩鸿彪|粮食|卢旺达面粉厂3x2500T小麦仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="F70" s="43" t="inlineStr">
+        <is>
+          <t>面粉厂扩建项目，规模不大，但项目真实，第一版报价阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="43" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B71" s="43" t="n">
+        <v>93</v>
+      </c>
+      <c r="C71" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D71" s="43" t="inlineStr">
+        <is>
+          <t>新加坡储水罐，延标到年底</t>
+        </is>
+      </c>
+      <c r="E71" s="43" t="inlineStr">
+        <is>
+          <t>C00009797  | 马鹏飞 | 工业 | 新加坡波纹钢板储水罐 | 方案V1 |</t>
+        </is>
+      </c>
+      <c r="F71" s="43" t="inlineStr">
+        <is>
+          <t>业主仍在投标，目前项目延标，预计2026年底投标</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="43" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B72" s="43" t="n">
+        <v>99</v>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
+        <is>
+          <t>生力冷却站，待决策层批复</t>
+        </is>
+      </c>
+      <c r="E72" s="43" t="inlineStr">
+        <is>
+          <t>C00001420 | 马鹏飞 | 工业 |生力集团100TPH水泥冷却站项目需画电气单线图及理清范围 | 方案V4 |</t>
+        </is>
+      </c>
+      <c r="F72" s="43" t="inlineStr">
+        <is>
+          <t>已完成单线图提供，生力水泥冷却站项目，已提交所有所需资料，待生力决策层批复，目前尚未有更新情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="43" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B73" s="43" t="n">
+        <v>102</v>
+      </c>
+      <c r="C73" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D73" s="43" t="inlineStr">
+        <is>
+          <t>Intercem法国单仓，投标长期无更新</t>
+        </is>
+      </c>
+      <c r="E73" s="43" t="inlineStr">
+        <is>
+          <t>C00004564 | 马鹏飞 | 德国Intercem公司法国水泥厂项目单仓询价 | 方案 V3 |</t>
+        </is>
+      </c>
+      <c r="F73" s="43" t="inlineStr">
+        <is>
+          <t>已做方案，及报价，目前此业主也是投标，目前并无更新的投标情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="43" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="B74" s="43" t="n">
+        <v>103</v>
+      </c>
+      <c r="C74" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>拉法基墨西哥，刚报价尚无反馈</t>
+        </is>
+      </c>
+      <c r="E74" s="43" t="inlineStr">
+        <is>
+          <t>C00001611| 马鹏飞 | 工业 | 墨西哥拉法基1*500吨水泥仓项目 | 方案V1 |</t>
+        </is>
+      </c>
+      <c r="F74" s="43" t="inlineStr">
+        <is>
+          <t>已做方案，及报价，刚发出报价，尚无业主对价格的反馈意见。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="43" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="n">
+        <v>144</v>
+      </c>
+      <c r="C75" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>苏丹农行，还在做预算报价</t>
+        </is>
+      </c>
+      <c r="E75" s="43" t="inlineStr">
+        <is>
+          <t>C00006335 | 王伟乐 | 粮食|  苏丹农业银行粮储项目 | 方案 V1|</t>
+        </is>
+      </c>
+      <c r="F75" s="43" t="inlineStr">
+        <is>
+          <t>还在进行预算的报价，土建的报价需要预估</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="43" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B76" s="43" t="n">
+        <v>145</v>
+      </c>
+      <c r="C76" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
+        <is>
+          <t>埃及螺旋仓，已报价未反馈</t>
+        </is>
+      </c>
+      <c r="E76" s="43" t="inlineStr">
+        <is>
+          <t>C00006274| 王伟乐|工业|2026.6.15 |埃及 4*3000t 螺旋咬口仓项目| 方案V1</t>
+        </is>
+      </c>
+      <c r="F76" s="43" t="inlineStr">
+        <is>
+          <t>已报价，客户未反馈报价的情况，后期可以继续跟进</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="43" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B77" s="43" t="n">
+        <v>146</v>
+      </c>
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>裕廊港，最新价澄清中</t>
+        </is>
+      </c>
+      <c r="E77" s="43" t="inlineStr">
+        <is>
+          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="F77" s="43" t="inlineStr">
+        <is>
+          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="43" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="B78" s="43" t="n">
+        <v>151</v>
+      </c>
+      <c r="C78" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>CIMAF，已报价库龄偏长</t>
+        </is>
+      </c>
+      <c r="E78" s="43" t="inlineStr">
+        <is>
+          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
+        </is>
+      </c>
+      <c r="F78" s="43" t="inlineStr">
+        <is>
+          <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="43" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B79" s="43" t="n">
+        <v>153</v>
+      </c>
+      <c r="C79" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>仅写已报价，超90天无下一步</t>
+        </is>
+      </c>
+      <c r="E79" s="43" t="inlineStr">
+        <is>
+          <t>C00009303｜尹韬越｜工业｜乌兹别克斯坦尼什巴什一期储煤场末煤仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F79" s="43" t="inlineStr">
+        <is>
+          <t>已报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="43" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B80" s="43" t="n">
+        <v>154</v>
+      </c>
+      <c r="C80" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D80" s="43" t="inlineStr">
+        <is>
+          <t>仅写已报方案，无互动</t>
+        </is>
+      </c>
+      <c r="E80" s="43" t="inlineStr">
+        <is>
+          <t>C00009297｜尹韬越｜粮食｜格鲁吉亚第比利斯3×1000吨玉米仓｜方案V1</t>
+        </is>
+      </c>
+      <c r="F80" s="43" t="inlineStr">
+        <is>
+          <t>已报方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="43" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B81" s="43" t="n">
+        <v>156</v>
+      </c>
+      <c r="C81" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr">
+        <is>
+          <t>哈萨克征地，长周期有节点</t>
+        </is>
+      </c>
+      <c r="E81" s="43" t="inlineStr">
+        <is>
+          <t>C00008577｜尹韬越｜粮食｜哈萨克斯坦4×3500吨粮食项目｜方案V2</t>
+        </is>
+      </c>
+      <c r="F81" s="43" t="inlineStr">
+        <is>
+          <t>已报方案，目前对方在征地</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="B82" s="43" t="n">
+        <v>158</v>
+      </c>
+      <c r="C82" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="inlineStr">
+        <is>
+          <t>与156同一征地，重复开单</t>
+        </is>
+      </c>
+      <c r="E82" s="43" t="inlineStr">
+        <is>
+          <t>C00008577 尹韬越哈萨克斯坦4×3500吨粮食项目 方案1</t>
+        </is>
+      </c>
+      <c r="F82" s="43" t="inlineStr">
+        <is>
+          <t>已报方案，目前对方在征地</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B83" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="C83" s="47" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="inlineStr">
+        <is>
+          <t>乌干达，非业主了解预算</t>
+        </is>
+      </c>
+      <c r="E83" s="43" t="inlineStr">
+        <is>
+          <t>C00009593｜王伟超｜粮食｜乌干达生咖啡豆筒仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F83" s="43" t="inlineStr">
+        <is>
+          <t>已经和客户开过视频会，发了方案和报价，但不是最终业主，而且业主表示目前是在准备阶段，这次询价可能是为了了解大概需要多少预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="43" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B84" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="C84" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="inlineStr">
+        <is>
+          <t>哥斯达黎加，多次改图等回复</t>
+        </is>
+      </c>
+      <c r="E84" s="43" t="inlineStr">
+        <is>
+          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
+        </is>
+      </c>
+      <c r="F84" s="43" t="inlineStr">
+        <is>
+          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="B85" s="43" t="n">
+        <v>143</v>
+      </c>
+      <c r="C85" s="45" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
+        <is>
+          <t>达沃料场，价格超预期</t>
+        </is>
+      </c>
+      <c r="E85" s="43" t="inlineStr">
+        <is>
+          <t>C00006712｜王伟超｜工业｜菲律宾达沃料场项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F85" s="43" t="inlineStr">
+        <is>
+          <t>与陈总沟通后，最终决定让我继续跟进，已经发送过方案与报价，但是根据料场的跨度过大，结构计算重量偏大，所以价格超过对方的预期，中间商正在与业主了解更多信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="43" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B86" s="43" t="n">
+        <v>168</v>
+      </c>
+      <c r="C86" s="44" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="inlineStr">
+        <is>
+          <t>斯里兰卡小麦仓，报价已上呈总裁</t>
+        </is>
+      </c>
+      <c r="E86" s="43" t="inlineStr">
+        <is>
+          <t>C00009858 | 张硕 | 粮食 | 斯里兰卡汉班托塔Golden Harvest Mill3x1500MT小麦仓扩建项目</t>
+        </is>
+      </c>
+      <c r="F86" s="43" t="inlineStr">
+        <is>
+          <t>业主收到3座仓的正式报价后没有直接给出评论意见，仅回复说以将报价上呈给公司总裁，判断其从多方供应商处比较报价后再做决定，跟进策略对业主按保持每周频次跟进，不表现急切情绪；另从近期开发的当地代理处侧面了解项目进展</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="43" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B87" s="43" t="n">
+        <v>169</v>
+      </c>
+      <c r="C87" s="46" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>印尼料斗，确认清单时无视邮件</t>
+        </is>
+      </c>
+      <c r="E87" s="43" t="inlineStr">
+        <is>
+          <t>C00009866 | 张硕｜工业｜印尼工程公司PT REXLINE生物质30m³定量料斗项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="F87" s="43" t="inlineStr">
+        <is>
+          <t>客户为印尼本地工程公司，在收到我方的方案和设备清单（不含报价），与其沟通对方案图纸和设备清单参数确认时，对方多次无视邮件和Whatsapp信息，初步判定为客户可能已收到合适的报价</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -33,8 +33,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2-质量对比'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2b-图数据'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3-重点项目'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4-前期调研清单'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5-该结未结与重复'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4-前期调研清单'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5-该结未结与重复'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'6-有效在手'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'7-全量明细'!$A$1:$Q$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'8-逐人要点'!$A$1:$I$1</definedName>
@@ -98,7 +98,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -187,11 +187,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
@@ -227,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -308,11 +303,11 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -327,16 +322,13 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -360,7 +352,7 @@
     <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1097,7 +1089,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17；填报版本 0830（崔阳已补进展）</t>
+          <t>2026-08-17；填报版本 0830（崔阳已补进展；2条空白状态已补：韩鸿彪暂停、张硕进行中）</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1101,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>国际业务部方案任务 165 条（已剔除国内业务部郭朝伟 4 条）；崔阳 38 条已补进展</t>
+          <t>国际业务部方案任务 165 条（已剔除国内业务部郭朝伟 4 条）；崔阳 38 条已补进展；状态已全部标注</t>
         </is>
       </c>
     </row>
@@ -1297,10 +1289,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.5212121212121212</v>
+        <v>0.5272727272727272</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1323,10 +1315,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.09696969696969697</v>
+        <v>0.103030303030303</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1349,10 +1341,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.01212121212121212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1"/>
@@ -1387,10 +1379,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4727272727272727</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1413,10 +1405,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>0.103030303030303</v>
+        <v>0.1090909090909091</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1439,10 +1431,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1272727272727273</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1452,10 +1444,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>0.006060606060606061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1486,7 +1478,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>17 条 / 16 个客户，占全部 10.3%</t>
+          <t>18 条 / 17 个客户，占全部 10.9%</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1490,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>22 条，直接虚增进行中盘子</t>
+          <t>21 条，直接虚增进行中盘子</t>
         </is>
       </c>
     </row>
@@ -1567,47 +1559,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>一句话</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>提报</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>闭环</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="28" t="inlineStr">
         <is>
           <t>前期客户</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>重点</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="28" t="inlineStr">
         <is>
           <t>有效在手</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="28" t="inlineStr">
         <is>
           <t>主要问题</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="28" t="inlineStr">
         <is>
           <t>建议动作</t>
         </is>
@@ -1843,14 +1835,14 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>长周期项目跟得住，雨棚重复未结</t>
+          <t>长周期项目跟得住，雨棚重复已暂停</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1863,12 +1855,12 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>QNC包装线/也门扩建/越南码头贷款节点清楚；3条已暂停；雨棚与86重复状态空；配合性Halong不做重点但仍挂</t>
+          <t>QNC包装线/也门扩建/越南码头贷款节点清楚；4条已暂停（含与86重复的雨棚）；配合性Halong不做重点但仍挂</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>重复雨棚关掉；配合性项目降级或暂停</t>
+          <t>配合性项目降级或暂停；河边雨棚报建复杂仍进行中，该关则关</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1983,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>旧单已关，新单一条跟得细、一条该结</t>
+          <t>旧单已关，新单一条跟得细、一条该结、哈利法港按前期</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
@@ -2001,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -2011,12 +2003,12 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>5条；2条旧失联已结；哈利法港陈总发起未跟；斯里兰卡小麦仓策略清楚；印尼料斗已不理邮件</t>
+          <t>5条；2条旧失联已结；哈利法港已标进行中（大EPC需投标并设当地分公司，按前期，不算有效在手）；斯里兰卡小麦仓策略清楚；印尼料斗已不理邮件</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>哈利法港交还陈总或改状态；印尼料斗结项</t>
+          <t>哈利法港按前期跟，设退出条件；印尼料斗结项</t>
         </is>
       </c>
     </row>
@@ -2194,13 +2186,13 @@
       <c r="I2" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="J2" s="29" t="n">
         <v>0.1842105263157895</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="L2" s="29" t="n">
         <v>0.4210526315789473</v>
       </c>
       <c r="M2" s="7" t="n">
@@ -2244,13 +2236,13 @@
       <c r="I3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J3" s="29" t="n">
         <v>0.05555555555555555</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" s="29" t="n">
         <v>0.1666666666666667</v>
       </c>
       <c r="M3" s="7" t="n">
@@ -2294,13 +2286,13 @@
       <c r="I4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="29" t="n">
         <v>0.1764705882352941</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="29" t="n">
         <v>0.2941176470588235</v>
       </c>
       <c r="M4" s="7" t="n">
@@ -2344,13 +2336,13 @@
       <c r="I5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="29" t="n">
         <v>0.2352941176470588</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" s="29" t="n">
         <v>0.4117647058823529</v>
       </c>
       <c r="M5" s="7" t="n">
@@ -2394,13 +2386,13 @@
       <c r="I6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="29" t="n">
         <v>0.25</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="L6" s="29" t="n">
         <v>0.4375</v>
       </c>
       <c r="M6" s="7" t="n">
@@ -2444,13 +2436,13 @@
       <c r="I7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="29" t="n">
         <v>0.1538461538461539</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="29" t="n">
         <v>0.3076923076923077</v>
       </c>
       <c r="M7" s="7" t="n">
@@ -2494,13 +2486,13 @@
       <c r="I8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="29" t="n">
         <v>0.3636363636363636</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="29" t="n">
         <v>0.5454545454545454</v>
       </c>
       <c r="M8" s="7" t="n">
@@ -2544,13 +2536,13 @@
       <c r="I9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="29" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="29" t="n">
         <v>0.2727272727272727</v>
       </c>
       <c r="M9" s="7" t="n">
@@ -2594,13 +2586,13 @@
       <c r="I10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="29" t="n">
         <v>0.125</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="29" t="n">
         <v>0.375</v>
       </c>
       <c r="M10" s="7" t="n">
@@ -2644,13 +2636,13 @@
       <c r="I11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="29" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="29" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="M11" s="7" t="n">
@@ -2690,13 +2682,13 @@
       <c r="I12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="29" t="n">
         <v>0.6</v>
       </c>
       <c r="M12" s="7" t="n">
@@ -2740,13 +2732,13 @@
       <c r="I13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="29" t="n">
         <v>0.6</v>
       </c>
       <c r="M13" s="7" t="n">
@@ -4710,7 +4702,7 @@
         <v>5</v>
       </c>
       <c r="R2" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -4766,7 +4758,7 @@
         <v>3</v>
       </c>
       <c r="R3" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -5024,10 +5016,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="J8" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="L8" s="31" t="n">
         <v>0</v>
@@ -5046,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="R8" s="31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -5257,13 +5249,13 @@
         <v>0.2</v>
       </c>
       <c r="I12" s="32" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J12" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="32" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L12" s="31" t="n">
         <v>0</v>
@@ -5445,7 +5437,7 @@
       <c r="D2" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="29" t="n">
         <v>0.5</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -5469,7 +5461,7 @@
       <c r="D3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="29" t="n">
         <v>0.4444444444444444</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -5493,7 +5485,7 @@
       <c r="D4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="29" t="n">
         <v>0.6363636363636364</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -5517,7 +5509,7 @@
       <c r="D5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.375</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -5541,7 +5533,7 @@
       <c r="D6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="29" t="n">
         <v>0.3846153846153846</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -5565,7 +5557,7 @@
       <c r="D7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="29" t="n">
         <v>0.5</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -5589,7 +5581,7 @@
       <c r="D8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="29" t="n">
         <v>0.2352941176470588</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -5613,7 +5605,7 @@
       <c r="D9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="29" t="n">
         <v>0.1764705882352941</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -5637,7 +5629,7 @@
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="29" t="n">
         <v>0.4</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -5661,7 +5653,7 @@
       <c r="D11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -5685,7 +5677,7 @@
       <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="29" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -5709,7 +5701,7 @@
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="29" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -5748,22 +5740,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="B1" s="36" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C1" s="36" t="inlineStr">
+      <c r="C1" s="35" t="inlineStr">
         <is>
           <t>归并原因</t>
         </is>
       </c>
-      <c r="D1" s="36" t="inlineStr">
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>一句话</t>
         </is>
@@ -6997,57 +6989,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B1" s="37" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="C1" s="37" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>编码</t>
         </is>
       </c>
-      <c r="D1" s="37" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="E1" s="37" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>项目数</t>
         </is>
       </c>
-      <c r="F1" s="37" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>已丢单</t>
         </is>
       </c>
-      <c r="G1" s="37" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>暂停</t>
         </is>
       </c>
-      <c r="H1" s="37" t="inlineStr">
+      <c r="H1" s="36" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="I1" s="37" t="inlineStr">
+      <c r="I1" s="36" t="inlineStr">
         <is>
           <t>有效在手</t>
         </is>
       </c>
-      <c r="J1" s="37" t="inlineStr">
+      <c r="J1" s="36" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="K1" s="37" t="inlineStr">
+      <c r="K1" s="36" t="inlineStr">
         <is>
           <t>一句话</t>
         </is>
@@ -7397,22 +7389,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="B1" s="38" t="inlineStr">
+      <c r="B1" s="37" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="C1" s="38" t="inlineStr">
+      <c r="C1" s="37" t="inlineStr">
         <is>
           <t>项目数</t>
         </is>
       </c>
-      <c r="D1" s="38" t="inlineStr">
+      <c r="D1" s="37" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
@@ -8061,320 +8053,320 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="B1" s="39" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" s="38" t="inlineStr">
         <is>
           <t>前期调研</t>
         </is>
       </c>
-      <c r="D1" s="39" t="inlineStr">
+      <c r="D1" s="38" t="inlineStr">
         <is>
           <t>报价后观望</t>
         </is>
       </c>
-      <c r="E1" s="39" t="inlineStr">
+      <c r="E1" s="38" t="inlineStr">
         <is>
           <t>报价后决策</t>
         </is>
       </c>
-      <c r="F1" s="39" t="inlineStr">
+      <c r="F1" s="38" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n">
+      <c r="B2" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="C2" s="40" t="n">
+      <c r="C2" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="40" t="n">
+      <c r="D2" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="40" t="n">
+      <c r="E2" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="40" t="n">
+      <c r="F2" s="39" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="40" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B3" s="40" t="n">
+      <c r="B3" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="40" t="n">
+      <c r="C3" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="D3" s="40" t="n">
+      <c r="D3" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="40" t="n">
+      <c r="E3" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="40" t="n">
+      <c r="F3" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B4" s="40" t="n">
+      <c r="B4" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="40" t="n">
+      <c r="C4" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="39" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
+      <c r="B5" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="40" t="n">
+      <c r="C5" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="39" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>马鹏飞</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>王伟乐</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>尹韬越</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="C11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="39" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>王伟超</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="40" t="n">
+      <c r="C12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>张硕</t>
         </is>
       </c>
-      <c r="B13" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="40" t="n">
+      <c r="B13" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n">
-        <v>86</v>
-      </c>
-      <c r="C14" s="41" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" s="41" t="n">
+      <c r="B14" s="40" t="n">
+        <v>87</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="E14" s="41" t="n">
+      <c r="E14" s="40" t="n">
         <v>26</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F14" s="40" t="n">
         <v>23</v>
       </c>
     </row>
@@ -9007,7 +8999,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -9016,13 +9008,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>6</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>0</v>
@@ -9046,7 +9038,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>0</v>
@@ -9061,7 +9053,7 @@
         <v>0.3636363636363636</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0.6666666666666666</v>
@@ -9315,16 +9307,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>0</v>
@@ -9345,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="7" t="n">
         <v>2</v>
@@ -9360,7 +9352,7 @@
         <v>0.4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="X12" s="7" t="n"/>
     </row>
@@ -9451,7 +9443,7 @@
         <v>134</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>1</v>
@@ -9460,19 +9452,19 @@
         <v>60</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="11" t="n">
         <v>17</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>16</v>
       </c>
       <c r="L14" s="11" t="n">
         <v>15</v>
@@ -9490,10 +9482,10 @@
         <v>16</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="11" t="n">
         <v>23</v>
@@ -9505,10 +9497,10 @@
         <v>0.1757575757575758</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="W14" s="12" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3218390804597701</v>
       </c>
       <c r="X14" s="11" t="n"/>
     </row>
@@ -9524,7 +9516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="4" max="4"/>
@@ -9533,782 +9525,782 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C1" s="42" t="inlineStr">
+      <c r="C1" s="41" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="D1" s="42" t="inlineStr">
+      <c r="D1" s="41" t="inlineStr">
         <is>
           <t>阶段说明</t>
         </is>
       </c>
-      <c r="E1" s="42" t="inlineStr">
+      <c r="E1" s="41" t="inlineStr">
         <is>
           <t>任务标题</t>
         </is>
       </c>
-      <c r="F1" s="42" t="inlineStr">
+      <c r="F1" s="41" t="inlineStr">
         <is>
           <t>当前进展</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B2" s="43" t="n">
+      <c r="B2" s="42" t="n">
         <v>34</v>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D2" s="43" t="inlineStr">
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>勘察后出最终方案</t>
         </is>
       </c>
-      <c r="E2" s="43" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>C00005424|崔阳|工业|Sibur塑料颗粒的气力输送项目|方案V1</t>
         </is>
       </c>
-      <c r="F2" s="43" t="inlineStr">
+      <c r="F2" s="42" t="inlineStr">
         <is>
           <t>项目进行实地勘察后，技术部正在出最终方案</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B3" s="43" t="n">
+      <c r="B3" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="C3" s="45" t="inlineStr">
+      <c r="C3" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D3" s="43" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>报价已交最终业主，等回复</t>
         </is>
       </c>
-      <c r="E3" s="43" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>C00006570|崔阳|工业|Powerz螺旋输送机采购|方案V1</t>
         </is>
       </c>
-      <c r="F3" s="43" t="inlineStr">
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>项目报价已提交最终业主</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B4" s="43" t="n">
+      <c r="B4" s="42" t="n">
         <v>36</v>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>方案未出，仍在找厂家</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>C00006458 崔阳|工业|达涅利 辊道和步进梁项目 |方案V1</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>正在寻找相应生产厂家，方案未出</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="42" t="n">
         <v>37</v>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>已报价，业主让等待回复</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>C00009596   崔阳|工业|乌克兰AIK-EKO 铜矿石筒仓项目 |方案V1</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>报价已报出，业主让等待回复</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="42" t="n">
         <v>38</v>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>资质已交业主审查</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>C00009055 崔阳|工业|CC7 Europe 化工回收项目 |方案V1</t>
         </is>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>已将我方资质提交最终业主，业主进行资质审查</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="42" t="n">
         <v>39</v>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>cotes矿石仓技术探讨，未报价</t>
         </is>
       </c>
-      <c r="E7" s="43" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>C00006514|崔阳|工业|cotes哈萨克斯坦4个矿石仓项目|方案V1</t>
         </is>
       </c>
-      <c r="F7" s="43" t="inlineStr">
+      <c r="F7" s="42" t="inlineStr">
         <is>
           <t>处于技术探讨阶段 还未报价</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B8" s="43" t="n">
+      <c r="B8" s="42" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>报价给中间人，等业主审核</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>C00009720|崔阳|工业|乌兹别克斯坦撒马尔罕3000吨水泥厂项目|方案V1</t>
         </is>
       </c>
-      <c r="F8" s="43" t="inlineStr">
+      <c r="F8" s="42" t="inlineStr">
         <is>
           <t>报价提供给中间人，中间人让等待业主审核</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="42" t="n">
         <v>41</v>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>已报价，最终业主评审中</t>
         </is>
       </c>
-      <c r="E9" s="43" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>C00007843|崔阳|工业|Эннова散装机|方案V1</t>
         </is>
       </c>
-      <c r="F9" s="43" t="inlineStr">
+      <c r="F9" s="42" t="inlineStr">
         <is>
           <t>已提供报价 最终业主在评审</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B10" s="43" t="n">
+      <c r="B10" s="42" t="n">
         <v>42</v>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>客户提议9月现场考察</t>
         </is>
       </c>
-      <c r="E10" s="43" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>C00009506  |崔阳|粮食| RUSAGRO农作物种子加工厂项目|方案V1</t>
         </is>
       </c>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="F10" s="42" t="inlineStr">
         <is>
           <t>客户提议九月份进行现场考察</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="42" t="n">
         <v>44</v>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>与38同一CC7项目</t>
         </is>
       </c>
-      <c r="E11" s="43" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>C00009055 崔阳|工业|CC7 Europe 石灰给料包项目 |方案V1</t>
         </is>
       </c>
-      <c r="F11" s="43" t="inlineStr">
+      <c r="F11" s="42" t="inlineStr">
         <is>
           <t>和38是同一个项目</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B12" s="43" t="n">
+      <c r="B12" s="42" t="n">
         <v>46</v>
       </c>
-      <c r="C12" s="45" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>已报价cotec，无节点</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>C00006514|崔阳|工业|cotes烧碱和硫酸钠化工仓|方案V1</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F12" s="42" t="inlineStr">
         <is>
           <t>已报价给cotec 正在继续跟进中</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="42" t="n">
         <v>47</v>
       </c>
-      <c r="C13" s="45" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>初步报价，业主评估中</t>
         </is>
       </c>
-      <c r="E13" s="43" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>C00009347 |崔阳|粮食| Ebad Pir Moradian Global Skills 40000吨储粮项目|方案V1</t>
         </is>
       </c>
-      <c r="F13" s="43" t="inlineStr">
+      <c r="F13" s="42" t="inlineStr">
         <is>
           <t>初步报价已提出，业主需要进行评估，和提交技术部门进行探讨</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B14" s="43" t="n">
+      <c r="B14" s="42" t="n">
         <v>51</v>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>方案未出3个月，希望不大</t>
         </is>
       </c>
-      <c r="E14" s="43" t="inlineStr">
+      <c r="E14" s="42" t="inlineStr">
         <is>
           <t>C00007843|崔阳|工业|Эннова新库兹涅兹克电厂烟气净化与脱硫系统项目|方案V1</t>
         </is>
       </c>
-      <c r="F14" s="43" t="inlineStr">
+      <c r="F14" s="42" t="inlineStr">
         <is>
           <t>方案未出，时间跨度已经三个月，希望以不大，</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B15" s="43" t="n">
+      <c r="B15" s="42" t="n">
         <v>53</v>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>cotes粉煤灰技术探讨，未报价</t>
         </is>
       </c>
-      <c r="E15" s="43" t="inlineStr">
+      <c r="E15" s="42" t="inlineStr">
         <is>
           <t>C00006514|崔阳|工业|cotes电厂粉煤灰|方案V2</t>
         </is>
       </c>
-      <c r="F15" s="43" t="inlineStr">
+      <c r="F15" s="42" t="inlineStr">
         <is>
           <t>处于技术探讨阶段 还未报价</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B16" s="43" t="n">
+      <c r="B16" s="42" t="n">
         <v>58</v>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>重点只写「进行中 重点任务」</t>
         </is>
       </c>
-      <c r="E16" s="43" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>C00009094|崔阳|粮食|75万吨小麦深加工项目|方案V1|重点项目</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="F16" s="42" t="inlineStr">
         <is>
           <t>进行中 重点任务</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B17" s="43" t="n">
+      <c r="B17" s="42" t="n">
         <v>62</v>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>找不到设备，该停未停</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>C00006570 Powerz 崔阳 工业 底渣输送机 方案V1</t>
         </is>
       </c>
-      <c r="F17" s="43" t="inlineStr">
+      <c r="F17" s="42" t="inlineStr">
         <is>
           <t>方案未出，国内找不到相应适合设备 暂停中</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B18" s="43" t="n">
+      <c r="B18" s="42" t="n">
         <v>65</v>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>方案未出5个月，希望不大</t>
         </is>
       </c>
-      <c r="E18" s="43" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>C00007843 | 崔阳 | 工业 | 哈萨克热列兹肯特热电站10号机组烟气净化（脱硫，除尘）项目 | 方案V1</t>
         </is>
       </c>
-      <c r="F18" s="43" t="inlineStr">
+      <c r="F18" s="42" t="inlineStr">
         <is>
           <t>方案未出，时间跨度已经五个月，希望以不大，</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B19" s="43" t="n">
+      <c r="B19" s="42" t="n">
         <v>69</v>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>方案未出6个月，希望不大</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>C00007843 | 崔阳 | 工业 | 外贝加尔发电厂项目 | 方案</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F19" s="42" t="inlineStr">
         <is>
           <t>方案未出，时间跨度已经六个月，希望以不大，</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B20" s="43" t="n">
+      <c r="B20" s="42" t="n">
         <v>70</v>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>立项阶段，自称暂停仍挂着</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>C00009506|崔阳|粮食| RUSAGRO大豆深度加工综合生产线|方案V1</t>
         </is>
       </c>
-      <c r="F20" s="43" t="inlineStr">
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>1.项目属于立项阶段，我方技术分析后，认为我们参与部分不是很多，决定暂时暂停任务，观望后再说</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>港口规划，已报预算</t>
         </is>
       </c>
-      <c r="E21" s="43" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>C00003352｜陈辉｜工业｜埃及4万吨料场项目｜方案V1（预算）</t>
         </is>
       </c>
-      <c r="F21" s="43" t="inlineStr">
+      <c r="F21" s="42" t="inlineStr">
         <is>
           <t>TCI预期拿到了埃及一港口的运营权，有计划建散料库，已报预算，还在规划阶段。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B22" s="43" t="n">
+      <c r="B22" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="44" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>大宇多次报价，双方比仓型</t>
         </is>
       </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="F22" s="43" t="inlineStr">
+      <c r="F22" s="42" t="inlineStr">
         <is>
           <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B23" s="43" t="n">
+      <c r="B23" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>塞拉利昂已拜访，缺资金</t>
         </is>
       </c>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="E23" s="42" t="inlineStr">
         <is>
           <t>C00002715｜陈辉｜工业｜塞拉利昂2个3万吨clinker项目｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="F23" s="43" t="inlineStr">
+      <c r="F23" s="42" t="inlineStr">
         <is>
           <t>已去拜访客户，客户想法很多，缺资金。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B24" s="43" t="n">
+      <c r="B24" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C24" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>突尼斯粮仓，还在找钱</t>
         </is>
       </c>
-      <c r="E24" s="43" t="inlineStr">
+      <c r="E24" s="42" t="inlineStr">
         <is>
           <t>C00009463｜陈辉｜粮食｜突尼斯粮仓6x5,000t+10x8,000t｜方案V1</t>
         </is>
       </c>
-      <c r="F24" s="43" t="inlineStr">
+      <c r="F24" s="42" t="inlineStr">
         <is>
           <t>突尼斯一家工程公司想建这几个粮仓，没有资金，要靠国外银行给贷款，介绍了TCI给他们。项目还在找钱的阶段。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B25" s="43" t="n">
+      <c r="B25" s="42" t="n">
         <v>9</v>
       </c>
-      <c r="C25" s="44" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>大宇卸料，等DY分包结果</t>
         </is>
       </c>
-      <c r="E25" s="43" t="inlineStr">
+      <c r="E25" s="42" t="inlineStr">
         <is>
           <t>C00009287｜陈辉｜工业｜大宇8套磷矿粉平底仓卸料｜方案V1</t>
         </is>
       </c>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="F25" s="42" t="inlineStr">
         <is>
           <t>大宇在土库曼化肥厂项目，筒仓的卸料分包给了韩国的一家公司DY，我们给DY报价，仅报一次，技术澄清比较多，DY如果中标大概率优选选我们。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B26" s="43" t="n">
+      <c r="B26" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C26" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>火车卸料，项目计划评审</t>
         </is>
       </c>
-      <c r="E26" s="43" t="inlineStr">
+      <c r="E26" s="42" t="inlineStr">
         <is>
           <t>C00009244｜陈辉｜工业｜火车卸料项目｜方案V1</t>
         </is>
       </c>
-      <c r="F26" s="43" t="inlineStr">
+      <c r="F26" s="42" t="inlineStr">
         <is>
           <t>客户自有仓，让我们报火车卸料后进仓和出仓相关设备。
 客户的项目仍在计划评审阶段。</t>
@@ -10316,180 +10308,180 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B27" s="43" t="n">
+      <c r="B27" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="C27" s="44" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Lanwa老客户，利润被压着比</t>
         </is>
       </c>
-      <c r="E27" s="43" t="inlineStr">
+      <c r="E27" s="42" t="inlineStr">
         <is>
           <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="F27" s="43" t="inlineStr">
+      <c r="F27" s="42" t="inlineStr">
         <is>
           <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B28" s="43" t="n">
+      <c r="B28" s="42" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D28" s="42" t="inlineStr">
         <is>
           <t>配合埃及总包投标</t>
         </is>
       </c>
-      <c r="E28" s="43" t="inlineStr">
+      <c r="E28" s="42" t="inlineStr">
         <is>
           <t>C00006497｜陈辉｜粮食｜埃及面粉项目｜方案V1（仅仓和钢构）</t>
         </is>
       </c>
-      <c r="F28" s="43" t="inlineStr">
+      <c r="F28" s="42" t="inlineStr">
         <is>
           <t>埃及总包的一个投标项目，我们报价配合其投标。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B29" s="43" t="n">
+      <c r="B29" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>埃及建筑公司投铝厂</t>
         </is>
       </c>
-      <c r="E29" s="43" t="inlineStr">
+      <c r="E29" s="42" t="inlineStr">
         <is>
           <t>C00009849｜陈辉｜工业｜埃及3万吨混凝土仓（存氧化铝）项目｜方案V1</t>
         </is>
       </c>
-      <c r="F29" s="43" t="inlineStr">
+      <c r="F29" s="42" t="inlineStr">
         <is>
           <t>埃及的建筑公司作为投标人之一，向铝厂投标。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B30" s="43" t="n">
+      <c r="B30" s="42" t="n">
         <v>15</v>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C30" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>巴西仓，规划阶段了解价格</t>
         </is>
       </c>
-      <c r="E30" s="43" t="inlineStr">
+      <c r="E30" s="42" t="inlineStr">
         <is>
           <t>C00009244｜陈辉｜工业｜巴西钢板仓和卸到火车项目｜方案V1</t>
         </is>
       </c>
-      <c r="F30" s="43" t="inlineStr">
+      <c r="F30" s="42" t="inlineStr">
         <is>
           <t>规划阶段，客户未来可能有两万吨粘土仓的需求，目前只是了解仓型和价格。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B31" s="43" t="n">
+      <c r="B31" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C31" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>澳洲装配仓，预算评估仓型</t>
         </is>
       </c>
-      <c r="E31" s="43" t="inlineStr">
+      <c r="E31" s="42" t="inlineStr">
         <is>
           <t>C00009852｜陈辉｜工业｜澳洲8x6000t水泥装配仓｜方案V1（钢构量）</t>
         </is>
       </c>
-      <c r="F31" s="43" t="inlineStr">
+      <c r="F31" s="42" t="inlineStr">
         <is>
           <t>预算。客户仍在评估是建造混凝土仓or钢板仓。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="B32" s="43" t="n">
+      <c r="B32" s="42" t="n">
         <v>17</v>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C32" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="D32" s="42" t="inlineStr">
         <is>
           <t>莱歇镀锌仓，业主询价比是否分包</t>
         </is>
       </c>
-      <c r="E32" s="43" t="inlineStr">
+      <c r="E32" s="42" t="inlineStr">
         <is>
           <t>C00003392｜陈辉｜工业｜莱歇6个热镀锌仓项目｜方案V1（钢构量）</t>
         </is>
       </c>
-      <c r="F32" s="43" t="inlineStr">
+      <c r="F32" s="42" t="inlineStr">
         <is>
           <t>莱歇在台北正在做的磨粉项目，这几个仓是原本是业主范围，现在想拿出来询价，来决定是分包给莱歇去做还是业主自己做。
 莱歇要求足够低价。</t>
@@ -10497,1650 +10489,1680 @@
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n">
+      <c r="B33" s="42" t="n">
         <v>123</v>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C33" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>路易达孚只要预算</t>
         </is>
       </c>
-      <c r="E33" s="43" t="inlineStr">
+      <c r="E33" s="42" t="inlineStr">
         <is>
           <t>C00009733｜司斌｜粮食｜印度路易达孚4x500咖啡仓 |方案V1</t>
         </is>
       </c>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="F33" s="42" t="inlineStr">
         <is>
           <t>路易达孚印度公司咖啡公司，项目处于调研阶段，只要了预算，待管理层决定，不一定会上</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B34" s="43" t="n">
+      <c r="B34" s="42" t="n">
         <v>124</v>
       </c>
-      <c r="C34" s="44" t="inlineStr">
+      <c r="C34" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>斯里兰卡稻谷，已到决策期</t>
         </is>
       </c>
-      <c r="E34" s="43" t="inlineStr">
+      <c r="E34" s="42" t="inlineStr">
         <is>
           <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
         </is>
       </c>
-      <c r="F34" s="43" t="inlineStr">
+      <c r="F34" s="42" t="inlineStr">
         <is>
           <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B35" s="43" t="n">
+      <c r="B35" s="42" t="n">
         <v>125</v>
       </c>
-      <c r="C35" s="46" t="inlineStr">
+      <c r="C35" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>咖啡仓三次报价无反馈</t>
         </is>
       </c>
-      <c r="E35" s="43" t="inlineStr">
+      <c r="E35" s="42" t="inlineStr">
         <is>
           <t>C00008345｜司斌｜粮食｜咖啡仓方仓 |方案V1</t>
         </is>
       </c>
-      <c r="F35" s="43" t="inlineStr">
+      <c r="F35" s="42" t="inlineStr">
         <is>
           <t>客户公司主业咖啡生产线，在全球都有项目，国内与星巴克，瑞幸都有合作。项目处于前期价格咨询。已就此公司进行了三次报价，但均无任何反馈，客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B36" s="43" t="n">
+      <c r="B36" s="42" t="n">
         <v>126</v>
       </c>
-      <c r="C36" s="46" t="inlineStr">
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="D36" s="42" t="inlineStr">
         <is>
           <t>越南灰仓，技术无法澄清</t>
         </is>
       </c>
-      <c r="E36" s="43" t="inlineStr">
+      <c r="E36" s="42" t="inlineStr">
         <is>
           <t>C00009546｜司斌｜工业｜越南6*800+2*450灰仓｜方案V1</t>
         </is>
       </c>
-      <c r="F36" s="43" t="inlineStr">
+      <c r="F36" s="42" t="inlineStr">
         <is>
           <t>对接公司是工程公司，但是主业与我们行业不相关，此项目为投标项目，对接公司与最终业主有过合作，但技术问题无法澄清，虽然发送了报价，但是在较少的技术澄清下，胜率不高</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B37" s="43" t="n">
+      <c r="B37" s="42" t="n">
         <v>127</v>
       </c>
-      <c r="C37" s="46" t="inlineStr">
+      <c r="C37" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr">
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>咖啡缓冲斗，重复开单</t>
         </is>
       </c>
-      <c r="E37" s="43" t="inlineStr">
+      <c r="E37" s="42" t="inlineStr">
         <is>
           <t>C00008345｜司斌｜粮食｜咖啡缓冲斗｜方案V1</t>
         </is>
       </c>
-      <c r="F37" s="43" t="inlineStr">
+      <c r="F37" s="42" t="inlineStr">
         <is>
           <t>与123是同一个客户</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B38" s="43" t="n">
+      <c r="B38" s="42" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="46" t="inlineStr">
+      <c r="C38" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>越南咖啡改造，方案后无回复</t>
         </is>
       </c>
-      <c r="E38" s="43" t="inlineStr">
+      <c r="E38" s="42" t="inlineStr">
         <is>
           <t>C00001287｜司斌｜粮食｜越南咖啡仓改造项目｜方案V1</t>
         </is>
       </c>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="F38" s="42" t="inlineStr">
         <is>
           <t>已合作客户，上次拜访客户想要进行一定的改造，但是发送方案后一直没有任何回复，初步判断改造并非需要解决的大问题，可上可不上</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B39" s="43" t="n">
+      <c r="B39" s="42" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="46" t="inlineStr">
+      <c r="C39" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
+      <c r="D39" s="42" t="inlineStr">
         <is>
           <t>多米尼加塑料仓，报价后不再沟通</t>
         </is>
       </c>
-      <c r="E39" s="43" t="inlineStr">
+      <c r="E39" s="42" t="inlineStr">
         <is>
           <t>C00008398｜司斌｜工业｜多米尼加塑料颗粒筒仓项目｜方案V1</t>
         </is>
       </c>
-      <c r="F39" s="43" t="inlineStr">
+      <c r="F39" s="42" t="inlineStr">
         <is>
           <t>客户公司是做木屑颗粒生产加工，目前是收集报价阶段，但是价格发送后不再沟通，初步判断价格不具有任何优势</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B40" s="43" t="n">
+      <c r="B40" s="42" t="n">
         <v>135</v>
       </c>
-      <c r="C40" s="47" t="inlineStr">
+      <c r="C40" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
+      <c r="D40" s="42" t="inlineStr">
         <is>
           <t>阿联酋饲料，工程公司前期调研</t>
         </is>
       </c>
-      <c r="E40" s="43" t="inlineStr">
+      <c r="E40" s="42" t="inlineStr">
         <is>
           <t>C00009949｜司斌｜粮食｜阿联酋饲料颗粒，项目在俄罗斯 |方案V1</t>
         </is>
       </c>
-      <c r="F40" s="43" t="inlineStr">
+      <c r="F40" s="42" t="inlineStr">
         <is>
           <t>对接公司是工程公司，想要对此项目进行投标，但目前项目信息较少，对于客户端属于前期的调研阶段。由于客户要求的时间较短，无法延期。且采购这段时间忙于投标其他项目，因此预估价格晚于客户逾期3天后，由于客户强调一定要再次时间收到预算，所以不利于后续跟进</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="43" t="inlineStr">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B41" s="43" t="n">
+      <c r="B41" s="42" t="n">
         <v>136</v>
       </c>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="C41" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D41" s="43" t="inlineStr">
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Probat国内方仓，重复开单</t>
         </is>
       </c>
-      <c r="E41" s="43" t="inlineStr">
+      <c r="E41" s="42" t="inlineStr">
         <is>
           <t>C00008345｜司斌｜粮食｜Probat国内咖啡仓方仓 |方案V1</t>
         </is>
       </c>
-      <c r="F41" s="43" t="inlineStr">
+      <c r="F41" s="42" t="inlineStr">
         <is>
           <t>与123是同一个客户</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="43" t="inlineStr">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B42" s="43" t="n">
+      <c r="B42" s="42" t="n">
         <v>137</v>
       </c>
-      <c r="C42" s="46" t="inlineStr">
+      <c r="C42" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>伊朗石灰仓，战争前不可能上</t>
         </is>
       </c>
-      <c r="E42" s="43" t="inlineStr">
+      <c r="E42" s="42" t="inlineStr">
         <is>
           <t>C00009745｜司斌｜工业｜伊朗水净化项目石灰仓|方案V1</t>
         </is>
       </c>
-      <c r="F42" s="43" t="inlineStr">
+      <c r="F42" s="42" t="inlineStr">
         <is>
           <t>对接公司是工程公司，项目所处阶段为价格收集，由于霍尔木兹海峡现状，我认为在战争结束前不可能上</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>司斌</t>
         </is>
       </c>
-      <c r="B43" s="43" t="n">
+      <c r="B43" s="42" t="n">
         <v>138</v>
       </c>
-      <c r="C43" s="47" t="inlineStr">
+      <c r="C43" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>马来熟料料场，只要预算</t>
         </is>
       </c>
-      <c r="E43" s="43" t="inlineStr">
+      <c r="E43" s="42" t="inlineStr">
         <is>
           <t>C00009743｜司斌｜工业｜马来西亚熟料料场|方案V1</t>
         </is>
       </c>
-      <c r="F43" s="43" t="inlineStr">
+      <c r="F43" s="42" t="inlineStr">
         <is>
           <t>最终业主是马来西亚的三大水泥厂之一，此项目在前期调研，想要知道预算，需要管理层对此进行评估再判断是否上项目</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B44" s="43" t="n">
+      <c r="B44" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C44" s="47" t="inlineStr">
+      <c r="C44" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>TESO，询价或为了解预算</t>
         </is>
       </c>
-      <c r="E44" s="43" t="inlineStr">
+      <c r="E44" s="42" t="inlineStr">
         <is>
           <t>C00009556｜陈子凡｜工业｜蒙古TESO 4x2500水泥中转站｜方案V1</t>
         </is>
       </c>
-      <c r="F44" s="43" t="inlineStr">
+      <c r="F44" s="42" t="inlineStr">
         <is>
           <t>给客户发了方案，待更新报价。准备报价中，但客户主业是食品，本次询价可能只是为了解投资预算。 8月份在蒙古期间约客户见面，客户见面意愿不强</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="43" t="inlineStr">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B45" s="43" t="n">
+      <c r="B45" s="42" t="n">
         <v>19</v>
       </c>
-      <c r="C45" s="46" t="inlineStr">
+      <c r="C45" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>阿根廷面粉仓，希望不大</t>
         </is>
       </c>
-      <c r="E45" s="43" t="inlineStr">
+      <c r="E45" s="42" t="inlineStr">
         <is>
           <t>C00009734｜陈子凡｜粮食｜ 阿根廷6个面粉仓+3个润麦仓+1个麸皮仓 单仓｜重量计算+清单</t>
         </is>
       </c>
-      <c r="F45" s="43" t="inlineStr">
+      <c r="F45" s="42" t="inlineStr">
         <is>
           <t>报过价了，希望不大。客户为工程公司，项目投标中，且对方对中国供应链很了解，价格非常敏感</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B46" s="43" t="n">
+      <c r="B46" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="C46" s="45" t="inlineStr">
+      <c r="C46" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>厄瓜多尔方仓，比价等通知</t>
         </is>
       </c>
-      <c r="E46" s="43" t="inlineStr">
+      <c r="E46" s="42" t="inlineStr">
         <is>
           <t>C00007248｜陈子凡｜工业｜厄瓜多尔塑料方仓项目｜清单</t>
         </is>
       </c>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="F46" s="42" t="inlineStr">
         <is>
           <t>客户比价中。提交报价后等通知，本次报价相比1期项目有上涨，客户大概率会找新供应商比价</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B47" s="43" t="n">
+      <c r="B47" s="42" t="n">
         <v>21</v>
       </c>
-      <c r="C47" s="47" t="inlineStr">
+      <c r="C47" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>北京生物质，较前期</t>
         </is>
       </c>
-      <c r="E47" s="43" t="inlineStr">
+      <c r="E47" s="42" t="inlineStr">
         <is>
           <t>XXXXX｜陈子凡｜粮食｜北京生物质颗粒装车仓｜方案V1 | 初步方案</t>
         </is>
       </c>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="F47" s="42" t="inlineStr">
         <is>
           <t>跟进中。项目较前期，联系人在出差，需要过一段时间再联系</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B48" s="43" t="n">
+      <c r="B48" s="42" t="n">
         <v>22</v>
       </c>
-      <c r="C48" s="44" t="inlineStr">
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="D48" s="42" t="inlineStr">
         <is>
           <t>蒙古MAK气力，近期可成交</t>
         </is>
       </c>
-      <c r="E48" s="43" t="inlineStr">
+      <c r="E48" s="42" t="inlineStr">
         <is>
           <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="F48" s="42" t="inlineStr">
         <is>
           <t>报价中</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B49" s="43" t="n">
+      <c r="B49" s="42" t="n">
         <v>24</v>
       </c>
-      <c r="C49" s="44" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>MONCEMENT拜访后更新方案</t>
         </is>
       </c>
-      <c r="E49" s="43" t="inlineStr">
+      <c r="E49" s="42" t="inlineStr">
         <is>
           <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
         </is>
       </c>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="F49" s="42" t="inlineStr">
         <is>
           <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B50" s="43" t="n">
+      <c r="B50" s="42" t="n">
         <v>29</v>
       </c>
-      <c r="C50" s="44" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>生力取料机，等授标</t>
         </is>
       </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>20260304 菲律宾生力集团 取料机报价</t>
         </is>
       </c>
-      <c r="F50" s="43" t="inlineStr">
+      <c r="F50" s="42" t="inlineStr">
         <is>
           <t>等授标通知</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="43" t="inlineStr">
+      <c r="A51" s="42" t="inlineStr">
         <is>
           <t>陈子凡</t>
         </is>
       </c>
-      <c r="B51" s="43" t="n">
+      <c r="B51" s="42" t="n">
         <v>33</v>
       </c>
-      <c r="C51" s="45" t="inlineStr">
+      <c r="C51" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
+      <c r="D51" s="42" t="inlineStr">
         <is>
           <t>生力锥底仓，上周报价等反馈</t>
         </is>
       </c>
-      <c r="E51" s="43" t="inlineStr">
+      <c r="E51" s="42" t="inlineStr">
         <is>
           <t>Manila01｜陈子凡｜粮食｜菲律宾4x2000吨锥底仓｜清单V1 | 报价清单</t>
         </is>
       </c>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="F51" s="42" t="inlineStr">
         <is>
           <t>已提交报价，等反馈。单仓项目，上周报价，等反馈。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="43" t="inlineStr">
+      <c r="A52" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B52" s="43" t="n">
+      <c r="B52" s="42" t="n">
         <v>104</v>
       </c>
-      <c r="C52" s="46" t="inlineStr">
+      <c r="C52" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
+      <c r="D52" s="42" t="inlineStr">
         <is>
           <t>斯里兰卡稻谷，报价后反馈不积极</t>
         </is>
       </c>
-      <c r="E52" s="43" t="inlineStr">
+      <c r="E52" s="42" t="inlineStr">
         <is>
           <t>C00009786｜苗恒｜粮食｜斯里兰卡10x2000吨稻谷仓项目｜方案V1</t>
         </is>
       </c>
-      <c r="F52" s="43" t="inlineStr">
+      <c r="F52" s="42" t="inlineStr">
         <is>
           <t>客户与土耳其ALTINBILEK有合作，上次报价大概率找我们探价和比价，报价后反馈不积极</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="43" t="inlineStr">
+      <c r="A53" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B53" s="43" t="n">
+      <c r="B53" s="42" t="n">
         <v>105</v>
       </c>
-      <c r="C53" s="44" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
+      <c r="D53" s="42" t="inlineStr">
         <is>
           <t>新加坡熟石灰，约8月底/9月初反馈</t>
         </is>
       </c>
-      <c r="E53" s="43" t="inlineStr">
+      <c r="E53" s="42" t="inlineStr">
         <is>
           <t>C00009762｜苗恒｜工业｜新加坡4x200m3熟石灰粉不锈钢仓项目｜方案V1</t>
         </is>
       </c>
-      <c r="F53" s="43" t="inlineStr">
+      <c r="F53" s="42" t="inlineStr">
         <is>
           <t>跟进中，客户为工程公司，回复8月底或9月初给我们反馈</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="43" t="inlineStr">
+      <c r="A54" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B54" s="43" t="n">
+      <c r="B54" s="42" t="n">
         <v>106</v>
       </c>
-      <c r="C54" s="44" t="inlineStr">
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
+      <c r="D54" s="42" t="inlineStr">
         <is>
           <t>阿尔及利亚气力，9月更多现场信息</t>
         </is>
       </c>
-      <c r="E54" s="43" t="inlineStr">
+      <c r="E54" s="42" t="inlineStr">
         <is>
           <t>C00009353｜苗恒｜工业｜阿尔及利亚6x2500吨水泥仓+200TPH气力输送项目｜方案V1</t>
         </is>
       </c>
-      <c r="F54" s="43" t="inlineStr">
+      <c r="F54" s="42" t="inlineStr">
         <is>
           <t>跟进中，客户给了港口项目布置图，正在沟通方案布局，9月份客户会给更多项目现场信息</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="43" t="inlineStr">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B55" s="43" t="n">
+      <c r="B55" s="42" t="n">
         <v>109</v>
       </c>
-      <c r="C55" s="44" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D55" s="42" t="inlineStr">
         <is>
           <t>墨西哥粮仓，确认V4后更报价</t>
         </is>
       </c>
-      <c r="E55" s="43" t="inlineStr">
+      <c r="E55" s="42" t="inlineStr">
         <is>
           <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="F55" s="43" t="inlineStr">
+      <c r="F55" s="42" t="inlineStr">
         <is>
           <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="43" t="inlineStr">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B56" s="43" t="n">
+      <c r="B56" s="42" t="n">
         <v>113</v>
       </c>
-      <c r="C56" s="44" t="inlineStr">
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
+      <c r="D56" s="42" t="inlineStr">
         <is>
           <t>斯里兰卡熟料，已联真实业主</t>
         </is>
       </c>
-      <c r="E56" s="43" t="inlineStr">
+      <c r="E56" s="42" t="inlineStr">
         <is>
           <t>C00009001｜苗恒｜工业｜斯里兰卡1x35000吨熟料仓项目｜方案V2</t>
         </is>
       </c>
-      <c r="F56" s="43" t="inlineStr">
+      <c r="F56" s="42" t="inlineStr">
         <is>
           <t>重点项目跟进中，客户找了江苏鹏飞做的整厂规划布置，让我们报混凝土仓报价，准备给客户更新第二版</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B57" s="43" t="n">
+      <c r="B57" s="42" t="n">
         <v>120</v>
       </c>
-      <c r="C57" s="44" t="inlineStr">
+      <c r="C57" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>伊拉克水泥仓，9.2上海见面</t>
         </is>
       </c>
-      <c r="E57" s="43" t="inlineStr">
+      <c r="E57" s="42" t="inlineStr">
         <is>
           <t>C00009921｜苗恒｜工业｜伊拉克2x10000吨水泥仓项目｜方案V1</t>
         </is>
       </c>
-      <c r="F57" s="43" t="inlineStr">
+      <c r="F57" s="42" t="inlineStr">
         <is>
           <t>已报价，客户预计9.2到上海，希望可以见一面</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="43" t="inlineStr">
+      <c r="A58" s="42" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B58" s="43" t="n">
+      <c r="B58" s="42" t="n">
         <v>121</v>
       </c>
-      <c r="C58" s="46" t="inlineStr">
+      <c r="C58" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>与伊拉克同项目，重复开单</t>
         </is>
       </c>
-      <c r="E58" s="43" t="inlineStr">
+      <c r="E58" s="42" t="inlineStr">
         <is>
           <t>C00009883｜苗恒｜工业｜德国3x1600吨水泥仓+3个料斗投标项目｜方案V1</t>
         </is>
       </c>
-      <c r="F58" s="43" t="inlineStr">
+      <c r="F58" s="42" t="inlineStr">
         <is>
           <t>与上面伊拉克2x10000同属一个项目，需要等最终业主确认哪个方案</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="43" t="inlineStr">
+      <c r="A59" s="42" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B59" s="43" t="n">
+      <c r="B59" s="42" t="n">
         <v>72</v>
       </c>
-      <c r="C59" s="44" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="D59" s="42" t="inlineStr">
         <is>
           <t>坦桑小麦仓，新技术要求已反馈</t>
         </is>
       </c>
-      <c r="E59" s="43" t="inlineStr">
+      <c r="E59" s="42" t="inlineStr">
         <is>
           <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="F59" s="43" t="inlineStr">
+      <c r="F59" s="42" t="inlineStr">
         <is>
           <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="43" t="inlineStr">
+      <c r="A60" s="42" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B60" s="43" t="n">
+      <c r="B60" s="42" t="n">
         <v>73</v>
       </c>
-      <c r="C60" s="47" t="inlineStr">
+      <c r="C60" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D60" s="42" t="inlineStr">
         <is>
           <t>尼日利亚，中间商代询比价</t>
         </is>
       </c>
-      <c r="E60" s="43" t="inlineStr">
+      <c r="E60" s="42" t="inlineStr">
         <is>
           <t>C00009584|冯乐|粮食|尼日利亚-2×1200T玉米仓项目|方案V1</t>
         </is>
       </c>
-      <c r="F60" s="43" t="inlineStr">
+      <c r="F60" s="42" t="inlineStr">
         <is>
           <t>目前是一位中间贸易商替业主询价，我方已提供方案和报价，多家供应商对比。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="42" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B61" s="43" t="n">
+      <c r="B61" s="42" t="n">
         <v>74</v>
       </c>
-      <c r="C61" s="44" t="inlineStr">
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>也门装配仓V3，技术澄清中</t>
         </is>
       </c>
-      <c r="E61" s="43" t="inlineStr">
+      <c r="E61" s="42" t="inlineStr">
         <is>
           <t>C00009383｜冯乐｜工业｜也门-3×1200m³水泥装配仓项目｜方案V3</t>
         </is>
       </c>
-      <c r="F61" s="43" t="inlineStr">
+      <c r="F61" s="42" t="inlineStr">
         <is>
           <t>已进行多次报价，客户对价格比较敏感，目前正在和对方团队进行技术澄清。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="43" t="inlineStr">
+      <c r="A62" s="42" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B62" s="43" t="n">
+      <c r="B62" s="42" t="n">
         <v>75</v>
       </c>
-      <c r="C62" s="45" t="inlineStr">
+      <c r="C62" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D62" s="42" t="inlineStr">
         <is>
           <t>土库曼料斗，等总包更新</t>
         </is>
       </c>
-      <c r="E62" s="43" t="inlineStr">
+      <c r="E62" s="42" t="inlineStr">
         <is>
           <t>C00009344｜冯乐｜工业｜土库曼斯坦火车装载料斗项目｜方案V1</t>
         </is>
       </c>
-      <c r="F62" s="43" t="inlineStr">
+      <c r="F62" s="42" t="inlineStr">
         <is>
           <t>客户是总承包商，我们是分包，已进行过两次商务报价。整个项目比较大，我们只负责料斗报价，目前等总包更新项目进展。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="43" t="inlineStr">
+      <c r="A63" s="42" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B63" s="43" t="n">
+      <c r="B63" s="42" t="n">
         <v>76</v>
       </c>
-      <c r="C63" s="47" t="inlineStr">
+      <c r="C63" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D63" s="43" t="inlineStr">
+      <c r="D63" s="42" t="inlineStr">
         <is>
           <t>阿根廷储存仓，业主规划收集报价</t>
         </is>
       </c>
-      <c r="E63" s="43" t="inlineStr">
+      <c r="E63" s="42" t="inlineStr">
         <is>
           <t>C00009727｜冯乐｜粮食｜阿根廷2×3000T+6×800T 储存仓项目｜方案V2</t>
         </is>
       </c>
-      <c r="F63" s="43" t="inlineStr">
+      <c r="F63" s="42" t="inlineStr">
         <is>
           <t>直接业主，是一家从农田到深加工全产业链的农业综合集团，该项目是业主的规划项目。目前处于收集多方供应商的方案和报价，我方已提供商务报价。等待业主回复。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="43" t="inlineStr">
+      <c r="A64" s="42" t="inlineStr">
         <is>
           <t>冯乐</t>
         </is>
       </c>
-      <c r="B64" s="43" t="n">
+      <c r="B64" s="42" t="n">
         <v>77</v>
       </c>
-      <c r="C64" s="45" t="inlineStr">
+      <c r="C64" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
+      <c r="D64" s="42" t="inlineStr">
         <is>
           <t>新疆掺混仓，已提供商务报价</t>
         </is>
       </c>
-      <c r="E64" s="43" t="inlineStr">
+      <c r="E64" s="42" t="inlineStr">
         <is>
           <t>C00009344｜冯乐｜新疆｜PP掺混料仓×10+PE掺混料仓×10项目｜方案V1</t>
         </is>
       </c>
-      <c r="F64" s="43" t="inlineStr">
+      <c r="F64" s="42" t="inlineStr">
         <is>
           <t>客户是总承包商，我们是分包，已提供商务方案报价。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="43" t="inlineStr">
+      <c r="A65" s="42" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B65" s="43" t="n">
+      <c r="B65" s="42" t="n">
         <v>82</v>
       </c>
-      <c r="C65" s="44" t="inlineStr">
+      <c r="C65" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D65" s="43" t="inlineStr">
+      <c r="D65" s="42" t="inlineStr">
         <is>
           <t>越南码头，土地审批+贷款，10月底更新</t>
         </is>
       </c>
-      <c r="E65" s="43" t="inlineStr">
+      <c r="E65" s="42" t="inlineStr">
         <is>
           <t>C00009357|韩鸿彪|工业|越南水泥码头+木屑颗粒仓项目|方案V1</t>
         </is>
       </c>
-      <c r="F65" s="43" t="inlineStr">
+      <c r="F65" s="42" t="inlineStr">
         <is>
           <t>项目土地审批和银行贷款阶段，预计10月底会有进一步更新</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="43" t="inlineStr">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B66" s="43" t="n">
+      <c r="B66" s="42" t="n">
         <v>83</v>
       </c>
-      <c r="C66" s="44" t="inlineStr">
+      <c r="C66" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D66" s="43" t="inlineStr">
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>也门扩建V3，业主在对比方案</t>
         </is>
       </c>
-      <c r="E66" s="43" t="inlineStr">
+      <c r="E66" s="42" t="inlineStr">
         <is>
           <t>C00008493|韩鸿彪|工业|也门2x1600T水泥仓扩建项目方案V2</t>
         </is>
       </c>
-      <c r="F66" s="43" t="inlineStr">
+      <c r="F66" s="42" t="inlineStr">
         <is>
           <t>更新方案更新报价V3，业主在对比方案和报价，项目计划是27年Q1上</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="43" t="inlineStr">
+      <c r="A67" s="42" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B67" s="43" t="n">
+      <c r="B67" s="42" t="n">
         <v>86</v>
       </c>
-      <c r="C67" s="45" t="inlineStr">
+      <c r="C67" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D67" s="43" t="inlineStr">
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>QNC Halong，配合性等业主反馈</t>
         </is>
       </c>
-      <c r="E67" s="43" t="inlineStr">
+      <c r="E67" s="42" t="inlineStr">
         <is>
           <t>C00008036|韩鸿彪|工业|越南QNC-Halong2x1500T水泥仓方案V2</t>
         </is>
       </c>
-      <c r="F67" s="43" t="inlineStr">
+      <c r="F67" s="42" t="inlineStr">
         <is>
           <t>越南4x6000业主的客户，等待业主的跟进反馈，配合性项目不做重点</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="43" t="inlineStr">
+      <c r="A68" s="42" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B68" s="43" t="n">
+      <c r="B68" s="42" t="n">
         <v>88</v>
       </c>
-      <c r="C68" s="46" t="inlineStr">
+      <c r="C68" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D68" s="43" t="inlineStr">
+      <c r="D68" s="42" t="inlineStr">
         <is>
           <t>广宁雨棚，报建复杂或将放弃</t>
         </is>
       </c>
-      <c r="E68" s="43" t="inlineStr">
+      <c r="E68" s="42" t="inlineStr">
         <is>
           <t>20260120 韩鸿彪 越南广宁水泥4*6000T筒仓配套装船钢结构雨棚（河边雨棚）</t>
         </is>
       </c>
-      <c r="F68" s="43" t="inlineStr">
+      <c r="F68" s="42" t="inlineStr">
         <is>
           <t>土地报批手续中，杰余报建水槽手续复杂和预算原因，可能会放弃该项目建设</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="43" t="inlineStr">
+      <c r="A69" s="42" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B69" s="43" t="n">
+      <c r="B69" s="42" t="n">
         <v>89</v>
       </c>
-      <c r="C69" s="44" t="inlineStr">
+      <c r="C69" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
+      <c r="D69" s="42" t="inlineStr">
         <is>
           <t>QNC包装线，更新报价等决策</t>
         </is>
       </c>
-      <c r="E69" s="43" t="inlineStr">
+      <c r="E69" s="42" t="inlineStr">
         <is>
           <t>C00008036 韩鸿彪 越南 4x6000T筒仓系统配套输送设备方案 V5</t>
         </is>
       </c>
-      <c r="F69" s="43" t="inlineStr">
+      <c r="F69" s="42" t="inlineStr">
         <is>
           <t>更新方案，更新报价，等待决策。业主计划先上一条（6台）包装线，第一个筒仓完工后先运行起来</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="43" t="inlineStr">
+      <c r="A70" s="42" t="inlineStr">
         <is>
           <t>韩鸿彪</t>
         </is>
       </c>
-      <c r="B70" s="43" t="n">
+      <c r="B70" s="42" t="n">
         <v>91</v>
       </c>
-      <c r="C70" s="45" t="inlineStr">
+      <c r="C70" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D70" s="43" t="inlineStr">
+      <c r="D70" s="42" t="inlineStr">
         <is>
           <t>卢旺达面粉厂，第一版报价阶段</t>
         </is>
       </c>
-      <c r="E70" s="43" t="inlineStr">
+      <c r="E70" s="42" t="inlineStr">
         <is>
           <t>C00009474|韩鸿彪|粮食|卢旺达面粉厂3x2500T小麦仓项目|方案V1</t>
         </is>
       </c>
-      <c r="F70" s="43" t="inlineStr">
+      <c r="F70" s="42" t="inlineStr">
         <is>
           <t>面粉厂扩建项目，规模不大，但项目真实，第一版报价阶段</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="43" t="inlineStr">
+      <c r="A71" s="42" t="inlineStr">
         <is>
           <t>马鹏飞</t>
         </is>
       </c>
-      <c r="B71" s="43" t="n">
+      <c r="B71" s="42" t="n">
         <v>93</v>
       </c>
-      <c r="C71" s="45" t="inlineStr">
+      <c r="C71" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D71" s="43" t="inlineStr">
+      <c r="D71" s="42" t="inlineStr">
         <is>
           <t>新加坡储水罐，延标到年底</t>
         </is>
       </c>
-      <c r="E71" s="43" t="inlineStr">
+      <c r="E71" s="42" t="inlineStr">
         <is>
           <t>C00009797  | 马鹏飞 | 工业 | 新加坡波纹钢板储水罐 | 方案V1 |</t>
         </is>
       </c>
-      <c r="F71" s="43" t="inlineStr">
+      <c r="F71" s="42" t="inlineStr">
         <is>
           <t>业主仍在投标，目前项目延标，预计2026年底投标</t>
         </is>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="43" t="inlineStr">
+      <c r="A72" s="42" t="inlineStr">
         <is>
           <t>马鹏飞</t>
         </is>
       </c>
-      <c r="B72" s="43" t="n">
+      <c r="B72" s="42" t="n">
         <v>99</v>
       </c>
-      <c r="C72" s="44" t="inlineStr">
+      <c r="C72" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D72" s="43" t="inlineStr">
+      <c r="D72" s="42" t="inlineStr">
         <is>
           <t>生力冷却站，待决策层批复</t>
         </is>
       </c>
-      <c r="E72" s="43" t="inlineStr">
+      <c r="E72" s="42" t="inlineStr">
         <is>
           <t>C00001420 | 马鹏飞 | 工业 |生力集团100TPH水泥冷却站项目需画电气单线图及理清范围 | 方案V4 |</t>
         </is>
       </c>
-      <c r="F72" s="43" t="inlineStr">
+      <c r="F72" s="42" t="inlineStr">
         <is>
           <t>已完成单线图提供，生力水泥冷却站项目，已提交所有所需资料，待生力决策层批复，目前尚未有更新情况</t>
         </is>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="43" t="inlineStr">
+      <c r="A73" s="42" t="inlineStr">
         <is>
           <t>马鹏飞</t>
         </is>
       </c>
-      <c r="B73" s="43" t="n">
+      <c r="B73" s="42" t="n">
         <v>102</v>
       </c>
-      <c r="C73" s="45" t="inlineStr">
+      <c r="C73" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
+      <c r="D73" s="42" t="inlineStr">
         <is>
           <t>Intercem法国单仓，投标长期无更新</t>
         </is>
       </c>
-      <c r="E73" s="43" t="inlineStr">
+      <c r="E73" s="42" t="inlineStr">
         <is>
           <t>C00004564 | 马鹏飞 | 德国Intercem公司法国水泥厂项目单仓询价 | 方案 V3 |</t>
         </is>
       </c>
-      <c r="F73" s="43" t="inlineStr">
+      <c r="F73" s="42" t="inlineStr">
         <is>
           <t>已做方案，及报价，目前此业主也是投标，目前并无更新的投标情况</t>
         </is>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="43" t="inlineStr">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>马鹏飞</t>
         </is>
       </c>
-      <c r="B74" s="43" t="n">
+      <c r="B74" s="42" t="n">
         <v>103</v>
       </c>
-      <c r="C74" s="45" t="inlineStr">
+      <c r="C74" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
+      <c r="D74" s="42" t="inlineStr">
         <is>
           <t>拉法基墨西哥，刚报价尚无反馈</t>
         </is>
       </c>
-      <c r="E74" s="43" t="inlineStr">
+      <c r="E74" s="42" t="inlineStr">
         <is>
           <t>C00001611| 马鹏飞 | 工业 | 墨西哥拉法基1*500吨水泥仓项目 | 方案V1 |</t>
         </is>
       </c>
-      <c r="F74" s="43" t="inlineStr">
+      <c r="F74" s="42" t="inlineStr">
         <is>
           <t>已做方案，及报价，刚发出报价，尚无业主对价格的反馈意见。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="43" t="inlineStr">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>王伟乐</t>
         </is>
       </c>
-      <c r="B75" s="43" t="n">
+      <c r="B75" s="42" t="n">
         <v>144</v>
       </c>
-      <c r="C75" s="47" t="inlineStr">
+      <c r="C75" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
+      <c r="D75" s="42" t="inlineStr">
         <is>
           <t>苏丹农行，还在做预算报价</t>
         </is>
       </c>
-      <c r="E75" s="43" t="inlineStr">
+      <c r="E75" s="42" t="inlineStr">
         <is>
           <t>C00006335 | 王伟乐 | 粮食|  苏丹农业银行粮储项目 | 方案 V1|</t>
         </is>
       </c>
-      <c r="F75" s="43" t="inlineStr">
+      <c r="F75" s="42" t="inlineStr">
         <is>
           <t>还在进行预算的报价，土建的报价需要预估</t>
         </is>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="43" t="inlineStr">
+      <c r="A76" s="42" t="inlineStr">
         <is>
           <t>王伟乐</t>
         </is>
       </c>
-      <c r="B76" s="43" t="n">
+      <c r="B76" s="42" t="n">
         <v>145</v>
       </c>
-      <c r="C76" s="46" t="inlineStr">
+      <c r="C76" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D76" s="43" t="inlineStr">
+      <c r="D76" s="42" t="inlineStr">
         <is>
           <t>埃及螺旋仓，已报价未反馈</t>
         </is>
       </c>
-      <c r="E76" s="43" t="inlineStr">
+      <c r="E76" s="42" t="inlineStr">
         <is>
           <t>C00006274| 王伟乐|工业|2026.6.15 |埃及 4*3000t 螺旋咬口仓项目| 方案V1</t>
         </is>
       </c>
-      <c r="F76" s="43" t="inlineStr">
+      <c r="F76" s="42" t="inlineStr">
         <is>
           <t>已报价，客户未反馈报价的情况，后期可以继续跟进</t>
         </is>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="43" t="inlineStr">
+      <c r="A77" s="42" t="inlineStr">
         <is>
           <t>王伟乐</t>
         </is>
       </c>
-      <c r="B77" s="43" t="n">
+      <c r="B77" s="42" t="n">
         <v>146</v>
       </c>
-      <c r="C77" s="44" t="inlineStr">
+      <c r="C77" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D77" s="43" t="inlineStr">
+      <c r="D77" s="42" t="inlineStr">
         <is>
           <t>裕廊港，最新价澄清中</t>
         </is>
       </c>
-      <c r="E77" s="43" t="inlineStr">
+      <c r="E77" s="42" t="inlineStr">
         <is>
           <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
         </is>
       </c>
-      <c r="F77" s="43" t="inlineStr">
+      <c r="F77" s="42" t="inlineStr">
         <is>
           <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
         </is>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="43" t="inlineStr">
+      <c r="A78" s="42" t="inlineStr">
         <is>
           <t>王伟乐</t>
         </is>
       </c>
-      <c r="B78" s="43" t="n">
+      <c r="B78" s="42" t="n">
         <v>151</v>
       </c>
-      <c r="C78" s="45" t="inlineStr">
+      <c r="C78" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D78" s="43" t="inlineStr">
+      <c r="D78" s="42" t="inlineStr">
         <is>
           <t>CIMAF，已报价库龄偏长</t>
         </is>
       </c>
-      <c r="E78" s="43" t="inlineStr">
+      <c r="E78" s="42" t="inlineStr">
         <is>
           <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
         </is>
       </c>
-      <c r="F78" s="43" t="inlineStr">
+      <c r="F78" s="42" t="inlineStr">
         <is>
           <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
         </is>
       </c>
     </row>
     <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="43" t="inlineStr">
+      <c r="A79" s="42" t="inlineStr">
         <is>
           <t>尹韬越</t>
         </is>
       </c>
-      <c r="B79" s="43" t="n">
+      <c r="B79" s="42" t="n">
         <v>153</v>
       </c>
-      <c r="C79" s="46" t="inlineStr">
+      <c r="C79" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D79" s="43" t="inlineStr">
+      <c r="D79" s="42" t="inlineStr">
         <is>
           <t>仅写已报价，超90天无下一步</t>
         </is>
       </c>
-      <c r="E79" s="43" t="inlineStr">
+      <c r="E79" s="42" t="inlineStr">
         <is>
           <t>C00009303｜尹韬越｜工业｜乌兹别克斯坦尼什巴什一期储煤场末煤仓项目｜方案V1</t>
         </is>
       </c>
-      <c r="F79" s="43" t="inlineStr">
+      <c r="F79" s="42" t="inlineStr">
         <is>
           <t>已报价</t>
         </is>
       </c>
     </row>
     <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="43" t="inlineStr">
+      <c r="A80" s="42" t="inlineStr">
         <is>
           <t>尹韬越</t>
         </is>
       </c>
-      <c r="B80" s="43" t="n">
+      <c r="B80" s="42" t="n">
         <v>154</v>
       </c>
-      <c r="C80" s="46" t="inlineStr">
+      <c r="C80" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D80" s="43" t="inlineStr">
+      <c r="D80" s="42" t="inlineStr">
         <is>
           <t>仅写已报方案，无互动</t>
         </is>
       </c>
-      <c r="E80" s="43" t="inlineStr">
+      <c r="E80" s="42" t="inlineStr">
         <is>
           <t>C00009297｜尹韬越｜粮食｜格鲁吉亚第比利斯3×1000吨玉米仓｜方案V1</t>
         </is>
       </c>
-      <c r="F80" s="43" t="inlineStr">
+      <c r="F80" s="42" t="inlineStr">
         <is>
           <t>已报方案</t>
         </is>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="43" t="inlineStr">
+      <c r="A81" s="42" t="inlineStr">
         <is>
           <t>尹韬越</t>
         </is>
       </c>
-      <c r="B81" s="43" t="n">
+      <c r="B81" s="42" t="n">
         <v>156</v>
       </c>
-      <c r="C81" s="44" t="inlineStr">
+      <c r="C81" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D81" s="43" t="inlineStr">
+      <c r="D81" s="42" t="inlineStr">
         <is>
           <t>哈萨克征地，长周期有节点</t>
         </is>
       </c>
-      <c r="E81" s="43" t="inlineStr">
+      <c r="E81" s="42" t="inlineStr">
         <is>
           <t>C00008577｜尹韬越｜粮食｜哈萨克斯坦4×3500吨粮食项目｜方案V2</t>
         </is>
       </c>
-      <c r="F81" s="43" t="inlineStr">
+      <c r="F81" s="42" t="inlineStr">
         <is>
           <t>已报方案，目前对方在征地</t>
         </is>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="43" t="inlineStr">
+      <c r="A82" s="42" t="inlineStr">
         <is>
           <t>尹韬越</t>
         </is>
       </c>
-      <c r="B82" s="43" t="n">
+      <c r="B82" s="42" t="n">
         <v>158</v>
       </c>
-      <c r="C82" s="46" t="inlineStr">
+      <c r="C82" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D82" s="43" t="inlineStr">
+      <c r="D82" s="42" t="inlineStr">
         <is>
           <t>与156同一征地，重复开单</t>
         </is>
       </c>
-      <c r="E82" s="43" t="inlineStr">
+      <c r="E82" s="42" t="inlineStr">
         <is>
           <t>C00008577 尹韬越哈萨克斯坦4×3500吨粮食项目 方案1</t>
         </is>
       </c>
-      <c r="F82" s="43" t="inlineStr">
+      <c r="F82" s="42" t="inlineStr">
         <is>
           <t>已报方案，目前对方在征地</t>
         </is>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="43" t="inlineStr">
+      <c r="A83" s="42" t="inlineStr">
         <is>
           <t>王伟超</t>
         </is>
       </c>
-      <c r="B83" s="43" t="n">
+      <c r="B83" s="42" t="n">
         <v>139</v>
       </c>
-      <c r="C83" s="47" t="inlineStr">
+      <c r="C83" s="46" t="inlineStr">
         <is>
           <t>前期</t>
         </is>
       </c>
-      <c r="D83" s="43" t="inlineStr">
+      <c r="D83" s="42" t="inlineStr">
         <is>
           <t>乌干达，非业主了解预算</t>
         </is>
       </c>
-      <c r="E83" s="43" t="inlineStr">
+      <c r="E83" s="42" t="inlineStr">
         <is>
           <t>C00009593｜王伟超｜粮食｜乌干达生咖啡豆筒仓项目｜方案V1</t>
         </is>
       </c>
-      <c r="F83" s="43" t="inlineStr">
+      <c r="F83" s="42" t="inlineStr">
         <is>
           <t>已经和客户开过视频会，发了方案和报价，但不是最终业主，而且业主表示目前是在准备阶段，这次询价可能是为了了解大概需要多少预算</t>
         </is>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="43" t="inlineStr">
+      <c r="A84" s="42" t="inlineStr">
         <is>
           <t>王伟超</t>
         </is>
       </c>
-      <c r="B84" s="43" t="n">
+      <c r="B84" s="42" t="n">
         <v>141</v>
       </c>
-      <c r="C84" s="44" t="inlineStr">
+      <c r="C84" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D84" s="43" t="inlineStr">
+      <c r="D84" s="42" t="inlineStr">
         <is>
           <t>哥斯达黎加，多次改图等回复</t>
         </is>
       </c>
-      <c r="E84" s="43" t="inlineStr">
+      <c r="E84" s="42" t="inlineStr">
         <is>
           <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
         </is>
       </c>
-      <c r="F84" s="43" t="inlineStr">
+      <c r="F84" s="42" t="inlineStr">
         <is>
           <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
         </is>
       </c>
     </row>
     <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="43" t="inlineStr">
+      <c r="A85" s="42" t="inlineStr">
         <is>
           <t>王伟超</t>
         </is>
       </c>
-      <c r="B85" s="43" t="n">
+      <c r="B85" s="42" t="n">
         <v>143</v>
       </c>
-      <c r="C85" s="45" t="inlineStr">
+      <c r="C85" s="44" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
-      <c r="D85" s="43" t="inlineStr">
+      <c r="D85" s="42" t="inlineStr">
         <is>
           <t>达沃料场，价格超预期</t>
         </is>
       </c>
-      <c r="E85" s="43" t="inlineStr">
+      <c r="E85" s="42" t="inlineStr">
         <is>
           <t>C00006712｜王伟超｜工业｜菲律宾达沃料场项目｜方案V1</t>
         </is>
       </c>
-      <c r="F85" s="43" t="inlineStr">
+      <c r="F85" s="42" t="inlineStr">
         <is>
           <t>与陈总沟通后，最终决定让我继续跟进，已经发送过方案与报价，但是根据料场的跨度过大，结构计算重量偏大，所以价格超过对方的预期，中间商正在与业主了解更多信息</t>
         </is>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="43" t="inlineStr">
+      <c r="A86" s="42" t="inlineStr">
         <is>
           <t>张硕</t>
         </is>
       </c>
-      <c r="B86" s="43" t="n">
+      <c r="B86" s="42" t="n">
+        <v>167</v>
+      </c>
+      <c r="C86" s="46" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
+        <is>
+          <t>大EPC需投标并设当地分公司，持续跟进</t>
+        </is>
+      </c>
+      <c r="E86" s="42" t="inlineStr">
+        <is>
+          <t>20260105张硕 哈里发港粮食码头来粮接收及储存项目</t>
+        </is>
+      </c>
+      <c r="F86" s="42" t="inlineStr">
+        <is>
+          <t>项目为大EPC，需要投标并在当地成立分公司，后续持续跟进</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="42" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="B87" s="42" t="n">
         <v>168</v>
       </c>
-      <c r="C86" s="44" t="inlineStr">
+      <c r="C87" s="43" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="D86" s="43" t="inlineStr">
+      <c r="D87" s="42" t="inlineStr">
         <is>
           <t>斯里兰卡小麦仓，报价已上呈总裁</t>
         </is>
       </c>
-      <c r="E86" s="43" t="inlineStr">
+      <c r="E87" s="42" t="inlineStr">
         <is>
           <t>C00009858 | 张硕 | 粮食 | 斯里兰卡汉班托塔Golden Harvest Mill3x1500MT小麦仓扩建项目</t>
         </is>
       </c>
-      <c r="F86" s="43" t="inlineStr">
+      <c r="F87" s="42" t="inlineStr">
         <is>
           <t>业主收到3座仓的正式报价后没有直接给出评论意见，仅回复说以将报价上呈给公司总裁，判断其从多方供应商处比较报价后再做决定，跟进策略对业主按保持每周频次跟进，不表现急切情绪；另从近期开发的当地代理处侧面了解项目进展</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="43" t="inlineStr">
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="42" t="inlineStr">
         <is>
           <t>张硕</t>
         </is>
       </c>
-      <c r="B87" s="43" t="n">
+      <c r="B88" s="42" t="n">
         <v>169</v>
       </c>
-      <c r="C87" s="46" t="inlineStr">
+      <c r="C88" s="45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D87" s="43" t="inlineStr">
+      <c r="D88" s="42" t="inlineStr">
         <is>
           <t>印尼料斗，确认清单时无视邮件</t>
         </is>
       </c>
-      <c r="E87" s="43" t="inlineStr">
+      <c r="E88" s="42" t="inlineStr">
         <is>
           <t>C00009866 | 张硕｜工业｜印尼工程公司PT REXLINE生物质30m³定量料斗项目｜方案V1</t>
         </is>
       </c>
-      <c r="F87" s="43" t="inlineStr">
+      <c r="F88" s="42" t="inlineStr">
         <is>
           <t>客户为印尼本地工程公司，在收到我方的方案和设备清单（不含报价），与其沟通对方案图纸和设备清单参数确认时，对方多次无视邮件和Whatsapp信息，初步判定为客户可能已收到合适的报价</t>
         </is>
@@ -12278,13 +12300,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>0</v>
@@ -12456,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
@@ -12480,7 +12502,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -12944,7 +12966,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>1</v>
@@ -13702,7 +13724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13710,7 +13732,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
@@ -14371,8 +14393,44 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="7" t="n">
+        <v>167</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>无编码</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>20260105张硕 哈里发港粮食码头来粮接收及储存项目</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>大EPC需投标并设当地分公司，已标进行中，按前期计</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>项目为大EPC，需要投标并在当地成立分公司，后续持续跟进</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14383,7 +14441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14733,48 +14791,48 @@
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>韩鸿彪</t>
+          <t>苗恒</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>无编码</t>
+          <t>C00009786</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>20260108 韩鸿彪 越南广宁水泥4*5000T筒仓配套装船钢结构雨棚</t>
+          <t>C00009786｜苗恒｜粮食｜斯里兰卡10x2000吨稻谷仓项目｜方案V1</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>未填</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>重复开单</t>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>该结未结</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>与序号86重复，状态未填</t>
+          <t>大概率探价比价，报价后反馈不积极</t>
         </is>
       </c>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>与86重复</t>
+          <t>客户与土耳其ALTINBILEK有合作，上次报价大概率找我们探价和比价，报价后反馈不积极</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="7" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -14783,12 +14841,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>C00009786</t>
+          <t>C00009883</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C00009786｜苗恒｜粮食｜斯里兰卡10x2000吨稻谷仓项目｜方案V1</t>
+          <t>C00009883｜苗恒｜工业｜德国3x1600吨水泥仓+3个料斗投标项目｜方案V1</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -14796,40 +14854,40 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>该结未结</t>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>重复开单</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>大概率探价比价，报价后反馈不积极</t>
+          <t>与伊拉克2万吨仓属同一项目等业主选方案</t>
         </is>
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>客户与土耳其ALTINBILEK有合作，上次报价大概率找我们探价和比价，报价后反馈不积极</t>
+          <t>与上面伊拉克2x10000同属一个项目，需要等最终业主确认哪个方案</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>苗恒</t>
+          <t>司斌</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>C00009883</t>
+          <t>C00008345</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>C00009883｜苗恒｜工业｜德国3x1600吨水泥仓+3个料斗投标项目｜方案V1</t>
+          <t>C00008345｜司斌｜粮食｜咖啡仓方仓 |方案V1</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -14837,26 +14895,26 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>重复开单</t>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>该结未结</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>与伊拉克2万吨仓属同一项目等业主选方案</t>
+          <t>三次报价均无反馈，前期价格咨询</t>
         </is>
       </c>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>与上面伊拉克2x10000同属一个项目，需要等最终业主确认哪个方案</t>
+          <t>客户公司主业咖啡生产线，在全球都有项目，国内与星巴克，瑞幸都有合作。项目处于前期价格咨询。已就此公司进行了三次报价，但均无任何反馈，客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -14865,12 +14923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>C00008345</t>
+          <t>C00009546</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>C00008345｜司斌｜粮食｜咖啡仓方仓 |方案V1</t>
+          <t>C00009546｜司斌｜工业｜越南6*800+2*450灰仓｜方案V1</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -14885,19 +14943,19 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>三次报价均无反馈，前期价格咨询</t>
+          <t>工程公司投标，技术无法澄清，胜率不高</t>
         </is>
       </c>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>客户公司主业咖啡生产线，在全球都有项目，国内与星巴克，瑞幸都有合作。项目处于前期价格咨询。已就此公司进行了三次报价，但均无任何反馈，客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+          <t>对接公司是工程公司，但是主业与我们行业不相关，此项目为投标项目，对接公司与最终业主有过合作，但技术问题无法澄清，虽然发送了报价，但是在较少的技术澄清下，胜率不高</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -14906,12 +14964,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>C00009546</t>
+          <t>C00008345</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>C00009546｜司斌｜工业｜越南6*800+2*450灰仓｜方案V1</t>
+          <t>C00008345｜司斌｜粮食｜咖啡缓冲斗｜方案V1</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -14919,26 +14977,26 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>该结未结</t>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>重复开单</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>工程公司投标，技术无法澄清，胜率不高</t>
+          <t>与咖啡仓方仓同一客户C00008345</t>
         </is>
       </c>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>对接公司是工程公司，但是主业与我们行业不相关，此项目为投标项目，对接公司与最终业主有过合作，但技术问题无法澄清，虽然发送了报价，但是在较少的技术澄清下，胜率不高</t>
+          <t>与123是同一个客户</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -14947,12 +15005,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>C00008345</t>
+          <t>C00001287</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>C00008345｜司斌｜粮食｜咖啡缓冲斗｜方案V1</t>
+          <t>C00001287｜司斌｜粮食｜越南咖啡仓改造项目｜方案V1</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -14960,26 +15018,26 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>重复开单</t>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>该结未结</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>与咖啡仓方仓同一客户C00008345</t>
+          <t>方案后无回复，可上可不上仍挂进行中</t>
         </is>
       </c>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>与123是同一个客户</t>
+          <t>已合作客户，上次拜访客户想要进行一定的改造，但是发送方案后一直没有任何回复，初步判断改造并非需要解决的大问题，可上可不上</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -14988,12 +15046,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>C00001287</t>
+          <t>C00008398</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>C00001287｜司斌｜粮食｜越南咖啡仓改造项目｜方案V1</t>
+          <t>C00008398｜司斌｜工业｜多米尼加塑料颗粒筒仓项目｜方案V1</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -15008,19 +15066,19 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>方案后无回复，可上可不上仍挂进行中</t>
+          <t>报价后不再沟通，五个月级库龄仍进行中</t>
         </is>
       </c>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>已合作客户，上次拜访客户想要进行一定的改造，但是发送方案后一直没有任何回复，初步判断改造并非需要解决的大问题，可上可不上</t>
+          <t>客户公司是做木屑颗粒生产加工，目前是收集报价阶段，但是价格发送后不再沟通，初步判断价格不具有任何优势</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="7" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -15029,12 +15087,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>C00008398</t>
+          <t>C00008345</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>C00008398｜司斌｜工业｜多米尼加塑料颗粒筒仓项目｜方案V1</t>
+          <t>C00008345｜司斌｜粮食｜Probat国内咖啡仓方仓 |方案V1</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -15042,26 +15100,26 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>该结未结</t>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>重复开单</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>报价后不再沟通，五个月级库龄仍进行中</t>
+          <t>与C00008345咖啡仓同一客户</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>客户公司是做木屑颗粒生产加工，目前是收集报价阶段，但是价格发送后不再沟通，初步判断价格不具有任何优势</t>
+          <t>与123是同一个客户</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -15070,12 +15128,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>C00008345</t>
+          <t>C00009745</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>C00008345｜司斌｜粮食｜Probat国内咖啡仓方仓 |方案V1</t>
+          <t>C00009745｜司斌｜工业｜伊朗水净化项目石灰仓|方案V1</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -15083,40 +15141,40 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>重复开单</t>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>该结未结</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>与C00008345咖啡仓同一客户</t>
+          <t>价格收集，战争结束前不可能上，仍进行中</t>
         </is>
       </c>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>与123是同一个客户</t>
+          <t>对接公司是工程公司，项目所处阶段为价格收集，由于霍尔木兹海峡现状，我认为在战争结束前不可能上</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>司斌</t>
+          <t>王伟乐</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>C00009745</t>
+          <t>C00006274</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>C00009745｜司斌｜工业｜伊朗水净化项目石灰仓|方案V1</t>
+          <t>C00006274| 王伟乐|工业|2026.6.15 |埃及 4*3000t 螺旋咬口仓项目| 方案V1</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -15131,33 +15189,33 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>价格收集，战争结束前不可能上，仍进行中</t>
+          <t>已报价未反馈，仅写可继续跟进</t>
         </is>
       </c>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>对接公司是工程公司，项目所处阶段为价格收集，由于霍尔木兹海峡现状，我认为在战争结束前不可能上</t>
+          <t>已报价，客户未反馈报价的情况，后期可以继续跟进</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="7" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>王伟乐</t>
+          <t>尹韬越</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>C00006274</t>
+          <t>C00009303</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>C00006274| 王伟乐|工业|2026.6.15 |埃及 4*3000t 螺旋咬口仓项目| 方案V1</t>
+          <t>C00009303｜尹韬越｜工业｜乌兹别克斯坦尼什巴什一期储煤场末煤仓项目｜方案V1</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -15172,19 +15230,19 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>已报价未反馈，仅写可继续跟进</t>
+          <t>仅写已报价，超90天无下一步</t>
         </is>
       </c>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>已报价，客户未反馈报价的情况，后期可以继续跟进</t>
+          <t>已报价</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="7" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -15193,12 +15251,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>C00009303</t>
+          <t>C00009297</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>C00009303｜尹韬越｜工业｜乌兹别克斯坦尼什巴什一期储煤场末煤仓项目｜方案V1</t>
+          <t>C00009297｜尹韬越｜粮食｜格鲁吉亚第比利斯3×1000吨玉米仓｜方案V1</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -15213,19 +15271,19 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>仅写已报价，超90天无下一步</t>
+          <t>仅写已报方案，无互动记录</t>
         </is>
       </c>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>已报价</t>
+          <t>已报方案</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="7" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -15234,12 +15292,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>C00009297</t>
+          <t>C00008577</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C00009297｜尹韬越｜粮食｜格鲁吉亚第比利斯3×1000吨玉米仓｜方案V1</t>
+          <t>C00008577 尹韬越哈萨克斯坦4×3500吨粮食项目 方案1</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -15247,40 +15305,40 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>该结未结</t>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>重复开单</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>仅写已报方案，无互动记录</t>
+          <t>与序号156同一征地项目V1/V2</t>
         </is>
       </c>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>已报方案</t>
+          <t>已报方案，目前对方在征地</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="7" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>尹韬越</t>
+          <t>张硕</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>C00008577</t>
+          <t>C00009866</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>C00008577 尹韬越哈萨克斯坦4×3500吨粮食项目 方案1</t>
+          <t>C00009866 | 张硕｜工业｜印尼工程公司PT REXLINE生物质30m³定量料斗项目｜方案V1</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -15288,66 +15346,25 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>重复开单</t>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>该结未结</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>与序号156同一征地项目V1/V2</t>
+          <t>确认清单时多次无视邮件和Whatsapp</t>
         </is>
       </c>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>已报方案，目前对方在征地</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="7" t="n">
-        <v>169</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>张硕</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>C00009866</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>C00009866 | 张硕｜工业｜印尼工程公司PT REXLINE生物质30m³定量料斗项目｜方案V1</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>该结未结</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>确认清单时多次无视邮件和Whatsapp</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
           <t>客户为印尼本地工程公司，在收到我方的方案和设备清单（不含报价），与其沟通对方案图纸和设备清单参数确认时，对方多次无视邮件和Whatsapp信息，初步判定为客户可能已收到合适的报价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21385,24 +21402,28 @@
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>未填</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="22" t="inlineStr">
-        <is>
-          <t>重复开单</t>
+      <c r="J87" s="26" t="inlineStr">
+        <is>
+          <t>规范闭环</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>与序号86重复，状态未填</t>
+          <t>与序号86重复，已暂停</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
       <c r="N87" s="7" t="inlineStr"/>
-      <c r="O87" s="7" t="inlineStr"/>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="P87" s="7" t="inlineStr"/>
       <c r="Q87" s="7" t="inlineStr">
         <is>
@@ -25858,28 +25879,32 @@
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>未填</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I164" s="7" t="inlineStr"/>
-      <c r="J164" s="28" t="inlineStr">
-        <is>
-          <t>未跟进</t>
+      <c r="J164" s="24" t="inlineStr">
+        <is>
+          <t>前期调研</t>
         </is>
       </c>
       <c r="K164" s="7" t="inlineStr">
         <is>
-          <t>陈总发起哈利法港，本人未再跟进，状态未填</t>
-        </is>
-      </c>
-      <c r="L164" s="7" t="inlineStr"/>
+          <t>大EPC需投标并设当地分公司，已标进行中，按前期计</t>
+        </is>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="M164" s="7" t="inlineStr"/>
       <c r="N164" s="7" t="inlineStr"/>
       <c r="O164" s="7" t="inlineStr"/>
       <c r="P164" s="7" t="inlineStr"/>
       <c r="Q164" s="7" t="inlineStr">
         <is>
-          <t>此方案任务为陈总阿联酋哈利法港粮食码头项目发起，工艺工程师出具方案给陈总后，我未再做跟进</t>
+          <t>项目为大EPC，需要投标并在当地成立分公司，后续持续跟进</t>
         </is>
       </c>
     </row>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -27,6 +27,8 @@
     <sheet name="15-多项目客户明细" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="16-进行中阶段" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="17-进行中明细" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="18-丢单原因分类" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="19-丢单原因明细" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
@@ -222,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -356,6 +358,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12173,6 +12184,1406 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>原因分类</t>
+        </is>
+      </c>
+      <c r="B1" s="35" t="inlineStr">
+        <is>
+          <t>条数</t>
+        </is>
+      </c>
+      <c r="C1" s="35" t="inlineStr">
+        <is>
+          <t>占已关丢单</t>
+        </is>
+      </c>
+      <c r="D1" s="35" t="inlineStr">
+        <is>
+          <t>主要是谁</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2" s="29" t="n">
+        <v>0.3833333333333334</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>苗恒 5；马鹏飞 4；王伟乐 4；司斌 3；崔阳 2；尹韬越 2；张硕 2；韩鸿彪 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>崔阳 5；尹韬越 3；陈子凡 2；陈辉 1；王伟超 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡 3；马鹏飞 3；崔阳 2；司斌 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>崔阳 7；苗恒 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>崔阳 3；苗恒 2；陈辉 2；陈子凡 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>已结项-丢单/已结项；不含暂停17条</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>口径：国际部已关掉、判定丢掉的60条。暂停17条多数未填原因，不进本表。尹韬越另有4条暂停也是失联。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:D9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>原因分类</t>
+        </is>
+      </c>
+      <c r="B1" s="49" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C1" s="49" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="D1" s="49" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B2" s="42" t="n">
+        <v>54</v>
+      </c>
+      <c r="C2" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
+        <is>
+          <t>Anush饲料仓，报后一直说在考虑</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
+        <is>
+          <t>500吨水泥仓，报价后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="n">
+        <v>87</v>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>巴拿马粮库，非终端业主后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n">
+        <v>94</v>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>保加利亚消石灰仓，澄清未回</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="n">
+        <v>95</v>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>澳洲农场仓，澄清未回后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="n">
+        <v>96</v>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>智利麦麸料斗，澄清未回后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n">
+        <v>101</v>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>阿尔及利亚干燥，报价后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="n">
+        <v>107</v>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>印尼玉米仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="n">
+        <v>108</v>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>阿联酋玻璃瓶厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="n">
+        <v>110</v>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>也门麸皮仓，更新后无答复</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="n">
+        <v>111</v>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>德国水泥仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="n">
+        <v>115</v>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>马拉维大豆仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="n">
+        <v>128</v>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>越南粉煤灰，报价后不再联系</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="n">
+        <v>129</v>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>马来发放仓，按失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="n">
+        <v>134</v>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>苏丹小麦仓，收集价格后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="n">
+        <v>147</v>
+      </c>
+      <c r="C17" s="42" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>德方仓，报价未反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="n">
+        <v>148</v>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>菲律宾玉米仓，不反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="n">
+        <v>149</v>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>塞舌尔水泥码头，出方案后失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="n">
+        <v>150</v>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>沙特水泥仓，报价无反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n">
+        <v>152</v>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>苏亚克磷矿，报后无回复就结</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="n">
+        <v>155</v>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>乌拉尔斯克转运站失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="n">
+        <v>165</v>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>苏里南糙米线失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>失联/无反馈</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="n">
+        <v>166</v>
+      </c>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr">
+        <is>
+          <t>Sibelco法国失联</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
+        <is>
+          <t>Kim石膏粉仓，价格不及当地</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>益海大豆仓，工厂砍预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="inlineStr">
+        <is>
+          <t>生力SMC平方仓，钢构价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B28" s="42" t="n">
+        <v>43</v>
+      </c>
+      <c r="C28" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr">
+        <is>
+          <t>UZMET石灰仓储，价格过高</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="n">
+        <v>48</v>
+      </c>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>SILOS KZ 30000吨，价格+资料不完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="n">
+        <v>49</v>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>SILOS KZ 1000吨，同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="n">
+        <v>50</v>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>ELFORS谷物码头，价格过高</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="n">
+        <v>57</v>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>粮食储运，价格敏感选其他家</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="n">
+        <v>140</v>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>南非玉米仓，价格超预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="n">
+        <v>157</v>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>哈萨克4×3000粮食，价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="n">
+        <v>159</v>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>哈萨克1×5000粮仓，价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>价格/预算</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="n">
+        <v>160</v>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr">
+        <is>
+          <t>哈萨克70000吨筒仓，价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B37" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>生力临建EPC，土建占比高未参与</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="n">
+        <v>27</v>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>毛里求斯塑料圆仓，体量小放弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="n">
+        <v>28</v>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>印尼碳酸钙仓，体量小放弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B40" s="42" t="n">
+        <v>45</v>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>氧化铝，技术方案不满足</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="n">
+        <v>66</v>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>Powerz旋转阀，我方主动拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="n">
+        <v>97</v>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>科特迪瓦可可豆，风险过大主动停</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="n">
+        <v>98</v>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>污泥刮板机做不了</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B44" s="42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>科特迪瓦航油罐，交期不满足</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>我方做不了/主动放弃</t>
+        </is>
+      </c>
+      <c r="B45" s="42" t="n">
+        <v>122</v>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
+        <is>
+          <t>蒙古沙仓热能存储，工艺做不了</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B46" s="42" t="n">
+        <v>52</v>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
+        <is>
+          <t>Powerz设备采购</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="n">
+        <v>56</v>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>麻类深加工，改选其他工艺</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B48" s="42" t="n">
+        <v>59</v>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="inlineStr">
+        <is>
+          <t>75吨熟石灰仓，当地供应商</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B49" s="42" t="n">
+        <v>61</v>
+      </c>
+      <c r="C49" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>Powerz灰渣气力，当地供应商</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B50" s="42" t="n">
+        <v>63</v>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr">
+        <is>
+          <t>Астон葵花籽仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="n">
+        <v>64</v>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>Powerz旋转给料</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B52" s="42" t="n">
+        <v>71</v>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Powerz输送机</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>选其他供应商/工艺</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="n">
+        <v>116</v>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>印度氧化铝港口，业主选混凝土仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>Kim Jeju污泥仓，客户改计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="inlineStr">
+        <is>
+          <t>Kim welcron污泥仓，客户改计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="n">
+        <v>31</v>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="inlineStr">
+        <is>
+          <t>南美水泥仓，中间商真实性存疑</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B57" s="42" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr">
+        <is>
+          <t>Эннова石灰仓，产能存疑后取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B58" s="42" t="n">
+        <v>67</v>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr">
+        <is>
+          <t>cotes装配仓，客户结束询价</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="n">
+        <v>68</v>
+      </c>
+      <c r="C59" s="42" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>ROSATOM氧化铝仓，业主未立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="n">
+        <v>112</v>
+      </c>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
+        <is>
+          <t>孟加拉玉米仓，需求不实</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="42" t="inlineStr">
+        <is>
+          <t>需求不实/未立项/改计划</t>
+        </is>
+      </c>
+      <c r="B61" s="42" t="n">
+        <v>119</v>
+      </c>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>土耳其石灰石仓，需求不实</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -13,39 +13,42 @@
     <sheet name="2-质量对比" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2b-图数据" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="3-重点项目" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="4-前期调研清单" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5-该结未结与重复" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6-有效在手" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7-全量明细" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8-逐人要点" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="9-客户集中度" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="10-重复客户明细" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="9b-集中度图数据" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="11-打单能力排名" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="12-丢单排名" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="13-丢单明细" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="14-多项目客户排名" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="15-多项目客户明细" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="16-进行中阶段" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="17-进行中明细" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="18-丢单原因分类" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="19-丢单原因明细" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="3b-重点按人" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4-前期调研清单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5-该结未结与重复" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6-有效在手" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7-全量明细" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="8-逐人要点" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="9-客户集中度" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="10-重复客户明细" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="9b-集中度图数据" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="11-打单能力排名" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="12-丢单排名" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="13-丢单明细" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="14-多项目客户排名" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="15-多项目客户明细" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="16-进行中阶段" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="17-进行中明细" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="18-丢单原因分类" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="19-丢单原因明细" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'开场表'!$A$3:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2-质量对比'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2b-图数据'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'3-重点项目'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'4-前期调研清单'!$A$1:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'5-该结未结与重复'!$A$1:$I$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'6-有效在手'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'7-全量明细'!$A$1:$Q$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'8-逐人要点'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'9-客户集中度'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10-重复客户明细'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'9b-集中度图数据'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'11-打单能力排名'!$A$1:$R$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'3-重点项目'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'3b-重点按人'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3b-重点按人'!1:1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'4-前期调研清单'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'5-该结未结与重复'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'6-有效在手'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'7-全量明细'!$A$1:$Q$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'8-逐人要点'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'9-客户集中度'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'10-重复客户明细'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'9b-集中度图数据'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'11-打单能力排名'!$A$1:$R$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +59,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,6 +113,22 @@
     <font>
       <name val="微软雅黑"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -210,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -232,11 +251,25 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -387,6 +420,40 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1552,6 +1619,1009 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8.800000000000001" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>创建人</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>是否重点</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>任务标题</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>判定说明</t>
+        </is>
+      </c>
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>库龄天</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>当前进展</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>大宇土库曼磷矿粉，多次报价比仓型</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>C00009287｜陈辉｜工业｜大宇8套磷矿粉平底仓卸料｜方案V1</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>DY中标则大概率选我方，等分包结果</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>大宇在土库曼化肥厂项目，筒仓的卸料分包给了韩国的一家公司DY，我们给DY报价，仅报一次，技术澄清比较多，DY如果中标大概率优选选我们。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>老客户混拌，利润约束明确</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>报价中，近期可成交</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>报价中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>拜访后更新方案，有望落地</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>20260304 菲律宾生力集团 取料机报价</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>重点：生力取料机，等授标通知</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>等授标通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>C00005424|崔阳|工业|Sibur塑料颗粒的气力输送项目|方案V1</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>实地勘察后技术部出最终方案</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>项目进行实地勘察后，技术部正在出最终方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>C00009055 崔阳|工业|CC7 Europe 化工回收项目 |方案V1</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>资质已交最终业主审查</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>已将我方资质提交最终业主，业主进行资质审查</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes哈萨克斯坦4个矿石仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>cotes矿石仓技术探讨，尚未报价</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>处于技术探讨阶段 还未报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>C00009506  |崔阳|粮食| RUSAGRO农作物种子加工厂项目|方案V1</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>客户提议9月现场考察</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>客户提议九月份进行现场考察</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>C00006514|崔阳|工业|cotes电厂粉煤灰|方案V2</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>cotes粉煤灰仍在技术探讨</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>处于技术探讨阶段 还未报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>曾接受报价，新要求已技术反馈，等农场回复</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>C00009383｜冯乐｜工业｜也门-3×1200m³水泥装配仓项目｜方案V3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>V3多次报价，技术澄清中</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>已进行多次报价，客户对价格比较敏感，目前正在和对方团队进行技术澄清。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>C00009357|韩鸿彪|工业|越南水泥码头+木屑颗粒仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>土地审批+贷款，预计10月底更新</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>项目土地审批和银行贷款阶段，预计10月底会有进一步更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>C00008493|韩鸿彪|工业|也门2x1600T水泥仓扩建项目方案V2</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>V3对比中，计划27年Q1</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>更新方案更新报价V3，业主在对比方案和报价，项目计划是27年Q1上</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>C00008036 韩鸿彪 越南 4x6000T筒仓系统配套输送设备方案 V5</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>包装线更新方案，等决策，有明确分期</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>更新方案，更新报价，等待决策。业主计划先上一条（6台）包装线，第一个筒仓完工后先运行起来</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>C00009474|韩鸿彪|粮食|卢旺达面粉厂3x2500T小麦仓项目|方案V1</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>项目真实，第一版报价阶段</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>面粉厂扩建项目，规模不大，但项目真实，第一版报价阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>C00001420 | 马鹏飞 | 工业 |生力集团100TPH水泥冷却站项目需画电气单线图及理清范围 | 方案V4 |</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>冷却站资料已交，待生力决策层</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>已完成单线图提供，生力水泥冷却站项目，已提交所有所需资料，待生力决策层批复，目前尚未有更新情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>C00009762｜苗恒｜工业｜新加坡4x200m3熟石灰粉不锈钢仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>工程公司，约8月底/9月初反馈</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>跟进中，客户为工程公司，回复8月底或9月初给我们反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>C00009353｜苗恒｜工业｜阿尔及利亚6x2500吨水泥仓+200TPH气力输送项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>已给布置图，9月更多现场信息</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>跟进中，客户给了港口项目布置图，正在沟通方案布局，9月份客户会给更多项目现场信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>重点，确认方案V4后更报价V2</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="7" t="n">
+        <v>113</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>C00009001｜苗恒｜工业｜斯里兰卡1x35000吨熟料仓项目｜方案V2</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>已联系真实业主，但倾向混凝土仓</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>重点项目跟进中，客户找了江苏鹏飞做的整厂规划布置，让我们报混凝土仓报价，准备给客户更新第二版</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>C00009921｜苗恒｜工业｜伊拉克2x10000吨水泥仓项目｜方案V1</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>已报价，客户预计9.2到上海见面</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>已报价，客户预计9.2到上海，希望可以见一面</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>已到决策期，但钢构单价我方拿不到</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>参观工厂，多次方案报价，调图纸等回复</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>咨询公司招投标准备，最新价澄清中</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>C00008577｜尹韬越｜粮食｜哈萨克斯坦4×3500吨粮食项目｜方案V2</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>对方在征地，长周期仍有实质节点</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>已报方案，目前对方在征地</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="7" t="n">
+        <v>168</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>C00009858 | 张硕 | 粮食 | 斯里兰卡汉班托塔Golden Harvest Mill3x1500MT小麦仓扩建项目</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>报价已上呈总裁，每周跟进+当地代理侧面了解</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>业主收到3座仓的正式报价后没有直接给出评论意见，仅回复说以将报价上呈给公司总裁，判断其从多方供应商处比较报价后再做决定，跟进策略对业主按保持每周频次跟进，不表现急切情绪；另从近期开发的当地代理处侧面了解项目进展</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H29"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11202,7 +12272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11719,7 +12789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12453,7 +13523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13999,7 +15069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14192,7 +15262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15037,7 +16107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15389,7 +16459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16630,7 +17700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17039,7 +18109,509 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>方案任务跟进质量分析（2026-01-01 至 2026-08-17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>数据截止</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17；填报版本 0830（崔阳已补进展；2条空白状态已补：韩鸿彪暂停、张硕进行中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>样本</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>国际业务部方案任务 165 条（已剔除国内业务部郭朝伟 4 条）；崔阳 38 条已补进展；状态已全部标注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>口径说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>提报任务总数</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>管家中该业务员累计创建的方案任务条数，同一客户多条分别计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>已结项或暂停</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>状态为已结项-签约 / 已结项-丢单 / 已结项 / 暂停 / 项目暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>前期调研</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>进展明确为规划、只要预算、了解价格、收集报价、找钱、非最终业主探价等，尚未进入实质商务推进</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>前期调研客户数</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>按客户键去重（C编码；陈子凡生力/SMC/Manila01、MAK 已并户）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>客户数（集中度）</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>C编码去重；无编码各计1。业务确认：陈子凡未标编码的菲律宾生力集团/SMC/Manila01 并为一户，标题含MAK的并入蒙古MAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>标题标注「重点项目」；另补录业务确认的2条：菲律宾生力取料机、MAK 2×150吨小仓（已签约）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>有效在手</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>进行中且有真实互动或明确下一步（拜访、更新方案、授标、征地、约见面、技术澄清），排除纯预算和该结未结</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>已报价/已出方案后被动等回复，尚有一线希望但跟进动作弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>该结未结</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>失联、无反馈、希望不大、可上可不上、客户只要厂家等，仍挂「进行中」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>重复开单</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>同一客户拆多条任务且未合并，或明显重复任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>有效项目</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>已签约 + 有效在手。这是「提报很多但有效项目不足」的核心观察口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>闭环率</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>已结项或暂停 / 提报总数。敢结项是纪律，不代表能成交</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>全样本结构</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>条数</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.5272727272727272</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>已结项-丢单/其他</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.103030303030303</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>已结项-签约</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.006060606060606061</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>未填</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1"/>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>165 条跟进质量结构（国际业务部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>质量标签</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>条数</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>规范闭环（该关已关）</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>有效在手</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.1696969696969697</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>前期调研</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>该结未结+重复开单</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.1272727272727273</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>未跟进（张硕代填）</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1"/>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>核心结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>有效项目</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>29 条（1 签约 + 28 有效在手），占全部 17.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>前期调研</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>18 条 / 17 个客户，占全部 10.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>该关未关</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>21 条，直接虚增进行中盘子</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>失联/未反馈</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>23 条已按失联或未反馈记录（含部分暂停备注）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>签约</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>165 条里可确认签约 1 条（陈子凡 / 蒙古MAK 2×150 吨）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>崔阳补录</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>38 条已填；关账勤但有效在手少，Powerz/Эннова/cotes 重复开单多；75万吨重点进展仍空</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="53" t="inlineStr">
+        <is>
+          <t>3-重点项目</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15 条重点明细，按开场表组别、业务员排（不再按序号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="53" t="inlineStr">
+        <is>
+          <t>3b-重点按人</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>12 人汇总（与开场表同一顺序）；未标重点的 4 人为 0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17699,485 +19271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>方案任务跟进质量分析（2026-01-01 至 2026-08-17）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>数据截止</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17；填报版本 0830（崔阳已补进展；2条空白状态已补：韩鸿彪暂停、张硕进行中）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>样本</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>国际业务部方案任务 165 条（已剔除国内业务部郭朝伟 4 条）；崔阳 38 条已补进展；状态已全部标注</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1"/>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>口径说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>提报任务总数</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>管家中该业务员累计创建的方案任务条数，同一客户多条分别计</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>已结项或暂停</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>状态为已结项-签约 / 已结项-丢单 / 已结项 / 暂停 / 项目暂停</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>前期调研</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>进展明确为规划、只要预算、了解价格、收集报价、找钱、非最终业主探价等，尚未进入实质商务推进</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>前期调研客户数</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>按客户键去重（C编码；陈子凡生力/SMC/Manila01、MAK 已并户）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>客户数（集中度）</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>C编码去重；无编码各计1。业务确认：陈子凡未标编码的菲律宾生力集团/SMC/Manila01 并为一户，标题含MAK的并入蒙古MAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>重点项目</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>标题标注「重点项目」；另补录业务确认的2条：菲律宾生力取料机、MAK 2×150吨小仓（已签约）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>有效在手</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>进行中且有真实互动或明确下一步（拜访、更新方案、授标、征地、约见面、技术澄清），排除纯预算和该结未结</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>已报价/已出方案后被动等回复，尚有一线希望但跟进动作弱</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>该结未结</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>失联、无反馈、希望不大、可上可不上、客户只要厂家等，仍挂「进行中」</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>重复开单</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>同一客户拆多条任务且未合并，或明显重复任务</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>有效项目</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>已签约 + 有效在手。这是「提报很多但有效项目不足」的核心观察口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>闭环率</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>已结项或暂停 / 提报总数。敢结项是纪律，不代表能成交</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>全样本结构</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>条数</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0.5272727272727272</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>已结项-丢单/其他</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>暂停</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>0.103030303030303</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>已结项-签约</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>0.006060606060606061</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>未填</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1"/>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>165 条跟进质量结构（国际业务部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>质量标签</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>条数</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>规范闭环（该关已关）</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>0.4727272727272727</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>有效在手</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>0.1696969696969697</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>前期调研</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>0.1090909090909091</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>0.1212121212121212</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>该结未结+重复开单</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>0.1272727272727273</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>未跟进（张硕代填）</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1"/>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>核心结论</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>有效项目</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>29 条（1 签约 + 28 有效在手），占全部 17.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>前期调研</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>18 条 / 17 个客户，占全部 10.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>该关未关</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>21 条，直接虚增进行中盘子</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>失联/未反馈</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>23 条已按失联或未反馈记录（含部分暂停备注）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>签约</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>165 条里可确认签约 1 条（陈子凡 / 蒙古MAK 2×150 吨）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>崔阳补录</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>38 条已填；关账勤但有效在手少，Powerz/Эннова/cotes 重复开单多；75万吨重点进展仍空</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18527,7 +19621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21190,7 +22284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21350,7 +22444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24657,610 +25751,1225 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="11.5" customWidth="1" min="4" max="4"/>
-    <col width="8.800000000000001" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>创建人</t>
-        </is>
-      </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="E1" s="54" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" s="54" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="G1" s="54" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+      <c r="H1" s="54" t="inlineStr">
+        <is>
+          <t>跟进质量</t>
+        </is>
+      </c>
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>任务标题</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="E1" s="16" t="inlineStr">
-        <is>
-          <t>跟进质量</t>
-        </is>
-      </c>
-      <c r="F1" s="16" t="inlineStr">
-        <is>
-          <t>判定说明</t>
-        </is>
-      </c>
-      <c r="G1" s="16" t="inlineStr">
-        <is>
-          <t>库龄天</t>
-        </is>
-      </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>当前进展</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="7" t="n">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C2" s="55" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" s="56" t="inlineStr">
+        <is>
+          <t>蒙古 MAK 2×150 吨小仓</t>
+        </is>
+      </c>
+      <c r="E2" s="55" t="inlineStr">
+        <is>
+          <t>已结项-签约</t>
+        </is>
+      </c>
+      <c r="F2" s="57" t="inlineStr">
+        <is>
+          <t>已签约</t>
+        </is>
+      </c>
+      <c r="G2" s="56" t="inlineStr">
+        <is>
+          <t>样本内唯一签约</t>
+        </is>
+      </c>
+      <c r="H2" s="55" t="inlineStr">
+        <is>
+          <t>规范闭环</t>
+        </is>
+      </c>
+      <c r="I2" s="56" t="inlineStr">
+        <is>
+          <t>20260302 C00007247 MAK 陈子凡 2x150吨小仓方案 报价</t>
+        </is>
+      </c>
+      <c r="J2" s="56" t="inlineStr">
+        <is>
+          <t>已成交</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C3" s="55" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>蒙古 MAK 气力输送更新</t>
+        </is>
+      </c>
+      <c r="E3" s="55" t="inlineStr">
+        <is>
+          <t>进行中（近期可成交）</t>
+        </is>
+      </c>
+      <c r="F3" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G3" s="56" t="inlineStr">
+        <is>
+          <t>最接近成单的在手重点</t>
+        </is>
+      </c>
+      <c r="H3" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I3" s="56" t="inlineStr">
+        <is>
+          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J3" s="56" t="inlineStr">
+        <is>
+          <t>报价中</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>29</v>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>菲律宾生力取料机</t>
+        </is>
+      </c>
+      <c r="E4" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F4" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G4" s="56" t="inlineStr">
+        <is>
+          <t>等授标</t>
+        </is>
+      </c>
+      <c r="H4" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I4" s="56" t="inlineStr">
+        <is>
+          <t>20260304 菲律宾生力集团 取料机报价</t>
+        </is>
+      </c>
+      <c r="J4" s="56" t="inlineStr">
+        <is>
+          <t>等授标通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>MONCEMENT 3×2000 水泥中转</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F5" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G5" s="56" t="inlineStr">
+        <is>
+          <t>拜访后更新方案</t>
+        </is>
+      </c>
+      <c r="H5" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I5" s="56" t="inlineStr">
+        <is>
+          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J5" s="56" t="inlineStr">
+        <is>
+          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>124</v>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>斯里兰卡 30×3500 稻谷</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F6" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G6" s="56" t="inlineStr">
+        <is>
+          <t>已到决策期，钢构单价拿不到</t>
+        </is>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I6" s="56" t="inlineStr">
+        <is>
+          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="J6" s="56" t="inlineStr">
+        <is>
+          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="n">
+        <v>141</v>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>哥斯达黎加咖啡仓</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F7" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G7" s="56" t="inlineStr">
+        <is>
+          <t>到过工厂，多次改图</t>
+        </is>
+      </c>
+      <c r="H7" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I7" s="56" t="inlineStr">
+        <is>
+          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J7" s="56" t="inlineStr">
+        <is>
+          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>146</v>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>新加坡裕廊港 12×10000</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F8" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G8" s="56" t="inlineStr">
+        <is>
+          <t>最新价澄清中</t>
+        </is>
+      </c>
+      <c r="H8" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I8" s="56" t="inlineStr">
+        <is>
+          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="J8" s="56" t="inlineStr">
+        <is>
+          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="n">
+        <v>151</v>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>摩洛哥 CIMAF 1×700</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="G9" s="56" t="inlineStr">
+        <is>
+          <t>已报价、库龄偏长</t>
+        </is>
+      </c>
+      <c r="H9" s="58" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
+        </is>
+      </c>
+      <c r="I9" s="56" t="inlineStr">
+        <is>
+          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
+        </is>
+      </c>
+      <c r="J9" s="56" t="inlineStr">
+        <is>
+          <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>韩国大宇 3 万吨磷矿粉</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F10" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G10" s="56" t="inlineStr">
+        <is>
+          <t>多次报价，比仓型</t>
+        </is>
+      </c>
+      <c r="H10" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I10" s="56" t="inlineStr">
+        <is>
+          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J10" s="56" t="inlineStr">
+        <is>
+          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>陈辉</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="C11" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>Lanwa 水泥混拌</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="F11" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G11" s="56" t="inlineStr">
+        <is>
+          <t>老客户，利润被压</t>
+        </is>
+      </c>
+      <c r="H11" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>大宇土库曼磷矿粉，多次报价比仓型</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="7" t="n">
+      <c r="I11" s="56" t="inlineStr">
+        <is>
+          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J11" s="56" t="inlineStr">
+        <is>
+          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="n">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>塞拉利昂 2×3 万吨 clinker</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="F12" s="58" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="G12" s="56" t="inlineStr">
+        <is>
+          <t>已拜访，缺资金</t>
+        </is>
+      </c>
+      <c r="H12" s="58" t="inlineStr">
+        <is>
+          <t>前期调研</t>
+        </is>
+      </c>
+      <c r="I12" s="56" t="inlineStr">
         <is>
           <t>C00002715｜陈辉｜工业｜塞拉利昂2个3万吨clinker项目｜方案V1 | 重点项目</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="J12" s="56" t="inlineStr">
+        <is>
+          <t>已去拜访客户，客户想法很多，缺资金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="n">
+        <v>72</v>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>坦桑 2×4500 小麦仓</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>前期调研</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>已拜访但缺资金，有效性弱</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>已去拜访客户，客户想法很多，缺资金。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F13" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G13" s="56" t="inlineStr">
+        <is>
+          <t>曾接受报价，新要求已反馈</t>
+        </is>
+      </c>
+      <c r="H13" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
+        </is>
+      </c>
+      <c r="I13" s="56" t="inlineStr">
+        <is>
+          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J13" s="56" t="inlineStr">
+        <is>
+          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="n">
+        <v>109</v>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>墨西哥大型粮仓</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="F14" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="G14" s="56" t="inlineStr">
+        <is>
+          <t>V4 后更报价 V2</t>
+        </is>
+      </c>
+      <c r="H14" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>老客户混拌，利润约束明确</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="I14" s="56" t="inlineStr">
+        <is>
+          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J14" s="56" t="inlineStr">
+        <is>
+          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="n">
+        <v>114</v>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>孟加拉 2×3000 稻谷</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="F15" s="58" t="inlineStr">
+        <is>
+          <t>已暂停</t>
+        </is>
+      </c>
+      <c r="G15" s="56" t="inlineStr">
+        <is>
+          <t>重点已暂停，处理正确</t>
+        </is>
+      </c>
+      <c r="H15" s="55" t="inlineStr">
+        <is>
+          <t>规范闭环</t>
+        </is>
+      </c>
+      <c r="I15" s="56" t="inlineStr">
+        <is>
+          <t>C00008988｜苗恒｜粮食｜孟加拉2x3000吨稻谷仓项目｜方案V3 | 重点项目</t>
+        </is>
+      </c>
+      <c r="J15" s="56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="n">
+        <v>58</v>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t>75 万吨小麦深加工</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>报价中，近期可成交</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>报价中</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>拜访后更新方案，有望落地</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>20260304 菲律宾生力集团 取料机报价</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>重点：生力取料机，等授标通知</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>等授标通知</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>20260302 C00007247 MAK 陈子凡 2x150吨小仓方案 报价</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>已结项-签约</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>规范闭环</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>重点：MAK 2×150吨小仓，已成交，样本内唯一签约</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>已成交</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="F16" s="58" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="G16" s="56" t="inlineStr">
+        <is>
+          <t>只写「进行中 重点任务」，无下一步</t>
+        </is>
+      </c>
+      <c r="H16" s="58" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
+        </is>
+      </c>
+      <c r="I16" s="56" t="inlineStr">
         <is>
           <t>C00009094|崔阳|粮食|75万吨小麦深加工项目|方案V1|重点项目</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>重点项目，进展只写「进行中 重点任务」</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="J16" s="56" t="inlineStr">
         <is>
           <t>进行中 重点任务</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>冯乐</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>曾接受报价，新要求已技术反馈，等农场回复</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>重点，确认方案V4后更报价V2</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>114</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>C00008988｜苗恒｜粮食｜孟加拉2x3000吨稻谷仓项目｜方案V3 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>暂停</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>规范闭环</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>重点项目已暂停</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>124</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>司斌</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>已到决策期，但钢构单价我方拿不到</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>141</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>王伟超</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>参观工厂，多次方案报价，调图纸等回复</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>146</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>王伟乐</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>咨询公司招投标准备，最新价澄清中</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>151</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>王伟乐</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>老客户总部项目，已报价继续跟，库龄偏长</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
+    <row r="18">
+      <c r="A18" s="59" t="inlineStr">
+        <is>
+          <t>15 = 已签约 1 + 进行中有效 10 + 该降级/已暂停 4（CIMAF 浅层、塞拉利昂前期、孟加拉暂停、崔阳 75 万吨浅层）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:J16"/>
+  <mergeCells count="1">
+    <mergeCell ref="A18:J18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="C1" s="54" t="inlineStr">
+        <is>
+          <t>重点</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="inlineStr">
+        <is>
+          <t>已签约</t>
+        </is>
+      </c>
+      <c r="E1" s="54" t="inlineStr">
+        <is>
+          <t>进行中有效</t>
+        </is>
+      </c>
+      <c r="F1" s="54" t="inlineStr">
+        <is>
+          <t>该降级 / 已暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B2" s="60" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C2" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="C3" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="55" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="58" t="inlineStr">
+        <is>
+          <t>1 浅层</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C8" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="58" t="inlineStr">
+        <is>
+          <t>1 前期</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="58" t="inlineStr">
+        <is>
+          <t>1 已暂停</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>崔阳</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="58" t="inlineStr">
+        <is>
+          <t>1 浅层</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="n"/>
+      <c r="C14" s="63" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="63" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="64" t="inlineStr">
+        <is>
+          <t>陈子凡 4 条全有效（含唯一签约）。该降级 4 条：王伟乐 CIMAF 浅层、陈辉塞拉利昂前期、苗恒孟加拉已暂停、崔阳 75 万吨浅层。韩鸿彪未标重点，但有效项目率全员最高。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A16:F16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25977,7 +27686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26909,1007 +28618,4 @@
   <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8.800000000000001" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B1" s="23" t="inlineStr">
-        <is>
-          <t>创建人</t>
-        </is>
-      </c>
-      <c r="C1" s="23" t="inlineStr">
-        <is>
-          <t>是否重点</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
-        <is>
-          <t>任务标题</t>
-        </is>
-      </c>
-      <c r="E1" s="23" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="F1" s="23" t="inlineStr">
-        <is>
-          <t>判定说明</t>
-        </is>
-      </c>
-      <c r="G1" s="23" t="inlineStr">
-        <is>
-          <t>库龄天</t>
-        </is>
-      </c>
-      <c r="H1" s="23" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>大宇土库曼磷矿粉，多次报价比仓型</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>C00009287｜陈辉｜工业｜大宇8套磷矿粉平底仓卸料｜方案V1</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>DY中标则大概率选我方，等分包结果</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>大宇在土库曼化肥厂项目，筒仓的卸料分包给了韩国的一家公司DY，我们给DY报价，仅报一次，技术澄清比较多，DY如果中标大概率优选选我们。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>老客户混拌，利润约束明确</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>报价中，近期可成交</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>报价中</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>拜访后更新方案，有望落地</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>20260304 菲律宾生力集团 取料机报价</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>重点：生力取料机，等授标通知</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>等授标通知</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>C00005424|崔阳|工业|Sibur塑料颗粒的气力输送项目|方案V1</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>实地勘察后技术部出最终方案</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>项目进行实地勘察后，技术部正在出最终方案</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>C00009055 崔阳|工业|CC7 Europe 化工回收项目 |方案V1</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>资质已交最终业主审查</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>已将我方资质提交最终业主，业主进行资质审查</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>C00006514|崔阳|工业|cotes哈萨克斯坦4个矿石仓项目|方案V1</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>cotes矿石仓技术探讨，尚未报价</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>处于技术探讨阶段 还未报价</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>C00009506  |崔阳|粮食| RUSAGRO农作物种子加工厂项目|方案V1</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>客户提议9月现场考察</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>客户提议九月份进行现场考察</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>C00006514|崔阳|工业|cotes电厂粉煤灰|方案V2</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>cotes粉煤灰仍在技术探讨</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>处于技术探讨阶段 还未报价</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>冯乐</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>曾接受报价，新要求已技术反馈，等农场回复</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>冯乐</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>C00009383｜冯乐｜工业｜也门-3×1200m³水泥装配仓项目｜方案V3</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>V3多次报价，技术澄清中</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>已进行多次报价，客户对价格比较敏感，目前正在和对方团队进行技术澄清。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>韩鸿彪</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>C00009357|韩鸿彪|工业|越南水泥码头+木屑颗粒仓项目|方案V1</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>土地审批+贷款，预计10月底更新</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>项目土地审批和银行贷款阶段，预计10月底会有进一步更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>韩鸿彪</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>C00008493|韩鸿彪|工业|也门2x1600T水泥仓扩建项目方案V2</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>V3对比中，计划27年Q1</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>更新方案更新报价V3，业主在对比方案和报价，项目计划是27年Q1上</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>韩鸿彪</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>C00008036 韩鸿彪 越南 4x6000T筒仓系统配套输送设备方案 V5</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>包装线更新方案，等决策，有明确分期</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>更新方案，更新报价，等待决策。业主计划先上一条（6台）包装线，第一个筒仓完工后先运行起来</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>韩鸿彪</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>C00009474|韩鸿彪|粮食|卢旺达面粉厂3x2500T小麦仓项目|方案V1</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>项目真实，第一版报价阶段</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>面粉厂扩建项目，规模不大，但项目真实，第一版报价阶段</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>马鹏飞</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>C00001420 | 马鹏飞 | 工业 |生力集团100TPH水泥冷却站项目需画电气单线图及理清范围 | 方案V4 |</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>冷却站资料已交，待生力决策层</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>已完成单线图提供，生力水泥冷却站项目，已提交所有所需资料，待生力决策层批复，目前尚未有更新情况</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>105</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>C00009762｜苗恒｜工业｜新加坡4x200m3熟石灰粉不锈钢仓项目｜方案V1</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>工程公司，约8月底/9月初反馈</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>跟进中，客户为工程公司，回复8月底或9月初给我们反馈</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>C00009353｜苗恒｜工业｜阿尔及利亚6x2500吨水泥仓+200TPH气力输送项目｜方案V1</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>已给布置图，9月更多现场信息</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>跟进中，客户给了港口项目布置图，正在沟通方案布局，9月份客户会给更多项目现场信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>重点，确认方案V4后更报价V2</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="7" t="n">
-        <v>113</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>C00009001｜苗恒｜工业｜斯里兰卡1x35000吨熟料仓项目｜方案V2</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>已联系真实业主，但倾向混凝土仓</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>重点项目跟进中，客户找了江苏鹏飞做的整厂规划布置，让我们报混凝土仓报价，准备给客户更新第二版</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>C00009921｜苗恒｜工业｜伊拉克2x10000吨水泥仓项目｜方案V1</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>已报价，客户预计9.2到上海见面</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>已报价，客户预计9.2到上海，希望可以见一面</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="7" t="n">
-        <v>124</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>司斌</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>已到决策期，但钢构单价我方拿不到</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>141</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>王伟超</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>参观工厂，多次方案报价，调图纸等回复</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="7" t="n">
-        <v>146</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>王伟乐</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>咨询公司招投标准备，最新价澄清中</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>156</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>尹韬越</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>C00008577｜尹韬越｜粮食｜哈萨克斯坦4×3500吨粮食项目｜方案V2</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>对方在征地，长周期仍有实质节点</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>已报方案，目前对方在征地</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="7" t="n">
-        <v>168</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>张硕</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>C00009858 | 张硕 | 粮食 | 斯里兰卡汉班托塔Golden Harvest Mill3x1500MT小麦仓扩建项目</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>报价已上呈总裁，每周跟进+当地代理侧面了解</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>业主收到3座仓的正式报价后没有直接给出评论意见，仅回复说以将报价上呈给公司总裁，判断其从多方供应商处比较报价后再做决定，跟进策略对业主按保持每周频次跟进，不表现急切情绪；另从近期开发的当地代理处侧面了解项目进展</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H29"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -45,9 +45,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'6-有效在手'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'7-全量明细'!$A$1:$Q$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'8-逐人要点'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'9-客户集中度'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'9-客户集中度'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'10-重复客户明细'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'9b-集中度图数据'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'11-打单能力排名'!$A$1:$R$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -131,7 +130,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -228,6 +227,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -269,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -454,6 +458,36 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12793,732 +12827,705 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10.5" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10.5" customWidth="1" min="5" max="5"/>
-    <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="12.2" customWidth="1" min="7" max="7"/>
-    <col width="34.8" customWidth="1" min="8" max="8"/>
-    <col width="13.9" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="13.2" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
     <col width="17.6" customWidth="1" min="13" max="13"/>
     <col width="17.6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>提报任务数</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>客户数</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>条人均</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>有编码任务</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>无编码任务</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>最大客户编码</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>最大客户简称</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>最大客户任务数</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>最大客户占本人任务</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>前3客户任务数</t>
-        </is>
-      </c>
-      <c r="L1" s="6" t="inlineStr">
-        <is>
-          <t>前3客户占比</t>
-        </is>
-      </c>
-      <c r="M1" s="6" t="inlineStr">
-        <is>
-          <t>重复客户数_至少2条</t>
-        </is>
-      </c>
-      <c r="N1" s="6" t="inlineStr">
-        <is>
-          <t>重复客户数_至少3条</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="E1" s="54" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="F1" s="54" t="inlineStr">
+        <is>
+          <t>条/客</t>
+        </is>
+      </c>
+      <c r="G1" s="54" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="H1" s="54" t="inlineStr">
+        <is>
+          <t>最大客户</t>
+        </is>
+      </c>
+      <c r="I1" s="54" t="inlineStr">
+        <is>
+          <t>最大占本人</t>
+        </is>
+      </c>
+      <c r="J1" s="54" t="inlineStr">
+        <is>
+          <t>前三大占比</t>
+        </is>
+      </c>
+      <c r="K1" s="54" t="inlineStr">
+        <is>
+          <t>≥2条客户</t>
+        </is>
+      </c>
+      <c r="L1" s="54" t="inlineStr">
+        <is>
+          <t>怎么读</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="D2" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="E2" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="F2" s="65" t="n">
         <v>1.73</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="66" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
+      <c r="H2" s="56" t="inlineStr">
+        <is>
+          <t>Powerz ×7</t>
+        </is>
+      </c>
+      <c r="I2" s="67" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J2" s="67" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K2" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" s="56" t="inlineStr">
+        <is>
+          <t>前三户 16 条，集中在死单</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="C3" s="60" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="D3" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="68" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G3" s="57" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="H3" s="56" t="inlineStr">
+        <is>
+          <t>QNC ×4</t>
+        </is>
+      </c>
+      <c r="I3" s="67" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J3" s="67" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K3" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="56" t="inlineStr">
+        <is>
+          <t>占本人 36%，健康但单一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="68" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G4" s="57" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+      <c r="H4" s="56" t="inlineStr">
+        <is>
+          <t>生力 ×4</t>
+        </is>
+      </c>
+      <c r="I4" s="67" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="67" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K4" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="56" t="inlineStr">
+        <is>
+          <t>生力 + MAK，含唯一签约</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="55" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" s="69" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G5" s="70" t="inlineStr">
+        <is>
+          <t>渠道多询</t>
+        </is>
+      </c>
+      <c r="H5" s="56" t="inlineStr">
+        <is>
+          <t>Kim ×4</t>
+        </is>
+      </c>
+      <c r="I5" s="67" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J5" s="67" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K5" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="56" t="inlineStr">
+        <is>
+          <t>一个渠道四条询价，关了 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>五组</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" s="71" t="inlineStr">
+        <is>
+          <t>样本小</t>
+        </is>
+      </c>
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>C00009344 ×2</t>
+        </is>
+      </c>
+      <c r="I6" s="67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J6" s="67" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K6" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="56" t="inlineStr">
+        <is>
+          <t>同一编码跨土库曼 / 新疆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="72" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G7" s="66" t="inlineStr">
+        <is>
+          <t>局部拆单</t>
+        </is>
+      </c>
+      <c r="H7" s="56" t="inlineStr">
+        <is>
+          <t>咖啡仓 ×3</t>
+        </is>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J7" s="67" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K7" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="56" t="inlineStr">
+        <is>
+          <t>面上不集中，三条全挂着</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>俄语组</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G8" s="62" t="inlineStr">
+        <is>
+          <t>接近一人一客</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>征地 V1/V2 ×2</t>
+        </is>
+      </c>
+      <c r="I8" s="67" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J8" s="67" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K8" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="56" t="inlineStr">
+        <is>
+          <t>只多拆了征地</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>六组</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>苗恒</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="55" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="62" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H9" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="67" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J9" s="67" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>C00006570</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>工业 Powerz螺旋输送机采购</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" s="29" t="n">
-        <v>0.1842105263157895</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="L2" s="29" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>苗恒</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D3" s="17" t="n">
+      <c r="L9" s="56" t="inlineStr">
+        <is>
+          <t>铺得最开，留下 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="G10" s="62" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="67" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J10" s="67" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="56" t="inlineStr">
+        <is>
+          <t>11 条死 7 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>三组</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="62" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H11" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="67" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J11" s="67" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K11" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="56" t="inlineStr">
+        <is>
+          <t>一半丢掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>一组</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="62" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H12" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" s="67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="56" t="inlineStr">
+        <is>
+          <t>样本小；斯里兰卡跟得细</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>二组</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="62" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+      <c r="H13" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" s="67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K13" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="56" t="inlineStr">
+        <is>
+          <t>样本小；哥斯达黎加到过工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="63" t="inlineStr"/>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="n"/>
+      <c r="D14" s="63" t="n">
+        <v>165</v>
+      </c>
+      <c r="E14" s="63" t="n">
+        <v>134</v>
+      </c>
+      <c r="F14" s="74" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G14" s="63" t="n"/>
+      <c r="H14" s="63" t="n"/>
+      <c r="I14" s="63" t="n"/>
+      <c r="J14" s="63" t="n"/>
+      <c r="K14" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>C00009786</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>粮食 斯里兰卡10x2000吨稻谷仓项目</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="29" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="29" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>司斌</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>C00008345</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>粮食 咖啡仓方仓</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="29" t="n">
-        <v>0.1764705882352941</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" s="29" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>C00001305</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>工业 韩国Jeju-四套污泥仓</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" s="29" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>ALIAS-SMC</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>菲律宾生力集团</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" s="29" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>尹韬越</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>C00008577</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>粮食 哈萨克斯坦4×3500吨粮食项目</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="29" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="29" t="n">
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>韩鸿彪</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>C00008036</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>/ /越南QNC料场项目/</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="29" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" s="29" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>马鹏飞</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>C00009797</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>工业 新加坡波纹钢板储水罐</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="29" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>王伟乐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>C00006335</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>粮食 苏丹农业银行粮储项目 V1</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="29" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>冯乐</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>C00009344</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>工业 土库曼斯坦火车装载料斗项目</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="29" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>张硕</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>20260121 苏里南糙米碾白线配套筒仓项目</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>王伟超</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>C00009593</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>粮食 乌干达生咖啡豆筒仓项目</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>合计（客户不跨人去重）</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>165</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>134</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>141</v>
-      </c>
-      <c r="F14" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="G14" s="30" t="inlineStr"/>
-      <c r="H14" s="30" t="inlineStr"/>
-      <c r="I14" s="30" t="inlineStr"/>
-      <c r="J14" s="30" t="inlineStr"/>
-      <c r="K14" s="30" t="inlineStr"/>
-      <c r="L14" s="30" t="inlineStr"/>
-      <c r="M14" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="N14" s="30" t="n">
-        <v>7</v>
+      <c r="L14" s="63" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="64" t="inlineStr">
+        <is>
+          <t>崔阳最高是拆单；韩鸿彪、陈子凡是基本盘。底下五个 1.00 是一人一客、铺新客户。冯乐/张硕/王伟超样本小于 8。</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:L13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A16:L16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -15075,189 +15082,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10.5" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>业务员</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
+        <is>
+          <t>条/客</t>
+        </is>
+      </c>
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>提报任务数</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>客户数</t>
         </is>
       </c>
+      <c r="F1" s="54" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>崔阳</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="C2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D2" t="n">
         <v>38</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="E2" t="n">
         <v>22</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>拆单注水</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>韩鸿彪</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>陈子凡</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>基本盘深挖</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>陈辉</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>渠道多询</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>冯乐</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>样本小</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>司斌</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>局部拆单</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>尹韬越</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>接近一人一客</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>苗恒</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="E9" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>司斌</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>陈辉</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>陈子凡</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>尹韬越</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>韩鸿彪</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>马鹏飞</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王伟乐</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>马鹏飞</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>张硕</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>王伟乐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>冯乐</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="7" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>王伟超</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>张硕</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
+      <c r="E13" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>王伟超</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>5</v>
-      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>广撒网</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D14" t="n">
+        <v>165</v>
+      </c>
+      <c r="E14" t="n">
+        <v>134</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
+++ b/docs/reports/briefings/business/2026-08-17-方案任务跟进质量分析.xlsx
@@ -37,9 +37,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1-业务员总表'!$A$1:$X$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2-质量对比'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2b-图数据'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'3-重点项目'!$A$1:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'3b-重点按人'!$A$1:$F$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3b-重点按人'!1:1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'3-重点项目'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'3b-重点按人'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'4-前期调研清单'!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'5-该结未结与重复'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'6-有效在手'!$A$1:$H$29</definedName>
@@ -273,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -489,6 +488,7 @@
     <xf numFmtId="2" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4487,11 +4487,7 @@
           <t>已结项-签约</t>
         </is>
       </c>
-      <c r="I31" s="25" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I31" s="25" t="n"/>
       <c r="J31" s="26" t="inlineStr">
         <is>
           <t>规范闭环</t>
@@ -4499,7 +4495,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>重点：MAK 2×150吨小仓，已成交，样本内唯一签约</t>
+          <t>已成交，样本内唯一签约；标题未标重点，不进重点清单</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr"/>
@@ -12542,7 +12538,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>3</v>
@@ -15414,7 +15410,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>合计</t>
@@ -15429,7 +15424,6 @@
       <c r="E14" t="n">
         <v>134</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15818,10 +15812,10 @@
         <v>0.1875</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" s="31" t="inlineStr"/>
       <c r="O6" s="31" t="n">
@@ -16265,6 +16259,8 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -18404,7 +18400,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>标题标注「重点项目」；另补录业务确认的2条：菲律宾生力取料机、MAK 2×150吨小仓（已签约）</t>
+          <t>任务标题含「重点项目」13 条 + 补录菲律宾生力取料机 1 条，共 14。MAK 2×150 已签约但标题未标，不进清单。郭朝伟模拟粮仓已剔除。</t>
         </is>
       </c>
     </row>
@@ -18753,6 +18749,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
         <is>
@@ -18761,7 +18758,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15 条重点明细，按开场表组别、业务员排（不再按序号）</t>
+          <t>14 条重点明细，按开场表组别、业务员排；来源列区分标题标注 / 补录</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18770,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12 人汇总（与开场表同一顺序）；未标重点的 4 人为 0</t>
+          <t>12 人汇总（与开场表同一顺序）；未标重点的 4 人为 0。合计 14。</t>
         </is>
       </c>
     </row>
@@ -24348,10 +24345,10 @@
         <v>2</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>3</v>
@@ -24940,10 +24937,10 @@
         <v>17</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>28</v>
@@ -25257,10 +25254,10 @@
         <v>0.5</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>0</v>
@@ -25925,21 +25922,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -25965,30 +25963,35 @@
       </c>
       <c r="E1" s="54" t="inlineStr">
         <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="F1" s="54" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="54" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>判断</t>
         </is>
       </c>
-      <c r="G1" s="54" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>一句话</t>
         </is>
       </c>
-      <c r="H1" s="54" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>跟进质量</t>
         </is>
       </c>
-      <c r="I1" s="54" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>任务标题</t>
         </is>
       </c>
-      <c r="J1" s="54" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>当前进展</t>
         </is>
@@ -26006,41 +26009,46 @@
         </is>
       </c>
       <c r="C2" s="55" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D2" s="56" t="inlineStr">
         <is>
-          <t>蒙古 MAK 2×150 吨小仓</t>
+          <t>蒙古 MAK 气力输送更新</t>
         </is>
       </c>
       <c r="E2" s="55" t="inlineStr">
         <is>
-          <t>已结项-签约</t>
-        </is>
-      </c>
-      <c r="F2" s="57" t="inlineStr">
-        <is>
-          <t>已签约</t>
-        </is>
-      </c>
-      <c r="G2" s="56" t="inlineStr">
-        <is>
-          <t>样本内唯一签约</t>
-        </is>
-      </c>
-      <c r="H2" s="55" t="inlineStr">
-        <is>
-          <t>规范闭环</t>
-        </is>
-      </c>
-      <c r="I2" s="56" t="inlineStr">
-        <is>
-          <t>20260302 C00007247 MAK 陈子凡 2x150吨小仓方案 报价</t>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F2" s="55" t="inlineStr">
+        <is>
+          <t>进行中（近期可成交）</t>
+        </is>
+      </c>
+      <c r="G2" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="H2" s="56" t="inlineStr">
+        <is>
+          <t>标题重点；最接近成单</t>
+        </is>
+      </c>
+      <c r="I2" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
         </is>
       </c>
       <c r="J2" s="56" t="inlineStr">
         <is>
-          <t>已成交</t>
+          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K2" s="56" t="inlineStr">
+        <is>
+          <t>报价中</t>
         </is>
       </c>
     </row>
@@ -26056,41 +26064,46 @@
         </is>
       </c>
       <c r="C3" s="55" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D3" s="56" t="inlineStr">
         <is>
-          <t>蒙古 MAK 气力输送更新</t>
-        </is>
-      </c>
-      <c r="E3" s="55" t="inlineStr">
-        <is>
-          <t>进行中（近期可成交）</t>
-        </is>
-      </c>
-      <c r="F3" s="57" t="inlineStr">
+          <t>菲律宾生力取料机</t>
+        </is>
+      </c>
+      <c r="E3" s="58" t="inlineStr">
+        <is>
+          <t>补录</t>
+        </is>
+      </c>
+      <c r="F3" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="G3" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G3" s="56" t="inlineStr">
-        <is>
-          <t>最接近成单的在手重点</t>
-        </is>
-      </c>
-      <c r="H3" s="57" t="inlineStr">
+      <c r="H3" s="56" t="inlineStr">
+        <is>
+          <t>补录，标题未写重点；等授标</t>
+        </is>
+      </c>
+      <c r="I3" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I3" s="56" t="inlineStr">
-        <is>
-          <t>C00007247｜陈子凡｜工业｜MAK砖厂现有气力输送系统更新项目 ｜方案V1 | 重点项目</t>
-        </is>
-      </c>
       <c r="J3" s="56" t="inlineStr">
         <is>
-          <t>报价中</t>
+          <t>20260304 菲律宾生力集团 取料机报价</t>
+        </is>
+      </c>
+      <c r="K3" s="56" t="inlineStr">
+        <is>
+          <t>等授标通知</t>
         </is>
       </c>
     </row>
@@ -26106,91 +26119,101 @@
         </is>
       </c>
       <c r="C4" s="55" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D4" s="56" t="inlineStr">
         <is>
-          <t>菲律宾生力取料机</t>
+          <t>MONCEMENT 3×2000 水泥中转</t>
         </is>
       </c>
       <c r="E4" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F4" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F4" s="57" t="inlineStr">
+      <c r="G4" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G4" s="56" t="inlineStr">
-        <is>
-          <t>等授标</t>
-        </is>
-      </c>
-      <c r="H4" s="57" t="inlineStr">
+      <c r="H4" s="56" t="inlineStr">
+        <is>
+          <t>拜访后更新方案</t>
+        </is>
+      </c>
+      <c r="I4" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I4" s="56" t="inlineStr">
-        <is>
-          <t>20260304 菲律宾生力集团 取料机报价</t>
-        </is>
-      </c>
       <c r="J4" s="56" t="inlineStr">
         <is>
-          <t>等授标通知</t>
+          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K4" s="56" t="inlineStr">
+        <is>
+          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="55" t="inlineStr">
         <is>
-          <t>一组</t>
+          <t>二组</t>
         </is>
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>陈子凡</t>
+          <t>司斌</t>
         </is>
       </c>
       <c r="C5" s="55" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="D5" s="56" t="inlineStr">
         <is>
-          <t>MONCEMENT 3×2000 水泥中转</t>
+          <t>斯里兰卡 30×3500 稻谷</t>
         </is>
       </c>
       <c r="E5" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F5" s="57" t="inlineStr">
+      <c r="G5" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G5" s="56" t="inlineStr">
-        <is>
-          <t>拜访后更新方案</t>
-        </is>
-      </c>
-      <c r="H5" s="57" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr">
+        <is>
+          <t>已到决策期，钢构单价拿不到</t>
+        </is>
+      </c>
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I5" s="56" t="inlineStr">
-        <is>
-          <t>C00009104｜陈子凡｜工业｜MONCEMENT 3x2000水泥中转站｜方案V2 | 重点项目</t>
-        </is>
-      </c>
       <c r="J5" s="56" t="inlineStr">
         <is>
-          <t>更新方案中。拜访后按要求更新方案，有望近期落地</t>
+          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="K5" s="56" t="inlineStr">
+        <is>
+          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
         </is>
       </c>
     </row>
@@ -26202,95 +26225,105 @@
       </c>
       <c r="B6" s="55" t="inlineStr">
         <is>
-          <t>司斌</t>
+          <t>王伟超</t>
         </is>
       </c>
       <c r="C6" s="55" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D6" s="56" t="inlineStr">
         <is>
-          <t>斯里兰卡 30×3500 稻谷</t>
+          <t>哥斯达黎加咖啡仓</t>
         </is>
       </c>
       <c r="E6" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F6" s="57" t="inlineStr">
+      <c r="G6" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G6" s="56" t="inlineStr">
-        <is>
-          <t>已到决策期，钢构单价拿不到</t>
-        </is>
-      </c>
-      <c r="H6" s="57" t="inlineStr">
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>到过工厂，多次改图</t>
+        </is>
+      </c>
+      <c r="I6" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I6" s="56" t="inlineStr">
-        <is>
-          <t>C00009649｜司斌｜粮食｜斯里兰卡30*3500T稻谷仓 |方案V1|重点项目</t>
-        </is>
-      </c>
       <c r="J6" s="56" t="inlineStr">
         <is>
-          <t>老板自行决策，目前已到决策期，但是钢结构部分的报价客户告知6200CNY每吨，FOB含螺栓，采购部告知这个价格拿不到。客户对供货商成本把控严格，对国内采购价格深度熟悉，如果没有合适的价格，我们没有任何机会</t>
+          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K6" s="56" t="inlineStr">
+        <is>
+          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
         <is>
-          <t>二组</t>
+          <t>三组</t>
         </is>
       </c>
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>王伟超</t>
+          <t>王伟乐</t>
         </is>
       </c>
       <c r="C7" s="55" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D7" s="56" t="inlineStr">
         <is>
-          <t>哥斯达黎加咖啡仓</t>
+          <t>新加坡裕廊港 12×10000</t>
         </is>
       </c>
       <c r="E7" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F7" s="57" t="inlineStr">
+      <c r="G7" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G7" s="56" t="inlineStr">
-        <is>
-          <t>到过工厂，多次改图</t>
-        </is>
-      </c>
-      <c r="H7" s="57" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
+        <is>
+          <t>最新价澄清中</t>
+        </is>
+      </c>
+      <c r="I7" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I7" s="56" t="inlineStr">
-        <is>
-          <t>C00009044｜王伟超｜粮食｜哥斯达黎加室外2个175吨，室内32个咖啡豆仓｜方案V5 | 重点项目</t>
-        </is>
-      </c>
       <c r="J7" s="56" t="inlineStr">
         <is>
-          <t>已参观过公司和工厂，已发方案和报价，并且更新过多次方案与报价，正在调整图纸的细节变化，并且需要契合对方厂房中设备的安装位置，等待对方回复</t>
+          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+        </is>
+      </c>
+      <c r="K7" s="56" t="inlineStr">
+        <is>
+          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
         </is>
       </c>
     </row>
@@ -26306,91 +26339,101 @@
         </is>
       </c>
       <c r="C8" s="55" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D8" s="56" t="inlineStr">
         <is>
-          <t>新加坡裕廊港 12×10000</t>
+          <t>摩洛哥 CIMAF 1×700</t>
         </is>
       </c>
       <c r="E8" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F8" s="57" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="G8" s="56" t="inlineStr">
-        <is>
-          <t>最新价澄清中</t>
-        </is>
-      </c>
-      <c r="H8" s="57" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="I8" s="56" t="inlineStr">
-        <is>
-          <t>C00008344 |王伟乐|工业| 新加披裕廊港12*10000t水泥钢板仓项目|方案V1|重点项目</t>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>已报价、库龄偏长</t>
+        </is>
+      </c>
+      <c r="I8" s="58" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
         </is>
       </c>
       <c r="J8" s="56" t="inlineStr">
         <is>
-          <t>在更新方案和报价给咨询公司做前期招投标准备，目前报了一版最新的价格，还在澄清</t>
+          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
+        </is>
+      </c>
+      <c r="K8" s="56" t="inlineStr">
+        <is>
+          <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="55" t="inlineStr">
         <is>
-          <t>三组</t>
+          <t>五组</t>
         </is>
       </c>
       <c r="B9" s="55" t="inlineStr">
         <is>
-          <t>王伟乐</t>
+          <t>陈辉</t>
         </is>
       </c>
       <c r="C9" s="55" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="D9" s="56" t="inlineStr">
         <is>
-          <t>摩洛哥 CIMAF 1×700</t>
+          <t>韩国大宇 3 万吨磷矿粉</t>
         </is>
       </c>
       <c r="E9" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F9" s="58" t="inlineStr">
-        <is>
-          <t>浅层</t>
-        </is>
-      </c>
-      <c r="G9" s="56" t="inlineStr">
-        <is>
-          <t>已报价、库龄偏长</t>
-        </is>
-      </c>
-      <c r="H9" s="58" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
-        </is>
-      </c>
-      <c r="I9" s="56" t="inlineStr">
-        <is>
-          <t>C00007413|王伟乐|工业|摩洛哥CIMAF 1*700t 水泥装配仓项目|方案V7|重点项目</t>
+      <c r="G9" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="H9" s="56" t="inlineStr">
+        <is>
+          <t>多次报价，比仓型</t>
+        </is>
+      </c>
+      <c r="I9" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
         </is>
       </c>
       <c r="J9" s="56" t="inlineStr">
         <is>
-          <t>已报价，还在继续跟进，属于毛里塔尼亚老客户总部的项目</t>
+          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K9" s="56" t="inlineStr">
+        <is>
+          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
         </is>
       </c>
     </row>
@@ -26406,41 +26449,46 @@
         </is>
       </c>
       <c r="C10" s="55" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" s="56" t="inlineStr">
         <is>
-          <t>韩国大宇 3 万吨磷矿粉</t>
+          <t>Lanwa 水泥混拌</t>
         </is>
       </c>
       <c r="E10" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F10" s="57" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G10" s="56" t="inlineStr">
-        <is>
-          <t>多次报价，比仓型</t>
-        </is>
-      </c>
-      <c r="H10" s="57" t="inlineStr">
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>老客户，利润被压</t>
+        </is>
+      </c>
+      <c r="I10" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I10" s="56" t="inlineStr">
-        <is>
-          <t>C00007339｜陈辉｜工业｜韩国大宇3万吨磷矿粉项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
       <c r="J10" s="56" t="inlineStr">
         <is>
-          <t>大宇在土库曼化肥厂项目，仓型各种变化和多次报价后，目前最后一版是焊接仓的EPC。用户和大宇还在比较仓型。</t>
+          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K10" s="56" t="inlineStr">
+        <is>
+          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
         </is>
       </c>
     </row>
@@ -26456,41 +26504,46 @@
         </is>
       </c>
       <c r="C11" s="55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D11" s="56" t="inlineStr">
         <is>
-          <t>Lanwa 水泥混拌</t>
+          <t>塞拉利昂 2×3 万吨 clinker</t>
         </is>
       </c>
       <c r="E11" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F11" s="57" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="G11" s="56" t="inlineStr">
-        <is>
-          <t>老客户，利润被压</t>
-        </is>
-      </c>
-      <c r="H11" s="57" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="I11" s="56" t="inlineStr">
-        <is>
-          <t>C00008180｜陈辉｜工业｜Lanwa水泥混拌系统｜方案V1 | 重点项目</t>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>前期</t>
+        </is>
+      </c>
+      <c r="H11" s="56" t="inlineStr">
+        <is>
+          <t>已拜访，缺资金</t>
+        </is>
+      </c>
+      <c r="I11" s="58" t="inlineStr">
+        <is>
+          <t>前期调研</t>
         </is>
       </c>
       <c r="J11" s="56" t="inlineStr">
         <is>
-          <t>老客户，项目含3个仓+混拌（mixer客户从其他供应商订购），客户中国通，对中国钢材加工价格十万分的了解，仅允许报价有合理利润，超出会选其他供应商。</t>
+          <t>C00002715｜陈辉｜工业｜塞拉利昂2个3万吨clinker项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K11" s="56" t="inlineStr">
+        <is>
+          <t>已去拜访客户，客户想法很多，缺资金。</t>
         </is>
       </c>
     </row>
@@ -26502,95 +26555,105 @@
       </c>
       <c r="B12" s="55" t="inlineStr">
         <is>
-          <t>陈辉</t>
+          <t>冯乐</t>
         </is>
       </c>
       <c r="C12" s="55" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="D12" s="56" t="inlineStr">
         <is>
-          <t>塞拉利昂 2×3 万吨 clinker</t>
+          <t>坦桑 2×4500 小麦仓</t>
         </is>
       </c>
       <c r="E12" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F12" s="58" t="inlineStr">
-        <is>
-          <t>前期</t>
-        </is>
-      </c>
-      <c r="G12" s="56" t="inlineStr">
-        <is>
-          <t>已拜访，缺资金</t>
-        </is>
-      </c>
-      <c r="H12" s="58" t="inlineStr">
-        <is>
-          <t>前期调研</t>
-        </is>
-      </c>
-      <c r="I12" s="56" t="inlineStr">
-        <is>
-          <t>C00002715｜陈辉｜工业｜塞拉利昂2个3万吨clinker项目｜方案V1 | 重点项目</t>
+      <c r="G12" s="57" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="H12" s="56" t="inlineStr">
+        <is>
+          <t>曾接受报价，新要求已反馈</t>
+        </is>
+      </c>
+      <c r="I12" s="57" t="inlineStr">
+        <is>
+          <t>有效跟进</t>
         </is>
       </c>
       <c r="J12" s="56" t="inlineStr">
         <is>
-          <t>已去拜访客户，客户想法很多，缺资金。</t>
+          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K12" s="56" t="inlineStr">
+        <is>
+          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="55" t="inlineStr">
         <is>
-          <t>五组</t>
+          <t>六组</t>
         </is>
       </c>
       <c r="B13" s="55" t="inlineStr">
         <is>
-          <t>冯乐</t>
+          <t>苗恒</t>
         </is>
       </c>
       <c r="C13" s="55" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>坦桑 2×4500 小麦仓</t>
+          <t>墨西哥大型粮仓</t>
         </is>
       </c>
       <c r="E13" s="55" t="inlineStr">
         <is>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="F13" s="57" t="inlineStr">
+      <c r="G13" s="57" t="inlineStr">
         <is>
           <t>有效</t>
         </is>
       </c>
-      <c r="G13" s="56" t="inlineStr">
-        <is>
-          <t>曾接受报价，新要求已反馈</t>
-        </is>
-      </c>
-      <c r="H13" s="57" t="inlineStr">
+      <c r="H13" s="56" t="inlineStr">
+        <is>
+          <t>V4 后更报价 V2</t>
+        </is>
+      </c>
+      <c r="I13" s="57" t="inlineStr">
         <is>
           <t>有效跟进</t>
         </is>
       </c>
-      <c r="I13" s="56" t="inlineStr">
-        <is>
-          <t>C00009678｜冯乐｜坦桑尼亚｜小麦2×4500T装配仓项目｜方案V1 | 重点项目</t>
-        </is>
-      </c>
       <c r="J13" s="56" t="inlineStr">
         <is>
-          <t>客户主营粮食加工，此前已接受我方报价。回国与工程团队商讨后，客户提出了新要求，我方已做技术反馈。目前客户需视其农场情况再作回复。</t>
+          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K13" s="56" t="inlineStr">
+        <is>
+          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
         </is>
       </c>
     </row>
@@ -26606,158 +26669,117 @@
         </is>
       </c>
       <c r="C14" s="55" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D14" s="56" t="inlineStr">
         <is>
-          <t>墨西哥大型粮仓</t>
+          <t>孟加拉 2×3000 稻谷</t>
         </is>
       </c>
       <c r="E14" s="55" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F14" s="57" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="G14" s="56" t="inlineStr">
-        <is>
-          <t>V4 后更报价 V2</t>
-        </is>
-      </c>
-      <c r="H14" s="57" t="inlineStr">
-        <is>
-          <t>有效跟进</t>
-        </is>
-      </c>
-      <c r="I14" s="56" t="inlineStr">
-        <is>
-          <t>C00008938｜苗恒｜粮食｜墨西哥3x10000+2x5000+4x200+1x150粮仓项目｜方案V1 | 重点项目</t>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>暂停</t>
+        </is>
+      </c>
+      <c r="G14" s="58" t="inlineStr">
+        <is>
+          <t>已暂停</t>
+        </is>
+      </c>
+      <c r="H14" s="56" t="inlineStr">
+        <is>
+          <t>重点已暂停，处理正确</t>
+        </is>
+      </c>
+      <c r="I14" s="55" t="inlineStr">
+        <is>
+          <t>规范闭环</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr">
         <is>
-          <t>重点项目跟进中，客户反馈比较慢，下步计划确认方案V4后更新报价V2</t>
+          <t>C00008988｜苗恒｜粮食｜孟加拉2x3000吨稻谷仓项目｜方案V3 | 重点项目</t>
+        </is>
+      </c>
+      <c r="K14" s="56" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>六组</t>
+          <t>俄语组</t>
         </is>
       </c>
       <c r="B15" s="55" t="inlineStr">
         <is>
-          <t>苗恒</t>
+          <t>崔阳</t>
         </is>
       </c>
       <c r="C15" s="55" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="D15" s="56" t="inlineStr">
         <is>
-          <t>孟加拉 2×3000 稻谷</t>
+          <t>75 万吨小麦深加工</t>
         </is>
       </c>
       <c r="E15" s="55" t="inlineStr">
         <is>
-          <t>暂停</t>
-        </is>
-      </c>
-      <c r="F15" s="58" t="inlineStr">
-        <is>
-          <t>已暂停</t>
-        </is>
-      </c>
-      <c r="G15" s="56" t="inlineStr">
-        <is>
-          <t>重点已暂停，处理正确</t>
-        </is>
-      </c>
-      <c r="H15" s="55" t="inlineStr">
-        <is>
-          <t>规范闭环</t>
-        </is>
-      </c>
-      <c r="I15" s="56" t="inlineStr">
-        <is>
-          <t>C00008988｜苗恒｜粮食｜孟加拉2x3000吨稻谷仓项目｜方案V3 | 重点项目</t>
+          <t>标题标注</t>
+        </is>
+      </c>
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="G15" s="58" t="inlineStr">
+        <is>
+          <t>浅层</t>
+        </is>
+      </c>
+      <c r="H15" s="56" t="inlineStr">
+        <is>
+          <t>只写「进行中 重点任务」，无下一步</t>
+        </is>
+      </c>
+      <c r="I15" s="58" t="inlineStr">
+        <is>
+          <t>浅层等待</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
-        <is>
-          <t>俄语组</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="inlineStr">
-        <is>
-          <t>崔阳</t>
-        </is>
-      </c>
-      <c r="C16" s="55" t="n">
-        <v>58</v>
-      </c>
-      <c r="D16" s="56" t="inlineStr">
-        <is>
-          <t>75 万吨小麦深加工</t>
-        </is>
-      </c>
-      <c r="E16" s="55" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="F16" s="58" t="inlineStr">
-        <is>
-          <t>浅层</t>
-        </is>
-      </c>
-      <c r="G16" s="56" t="inlineStr">
-        <is>
-          <t>只写「进行中 重点任务」，无下一步</t>
-        </is>
-      </c>
-      <c r="H16" s="58" t="inlineStr">
-        <is>
-          <t>浅层等待</t>
-        </is>
-      </c>
-      <c r="I16" s="56" t="inlineStr">
-        <is>
           <t>C00009094|崔阳|粮食|75万吨小麦深加工项目|方案V1|重点项目</t>
         </is>
       </c>
-      <c r="J16" s="56" t="inlineStr">
+      <c r="K15" s="56" t="inlineStr">
         <is>
           <t>进行中 重点任务</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="59" t="inlineStr">
-        <is>
-          <t>15 = 已签约 1 + 进行中有效 10 + 该降级/已暂停 4（CIMAF 浅层、塞拉利昂前期、孟加拉暂停、崔阳 75 万吨浅层）。</t>
+    <row r="17">
+      <c r="A17" s="75" t="inlineStr">
+        <is>
+          <t>14 = 进行中有效 10 + 该降级/已暂停 4。生力取料机为补录。唯一签约 MAK 2×150 不在本清单。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:K15"/>
   <mergeCells count="1">
-    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -26765,17 +26787,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -26796,15 +26817,10 @@
       </c>
       <c r="D1" s="54" t="inlineStr">
         <is>
-          <t>已签约</t>
+          <t>进行中有效</t>
         </is>
       </c>
       <c r="E1" s="54" t="inlineStr">
-        <is>
-          <t>进行中有效</t>
-        </is>
-      </c>
-      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>该降级 / 已暂停</t>
         </is>
@@ -26822,15 +26838,12 @@
         </is>
       </c>
       <c r="C2" s="61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26854,9 +26867,6 @@
       <c r="E3" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="55" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="55" t="inlineStr">
@@ -26873,12 +26883,9 @@
         <v>1</v>
       </c>
       <c r="D4" s="55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26897,12 +26904,9 @@
         <v>1</v>
       </c>
       <c r="D5" s="55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26921,12 +26925,9 @@
         <v>2</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="E6" s="58" t="inlineStr">
         <is>
           <t>1 浅层</t>
         </is>
@@ -26952,9 +26953,6 @@
       <c r="E7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="55" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="55" t="inlineStr">
@@ -26971,12 +26969,9 @@
         <v>3</v>
       </c>
       <c r="D8" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="58" t="inlineStr">
+      <c r="E8" s="58" t="inlineStr">
         <is>
           <t>1 前期</t>
         </is>
@@ -26997,12 +26992,9 @@
         <v>1</v>
       </c>
       <c r="D9" s="55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27026,9 +27018,6 @@
       <c r="E10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="55" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="55" t="inlineStr">
@@ -27045,12 +27034,9 @@
         <v>2</v>
       </c>
       <c r="D11" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="58" t="inlineStr">
+      <c r="E11" s="58" t="inlineStr">
         <is>
           <t>1 已暂停</t>
         </is>
@@ -27073,10 +27059,7 @@
       <c r="D12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="58" t="inlineStr">
+      <c r="E12" s="58" t="inlineStr">
         <is>
           <t>1 浅层</t>
         </is>
@@ -27102,11 +27085,8 @@
       <c r="E13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
+    </row>
+    <row r="14">
       <c r="A14" s="63" t="inlineStr">
         <is>
           <t>合计</t>
@@ -27114,32 +27094,28 @@
       </c>
       <c r="B14" s="63" t="n"/>
       <c r="C14" s="63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E14" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="63" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="64" t="inlineStr">
-        <is>
-          <t>陈子凡 4 条全有效（含唯一签约）。该降级 4 条：王伟乐 CIMAF 浅层、陈辉塞拉利昂前期、苗恒孟加拉已暂停、崔阳 75 万吨浅层。韩鸿彪未标重点，但有效项目率全员最高。</t>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="59" t="inlineStr">
+        <is>
+          <t>14 = 进行中有效 10 + 该降级/已暂停 4。生力取料机为补录。唯一签约 MAK 2×150 不在本清单。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:E13"/>
   <mergeCells count="1">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
